--- a/FOA SETS/Upholstery-Set.xlsx
+++ b/FOA SETS/Upholstery-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,20 +776,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ABERPORTH Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Features
-- Lawson Design
-- Box Seat Cushion
-- Loose Pillow Back
-- Rolled Arms
-- Tapered Plastic Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 87" L x 37" W x 38" H (SEAT HT: 18", SEAT DP: 21"); feature: Transitional
-- Loveseat: color: Gray; dimensions: 64" L x 37" W x 38" H (SEAT HT: 18", SEAT DP: 21"); feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Gray
-Weight: 234 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ABERPORTH Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Lawson Design&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Tapered Plastic Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 87" L x 37" W x 38" H (SEAT HT: 18", SEAT DP: 21"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 64" L x 37" W x 38" H (SEAT HT: 18", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 234 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -902,24 +902,24 @@
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ACAPULCO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, then finished in Black or Off-White tones to suit a range of interiors.
-Product Dimensions: Sofa: 84.5"L X 42"W X 48.5"H
-Features
-- Traditional
-- Black or Off-White
-- Diamond Tufted Back
-- Crown Molding
-- Carved Details
-- Cabriole Style Legs
-- Box Seat Cushion w/ Welt
-- Wing Back Design
-- Accent Pillow Included Included items and dimensions:
-- Sofa: color: Black or Off-White; dimensions: 84.5" W x 43"D x 48" H; feature: Traditional
-- Loveseat: color: Black or Off-White; dimensions: 70.5" W x 43"D x 48" H; feature: Traditional
-Materials: Fabric, Solid Wood.
-Color: Black or Off-White
-Weight: 347.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ACAPULCO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, then finished in Black or Off-White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 84.5"L X 42"W X 48.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Black or Off-White&lt;br&gt;
+- Diamond Tufted Back&lt;br&gt;
+- Crown Molding&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Cabriole Style Legs&lt;br&gt;
+- Box Seat Cushion w/ Welt&lt;br&gt;
+- Wing Back Design&lt;br&gt;
+- Accent Pillow Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black or Off-White; dimensions: 84.5" W x 43"D x 48" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Black or Off-White; dimensions: 70.5" W x 43"D x 48" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Black or Off-White&lt;br&gt;
+Weight: 347.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
@@ -1041,23 +1041,23 @@
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ACAPULCO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Fabric, Solid Wood, construction and Off-White tones, it blends durability with visual warmth.
-Product Dimensions: Sofa: 84.5"L X 42"W X 48.5"H
-Features
-- Traditional
-- Diamond Tufted Back
-- Crown Molding
-- Carved Details
-- Cabriole Style Legs
-- Box Seat Cushion w/ Welt
-- Wing Back Design
-- Accent Pillow Included Included items and dimensions:
-- Sofa: color: Off-White; dimensions: 84.5" W x 43"D x 48" H; feature: Traditional
-- Loveseat: color: Off-White; dimensions: 70.5" W x 43"D x 48" H; feature: Traditional
-Materials: Fabric, Solid Wood.
-Color: Off-White
-Weight: 355.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ACAPULCO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Fabric, Solid Wood, construction and Off-White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Sofa: 84.5"L X 42"W X 48.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Diamond Tufted Back&lt;br&gt;
+- Crown Molding&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Cabriole Style Legs&lt;br&gt;
+- Box Seat Cushion w/ Welt&lt;br&gt;
+- Wing Back Design&lt;br&gt;
+- Accent Pillow Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White; dimensions: 84.5" W x 43"D x 48" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Off-White; dimensions: 70.5" W x 43"D x 48" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Off-White&lt;br&gt;
+Weight: 355.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ADELPHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.
-Product Dimensions: 89"W X 37"D X 30"H Included items and dimensions:
-- Sofa: color: Beige or Gold; dimensions: 89" W x 37"D x 30" H; feature: Glam
-- Loveseat: color: Beige or Gold; dimensions: 72.5" W x 37"D x 30" H; feature: Glam
-Weight: 348 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ADELPHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 89"W X 37"D X 30"H Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Gold; dimensions: 89" W x 37"D x 30" H; feature: Glam&lt;br&gt;
+- Loveseat: color: Beige or Gold; dimensions: 72.5" W x 37"D x 30" H; feature: Glam&lt;br&gt;
+Weight: 348 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1281,22 +1281,22 @@
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALBACETE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Velvet, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.
-Product Dimensions: 94 1/2" X 41 3/4" X 26"
-Features
-- Traditional
-- Dark Cherry or Brown
-- Button Tufted Back
-- Carved Details
-- Reversible Seat Cushion w/ Welt
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Dark Cherry or Brown; dimensions: 94.5" x 48.25" x 38.5"; feature: Traditional
-- Loveseat: color: Dark Cherry or Brown; dimensions: 69.5" x 48.25" x 38.5"; feature: Traditional
-Materials: Velvet, Solid Wood.
-Color: Dark Cherry or Brown
-Weight: 420.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALBACETE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Velvet, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 94 1/2" X 41 3/4" X 26"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Brown&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Reversible Seat Cushion w/ Welt&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Cherry or Brown; dimensions: 94.5" x 48.25" x 38.5"; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Cherry or Brown; dimensions: 69.5" x 48.25" x 38.5"; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Brown&lt;br&gt;
+Weight: 420.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALBACETE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Velvet, Solid Wood, construction and Champagne or Purple tones, it blends durability with visual warmth.
-Product Dimensions: 94.5" X 48.25" X 38.5"
-Features
-- Traditional
-- Champagne or Purple
-- Button Tufted Back
-- Carved Details
-- Reversible Seat Cushion w/ Welt
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Champagne or Purple; dimensions: 94.5" x 48.25" x 38.5"; feature: Traditional
-- Loveseat: color: Champagne or Purple; dimensions: 69.5" x 48.25" x 38.5"; feature: Traditional
-Materials: Velvet, Solid Wood.
-Color: Champagne or Purple
-Weight: 430.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALBACETE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Velvet, Solid Wood, construction and Champagne or Purple tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 94.5" X 48.25" X 38.5"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Champagne or Purple&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Reversible Seat Cushion w/ Welt&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Champagne or Purple; dimensions: 94.5" x 48.25" x 38.5"; feature: Traditional&lt;br&gt;
+- Loveseat: color: Champagne or Purple; dimensions: 69.5" x 48.25" x 38.5"; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet, Solid Wood.&lt;br&gt;
+Color: Champagne or Purple&lt;br&gt;
+Weight: 430.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" s="16" t="inlineStr">
@@ -1555,23 +1555,23 @@
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALESUND Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Fabric, Solid Wood, construction and Beige or Light Oak tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 87"W X 38"D X 33"H (SEAT HT: 19", SEAT DP: 23")
-Features
-- Beige or Light Oak
-- Ash Wood Trim
-- Rattan Details
-- Reversible Loose Pillow Back
-- Webbing Seat Suspension
-- Tapered Wooden Leg
-- Side Bolster Pillow
-- Feather Fiber Pillow Construction Included items and dimensions:
-- Sofa: color: Beige or Light Oak; dimensions: 87" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern
-- Loveseat: color: Beige or Light Oak; dimensions: 65" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern
-Materials: Fabric, Solid Wood.
-Color: Beige or Light Oak
-Weight: 323 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALESUND Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Fabric, Solid Wood, construction and Beige or Light Oak tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 87"W X 38"D X 33"H (SEAT HT: 19", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Light Oak&lt;br&gt;
+- Ash Wood Trim&lt;br&gt;
+- Rattan Details&lt;br&gt;
+- Reversible Loose Pillow Back&lt;br&gt;
+- Webbing Seat Suspension&lt;br&gt;
+- Tapered Wooden Leg&lt;br&gt;
+- Side Bolster Pillow&lt;br&gt;
+- Feather Fiber Pillow Construction Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Light Oak; dimensions: 87" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;br&gt;
+- Loveseat: color: Beige or Light Oak; dimensions: 65" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Beige or Light Oak&lt;br&gt;
+Weight: 323 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
@@ -1693,23 +1693,23 @@
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALESUND Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Finished in Beige or Walnut tones, the Fabric, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 87"W X 38"D X 33"H (SEAT HT: 19", SEAT DP: 23")
-Features
-- Beige or Walnut
-- Ash Wood Trim
-- Rattan Details
-- Reversible Loose Pillow Back
-- Webbing Seat Suspension
-- Tapered Wooden Leg
-- Side Bolster Pillow
-- Feather Fiber Pillow Construction Included items and dimensions:
-- Sofa: color: Beige or Walnut; dimensions: 87" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern
-- Loveseat: color: Beige or Walnut; dimensions: 65" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern
-Materials: Fabric, Solid Wood.
-Color: Beige or Walnut
-Weight: 323 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALESUND Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Finished in Beige or Walnut tones, the Fabric, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 87"W X 38"D X 33"H (SEAT HT: 19", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Walnut&lt;br&gt;
+- Ash Wood Trim&lt;br&gt;
+- Rattan Details&lt;br&gt;
+- Reversible Loose Pillow Back&lt;br&gt;
+- Webbing Seat Suspension&lt;br&gt;
+- Tapered Wooden Leg&lt;br&gt;
+- Side Bolster Pillow&lt;br&gt;
+- Feather Fiber Pillow Construction Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Walnut; dimensions: 87" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;br&gt;
+- Loveseat: color: Beige or Walnut; dimensions: 65" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Beige or Walnut&lt;br&gt;
+Weight: 323 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
@@ -1830,22 +1830,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AMAYA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Linen-like, Solid Wood, then finished in Cream tones to suit a range of interiors.
-Product Dimensions: 90"L X 37"W X 35"H (SEAT HT: 21", SEAT DP: 21 1/2")
-Features
-- Amish-built Frame
-- Loose Back &amp; Box Seat Cushions
-- Rolled Arms
-- Welt Trim
-- Turned Bun Legs
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Cream; dimensions: 90" L x 37" W x 35" H (SEAT HT: 21", SEAT DP: 21 1 or 2"); feature: Transitional
-- Loveseat: color: Cream; dimensions: 67" L x 37" W x 35" H (SEAT HT: 21", SEAT DP: 21 1 or 2"); feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Cream
-Weight: 303 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AMAYA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Linen-like, Solid Wood, then finished in Cream tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 90"L X 37"W X 35"H (SEAT HT: 21", SEAT DP: 21 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Amish-built Frame&lt;br&gt;
+- Loose Back &amp;amp; Box Seat Cushions&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Turned Bun Legs&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Cream; dimensions: 90" L x 37" W x 35" H (SEAT HT: 21", SEAT DP: 21 1 or 2"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Cream; dimensions: 67" L x 37" W x 35" H (SEAT HT: 21", SEAT DP: 21 1 or 2"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Cream&lt;br&gt;
+Weight: 303 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1962,23 +1962,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANDALUSIA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, Pine, Foam, Other construction and Light Brown or Dark Cherry tones, it blends durability with visual warmth.
-Product Dimensions: SF: 95"W X 36"D X 44"H, LV: 73"W X 36"D X 44"H
-Features
-- Traditional
-- Light Brown or Dark Cherry
-- 100% Polyester Fabric
-- Ornate Carved Details
-- Jacquard Pattern Box Seat Cushion
-- Rolled Arms
-- Pillows Included
-- Bun Feet Included items and dimensions:
-- Sofa: color: Light Brown or Dark Cherry; dimensions: 95" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional
-- Loveseat: color: Light Brown or Dark Cherry; dimensions: 73" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional
-Materials: Fabric, Solid Wood, Pine, Foam, Other.
-Color: Light Brown or Dark Cherry
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANDALUSIA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, Pine, Foam, Other construction and Light Brown or Dark Cherry tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SF: 95"W X 36"D X 44"H, LV: 73"W X 36"D X 44"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Light Brown or Dark Cherry&lt;br&gt;
+- 100% Polyester Fabric&lt;br&gt;
+- Ornate Carved Details&lt;br&gt;
+- Jacquard Pattern Box Seat Cushion&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Bun Feet Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Brown or Dark Cherry; dimensions: 95" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Light Brown or Dark Cherry; dimensions: 73" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Pine, Foam, Other.&lt;br&gt;
+Color: Light Brown or Dark Cherry&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2096,18 +2096,18 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTOINETTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. With Velvet-like, Solid Wood, construction and White tones, it blends durability with visual warmth.
-Features
-- Chesterfield Inspired Design
-- Deep Tufting w/ Acrylic Buttons
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: White; dimensions: 86 1 or 2" L x 39 1 or 2" W x 4" H (SEAT HT: 21 1 or 2", SEAT DP: 26"); feature: Glam
-- Loveseat: color: White; dimensions: 68" L x 39 1 or 2" W x 4" H (SEAT HT: 21 1 or 2", SEAT DP: 26"); feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: White
-Weight: 257 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTOINETTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. With Velvet-like, Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Chesterfield Inspired Design&lt;br&gt;
+- Deep Tufting w/ Acrylic Buttons&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: White; dimensions: 86 1 or 2" L x 39 1 or 2" W x 4" H (SEAT HT: 21 1 or 2", SEAT DP: 26"); feature: Glam&lt;br&gt;
+- Loveseat: color: White; dimensions: 68" L x 39 1 or 2" W x 4" H (SEAT HT: 21 1 or 2", SEAT DP: 26"); feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 257 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2225,18 +2225,18 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTOINETTE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.
-Features
-- Chesterfield Inspired Design
-- Deep Tufting w/ Acrylic Buttons
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Gray; dimensions: 91" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Glam
-- Loveseat: color: Gray; dimensions: 68" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Glam
-Materials: Velvet-like, Solid Wood.
-Color: Gray
-Weight: 257 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTOINETTE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Chesterfield Inspired Design&lt;br&gt;
+- Deep Tufting w/ Acrylic Buttons&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 91" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Glam&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 68" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 257 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -2353,19 +2353,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ATTWELL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Gray tones, the Linen-like Fabric, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 71"L X 32"W X 35"H
-Features
-- Tuxedo-inspired Design
-- Button Tufted Sides &amp; Seat
-- Track Arms
-- Nailhead Trim Included items and dimensions:
-- Sofa: color: Gray; dimensions: 71" L x 31" W x 35" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 58" L x 31" W x 35" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Gray
-Weight: 170.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ATTWELL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Gray tones, the Linen-like Fabric, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 71"L X 32"W X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Tuxedo-inspired Design&lt;br&gt;
+- Button Tufted Sides &amp;amp; Seat&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Nailhead Trim Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 71" L x 31" W x 35" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 58" L x 31" W x 35" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 170.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2482,23 +2482,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AZULETTI Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Velvet-like, Solid Wood, and finished in Dark Teal or Apple Green tones for a clean, cohesive look.
-Product Dimensions: 90"L X 36"W X 36"H (SEAT HT: 20 1/2", SEAT DP: 23")
-Features
-- Dark Teal or Apple Green
-- Button Tufted Back
-- Pillows w/ Hypo-allergenic Synthetic Down
-- Tuxedo Design &amp; Bench-style Single Cushion Seating
-- Frame Corner Blocked &amp; Glued
-- Individual Nailheads &amp; Welt Trim
-- Round Tapered Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Dark Teal or Apple Green; dimensions: 90" L x 36" W x 36" H (SEAT HT: 20 1 or 2", SEAT DP: 23"); feature: Transitional
-- Loveseat: color: Dark Teal or Apple Green; dimensions: 63" L x 36" W x 36" H (SEAT HT: 20 1 or 2", SEAT DP: 23"); feature: Transitional
-Materials: Velvet-like, Solid Wood.
-Color: Dark Teal or Apple Green
-Weight: 235 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AZULETTI Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Velvet-like, Solid Wood, and finished in Dark Teal or Apple Green tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 90"L X 36"W X 36"H (SEAT HT: 20 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Dark Teal or Apple Green&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Pillows w/ Hypo-allergenic Synthetic Down&lt;br&gt;
+- Tuxedo Design &amp;amp; Bench-style Single Cushion Seating&lt;br&gt;
+- Frame Corner Blocked &amp;amp; Glued&lt;br&gt;
+- Individual Nailheads &amp;amp; Welt Trim&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Teal or Apple Green; dimensions: 90" L x 36" W x 36" H (SEAT HT: 20 1 or 2", SEAT DP: 23"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Dark Teal or Apple Green; dimensions: 63" L x 36" W x 36" H (SEAT HT: 20 1 or 2", SEAT DP: 23"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Dark Teal or Apple Green&lt;br&gt;
+Weight: 235 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2615,22 +2615,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BASIE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: SOFA: 94"L X 37"W X 42"H
-Features
-- Medium Density Foam
-- Wide Track Arms
-- Angled Back
-- Box Cushion Seating
-- Loose Back Pillows
-- Block Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 94" L x 37" W x 42" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 68" L x 37" W x 42" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Gray
-Weight: 277 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BASIE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Wide Track Arms&lt;br&gt;
+- Angled Back&lt;br&gt;
+- Box Cushion Seating&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Block Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 94" L x 37" W x 42" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 68" L x 37" W x 42" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 277 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2748,23 +2748,23 @@
       </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELSIZE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Beige or Navy tones for a clean, cohesive look.
-Product Dimensions: 91"L X 38"W X 40"H
-Features
-- Beige or Navy
-- Box Seat Cushions
-- Loose Pillow Backs
-- Padded Sloped Armrests
-- Individual Nailheads
-- Welt Trim
-- Tapered Block Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Beige or Navy; dimensions: 91" L x 38" W x 40" H; feature: Transitional
-- Loveseat: color: Beige or Navy; dimensions: 70" L x 38" W x 40" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Beige or Navy
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELSIZE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Beige or Navy tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 91"L X 38"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Navy&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Padded Sloped Armrests&lt;br&gt;
+- Individual Nailheads&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Tapered Block Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Navy; dimensions: 91" L x 38" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige or Navy; dimensions: 70" L x 38" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Beige or Navy&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -2886,23 +2886,23 @@
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELSIZE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Linen-like, Solid Wood, then finished in Chocolate or Tan tones to suit a range of interiors.
-Product Dimensions: 91"L X 38"W X 40"H
-Features
-- Chocolate or Tan
-- Box Seat Cushions
-- Loose Pillow Backs
-- Padded Sloped Armrests
-- Individual Nailheads
-- Welt Trim
-- Tapered Block Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Chocolate or Tan; dimensions: 91" L x 38" W x 40" H; feature: Transitional
-- Loveseat: color: Chocolate or Tan; dimensions: 70" L x 38" W x 40" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Chocolate or Tan
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELSIZE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Linen-like, Solid Wood, then finished in Chocolate or Tan tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 91"L X 38"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Chocolate or Tan&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Padded Sloped Armrests&lt;br&gt;
+- Individual Nailheads&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Tapered Block Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Chocolate or Tan; dimensions: 91" L x 38" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Chocolate or Tan; dimensions: 70" L x 38" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Chocolate or Tan&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -3024,23 +3024,23 @@
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BELSIZE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Linen-like, Solid Wood, construction and Light Taupe or Black tones, it blends durability with visual warmth.
-Product Dimensions: 91"L X 38"W X 40"H
-Features
-- Light Taupe or Black
-- Box Seat Cushions
-- Loose Pillow Backs
-- Padded Sloped Armrests
-- Individual Nailheads
-- Welt Trim
-- Tapered Block Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Light Taupe or Black; dimensions: 91" L x 38" W x 40" H; feature: Transitional
-- Loveseat: color: Light Taupe or Black; dimensions: 70" L x 38" W x 40" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Light Taupe or Black
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BELSIZE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Linen-like, Solid Wood, construction and Light Taupe or Black tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 91"L X 38"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Taupe or Black&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Padded Sloped Armrests&lt;br&gt;
+- Individual Nailheads&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Tapered Block Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Taupe or Black; dimensions: 91" L x 38" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Taupe or Black; dimensions: 70" L x 38" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Light Taupe or Black&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -3162,18 +3162,18 @@
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIENNE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Black tones for a clean, cohesive look.
-Product Dimensions: SOFA: 38.6"L X 35.4"W X 40.6"H, LOVESEAT: 62.6"L X 35.4"W X 40.6"H
-Features
-- Flared Padded Arms
-- Welt Trim
-- FSC Certified Included items and dimensions:
-- Sofa: color: Black; dimensions: 86" W x 35.5"D x 40.5" H; feature: Transitional
-- Loveseat: color: Black; dimensions: 62.5" W x 35.5"D x 40.5" H; feature: Transitional
-Materials: Leather Match, Metal.
-Color: Black
-Weight: 363.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIENNE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Black tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 38.6"L X 35.4"W X 40.6"H, LOVESEAT: 62.6"L X 35.4"W X 40.6"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Flared Padded Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black; dimensions: 86" W x 35.5"D x 40.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Black; dimensions: 62.5" W x 35.5"D x 40.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 363.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -3295,18 +3295,18 @@
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BIENNE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Metal, then finished in Taupe tones to suit a range of interiors.
-Product Dimensions: SOFA: 38.6"L X 35.4"W X 40.6"H, LOVESEAT: 62.6"L X 35.4"W X 40.6"H
-Features
-- Flared Padded Arms
-- Welt Trim
-- FSC Certified Included items and dimensions:
-- Sofa: color: Taupe; dimensions: 86" W x 35.5"D x 40.5" H; feature: Transitional
-- Loveseat: color: Taupe; dimensions: 62.5" W x 35.5"D x 40.5" H; feature: Transitional
-Materials: Leather Match, Metal.
-Color: Taupe
-Weight: 372.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BIENNE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Metal, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 38.6"L X 35.4"W X 40.6"H, LOVESEAT: 62.6"L X 35.4"W X 40.6"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Flared Padded Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Sofa: color: Taupe; dimensions: 86" W x 35.5"D x 40.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Taupe; dimensions: 62.5" W x 35.5"D x 40.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 372.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -3428,20 +3428,20 @@
       </c>
       <c r="G22" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BONAVENTURA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in Brown tones to suit a range of interiors.
-Product Dimensions: SOFA: 92"L X 43"W X 41"H
-Features
-- T-Cushion Seating
-- Rolled Arms
-- Fitted Back Pillows
-- Block Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Brown; dimensions: 92" L x 43" W x 41" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 69" L x 43" W x 41" H; feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Brown
-Weight: 282 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BONAVENTURA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 92"L X 43"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Cushion Seating&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Fitted Back Pillows&lt;br&gt;
+- Block Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 92" L x 43" W x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 69" L x 43" W x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 282 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" s="26" t="inlineStr">
@@ -3563,20 +3563,20 @@
       </c>
       <c r="G23" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BONAVENTURA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Fabric, Solid Wood construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 92"L X 43"W X 41"H
-Features
-- T-Cushion Seating
-- Rolled Arms
-- Fitted Back Pillows
-- Block Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray or Pattern; dimensions: 92" L x 43" W x 41" H; feature: Transitional
-- Loveseat: color: Gray or Pattern; dimensions: 69" L x 43" W x 41" H; feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Gray
-Weight: 282 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BONAVENTURA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Fabric, Solid Wood construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 92"L X 43"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Cushion Seating&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Fitted Back Pillows&lt;br&gt;
+- Block Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray or Pattern; dimensions: 92" L x 43" W x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray or Pattern; dimensions: 69" L x 43" W x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 282 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="26" t="inlineStr">
@@ -3697,19 +3697,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BRIANA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Beige or Gold tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Features
-- Beige or Gold
-- Individual Nailhead Trim
-- Wood Construction
-- Rolled Arms
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige or Gold; dimensions: 94" L x 40" W x 40" H; feature: Transitional
-- Loveseat: color: Beige or Gold; dimensions: 68" L x 40" W x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Beige or Gold
-Weight: 293 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BRIANA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Beige or Gold tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Gold&lt;br&gt;
+- Individual Nailhead Trim&lt;br&gt;
+- Wood Construction&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Gold; dimensions: 94" L x 40" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige or Gold; dimensions: 68" L x 40" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige or Gold&lt;br&gt;
+Weight: 293 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3821,22 +3821,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CASSANI Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Light Gray or Walnut tones, it blends durability with visual warmth.
-Features
-- Traditional
-- Light Gray or Walnut
-- Box Seat Cushions
-- Rolled Arms
-- Faux Wood Carved Details
-- Wooden Cabriole Bracket Leg
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Light Gray or Walnut; dimensions: 89" L x 35" W x 37" H (SEAT HT: 23", SEAT DP: 2"); feature: Traditional
-- Loveseat: color: Light Gray or Walnut; dimensions: 68" L x 35" W x 37" H (SEAT HT: 23", SEAT DP: 2"); feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Light Gray or Walnut
-Weight: 250 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CASSANI Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Light Gray or Walnut tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Light Gray or Walnut&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Faux Wood Carved Details&lt;br&gt;
+- Wooden Cabriole Bracket Leg&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray or Walnut; dimensions: 89" L x 35" W x 37" H (SEAT HT: 23", SEAT DP: 2"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Light Gray or Walnut; dimensions: 68" L x 35" W x 37" H (SEAT HT: 23", SEAT DP: 2"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Light Gray or Walnut&lt;br&gt;
+Weight: 250 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3948,23 +3948,23 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CATALONIA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Beige or Dark Cherry tones, the Fabric, Solid Wood, Pine, Foam, Other build keeps the look polished and practical.
-Product Dimensions: SF: 95"W X 36"D X 40"H, LV: 73"W X 36"D X 40"H
-Features
-- Traditional
-- Beige or Dark Cherry
-- Button Tufted Back
-- Ornate Details
-- Bench Style Seat Cushion w/ Welt
-- Rolled Arms
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Beige or Dark Cherry; dimensions: 95" W x 36"D x 40" H (SEAT HT: 21", SEAT DP: 23"); feature: Traditional
-- Loveseat: color: Beige or Dark Cherry; dimensions: 73" W x 36"D x 40" H (SEAT HT: 21", SEAT DP: 23"); feature: Traditional
-Materials: Fabric, Solid Wood, Pine, Foam, Other.
-Color: Beige or Dark Cherry
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CATALONIA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Beige or Dark Cherry tones, the Fabric, Solid Wood, Pine, Foam, Other build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SF: 95"W X 36"D X 40"H, LV: 73"W X 36"D X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Beige or Dark Cherry&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Ornate Details&lt;br&gt;
+- Bench Style Seat Cushion w/ Welt&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Dark Cherry; dimensions: 95" W x 36"D x 40" H (SEAT HT: 21", SEAT DP: 23"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Beige or Dark Cherry; dimensions: 73" W x 36"D x 40" H (SEAT HT: 21", SEAT DP: 23"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Pine, Foam, Other.&lt;br&gt;
+Color: Beige or Dark Cherry&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4081,23 +4081,23 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CATARINA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood, and finished in Beige or Teal tones for a clean, cohesive look.
-Product Dimensions: 91"L X 39"W X 37"H (SEAT HT: 19", SEAT DP: 29")
-Features
-- Beige or Teal
-- Low Profile Track Arms
-- Plush Fabric w/ Metallic Fiber Weave
-- Bench-style Single Cushion Seating or Back
-- Pillows w/ Hypo-allergenic Synthetic Down
-- Frame Corner Blocked &amp; Glued
-- Welt Trim &amp; Tapered Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Beige or Teal; dimensions: 91" L x 39" W x 37" H (SEAT HT: 19", SEAT DP: 29"); feature: Transitional
-- Loveseat: color: Beige or Teal; dimensions: 64" L x 39" W x 37" H (SEAT HT: 19", SEAT DP: 29"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Beige or Teal
-Weight: 260 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CATARINA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood, and finished in Beige or Teal tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 91"L X 39"W X 37"H (SEAT HT: 19", SEAT DP: 29")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Teal&lt;br&gt;
+- Low Profile Track Arms&lt;br&gt;
+- Plush Fabric w/ Metallic Fiber Weave&lt;br&gt;
+- Bench-style Single Cushion Seating or Back&lt;br&gt;
+- Pillows w/ Hypo-allergenic Synthetic Down&lt;br&gt;
+- Frame Corner Blocked &amp;amp; Glued&lt;br&gt;
+- Welt Trim &amp;amp; Tapered Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Teal; dimensions: 91" L x 39" W x 37" H (SEAT HT: 19", SEAT DP: 29"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige or Teal; dimensions: 64" L x 39" W x 37" H (SEAT HT: 19", SEAT DP: 29"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige or Teal&lt;br&gt;
+Weight: 260 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CHARLEVOIX Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.
-Product Dimensions: 89"W X 36"D X 32"H (SEAT HT: 19", SEAT DP: 26") Included items and dimensions:
-- Sofa: color: Beige or Gold; dimensions: 89" W x 36"D x 32" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam
-- Loveseat: color: Beige or Gold; dimensions: 67.5" W x 36"D x 32" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam
-Weight: 345 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CHARLEVOIX Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 89"W X 36"D X 32"H (SEAT HT: 19", SEAT DP: 26") Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Gold; dimensions: 89" W x 36"D x 32" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam&lt;br&gt;
+- Loveseat: color: Beige or Gold; dimensions: 67.5" W x 36"D x 32" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam&lt;br&gt;
+Weight: 345 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4316,20 +4316,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CHRISTINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Linen-like Fabric, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 94"L X 43"W X 40"H
-Features
-- Flared Arms
-- T-Cushion Seat
-- Wingback Design
-- Square Tapered Feet
-- Sun &amp; Stain Resistant Revolution Fabric Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 94" L x 43" W x 40" H; feature: Transitional
-- Loveseat: color: Light Gray; dimensions: 68" L x 43" W x 40" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Light Gray
-Weight: 250 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CHRISTINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Linen-like Fabric, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 43"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Flared Arms&lt;br&gt;
+- T-Cushion Seat&lt;br&gt;
+- Wingback Design&lt;br&gt;
+- Square Tapered Feet&lt;br&gt;
+- Sun &amp;amp; Stain Resistant Revolution Fabric Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 94" L x 43" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 68" L x 43" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 250 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4443,14 +4443,14 @@
       </c>
       <c r="G30" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CINDERFORD Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:
-- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H
-- Beige Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H
-- Beige Love Seat Base: dimensions: 61" W x 34"D x 35" H
-- Beige Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H
-Weight: 204.18 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CINDERFORD Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Love Seat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Beige Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 204.18 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CINDERFORD Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room.
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:
-- Dark Gray Sofa Base: dimensions: 85" W x 34"D x 35" H
-- Dark Gray Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H
-- Dark Gray Love Seat Base: dimensions: 61" W x 34"D x 35" H
-- Dark Gray Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H
-Weight: 193.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CINDERFORD Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+- Dark Gray Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Dark Gray Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Dark Gray Love Seat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Dark Gray Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 193.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
@@ -4673,20 +4673,20 @@
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CIVELLUTINO Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Velvet-like, Metal, Engineered Wood, and finished in Light Blue tones for a clean, cohesive look.
-Product Dimensions: SOFA: 79 1/2"L X 36 1/2"W X 33 1/8"H (SEAT HT: 18", SEAT DP: 21 3/4")
-Features
-- Biscuit Tufting &amp; 100% Polyester Fabric
-- Tight Back and Seat
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- Webbing Back and Ring Seat Suspension
-- Chrome X Legs
-- 100% Made in Italy
-Materials: Velvet-like, Metal, Engineered Wood.
-Color: Light Blue
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CIVELLUTINO Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Velvet-like, Metal, Engineered Wood, and finished in Light Blue tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 79 1/2"L X 36 1/2"W X 33 1/8"H (SEAT HT: 18", SEAT DP: 21 3/4")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Biscuit Tufting &amp;amp; 100% Polyester Fabric&lt;br&gt;
+- Tight Back and Seat&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- Webbing Back and Ring Seat Suspension&lt;br&gt;
+- Chrome X Legs&lt;br&gt;
+- 100% Made in Italy&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Metal, Engineered Wood.&lt;br&gt;
+Color: Light Blue&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" s="30" t="inlineStr">
@@ -4808,20 +4808,20 @@
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CIVELLUTINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Velvet-like, Metal, Engineered Wood, then finished in Teal tones to suit a range of interiors.
-Product Dimensions: Sofa: 79 1/2"L X 36 1/2"W X 33 1/8"H (SEAT HT: 18", SEAT DP: 21 3/4")
-Features
-- Biscuit Tufting
-- 100% Polyester Fabric
-- Tight Back and Seat
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- Chrome Legs
-- Made in Italy
-Materials: Velvet-like, Metal, Engineered Wood.
-Color: Teal
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CIVELLUTINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Velvet-like, Metal, Engineered Wood, then finished in Teal tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 79 1/2"L X 36 1/2"W X 33 1/8"H (SEAT HT: 18", SEAT DP: 21 3/4")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Biscuit Tufting&lt;br&gt;
+- 100% Polyester Fabric&lt;br&gt;
+- Tight Back and Seat&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- Chrome Legs&lt;br&gt;
+- Made in Italy&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Metal, Engineered Wood.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" s="30" t="inlineStr">
@@ -4942,21 +4942,21 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COCHRANE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Chenille, Solid Wood construction and Cream or Beige tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 96"L X 37"W X 38"H (SEAT HT: 21", SEAT DP: 23")
-Features
-- Cream or Beige
-- Box Seat Cushion
-- Loose Pillow Back
-- Track Arms
-- Accent Pillows Included
-- Matching Swivel Chair Included items and dimensions:
-- Sofa: color: Cream or Beige; dimensions: 96" L x 37" W x 38" H (SEAT HT: 21", SEAT DP: 23"); feature: Contemporary
-- Loveseat: color: Cream or Beige; dimensions: 70" L x 37" W x 38" H (SEAT HT: 21", SEAT DP: 23"); feature: Contemporary
-Materials: Chenille, Solid Wood.
-Color: Cream or Beige
-Weight: 285 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COCHRANE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Chenille, Solid Wood construction and Cream or Beige tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 96"L X 37"W X 38"H (SEAT HT: 21", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Cream or Beige&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Accent Pillows Included&lt;br&gt;
+- Matching Swivel Chair Included items and dimensions:&lt;br&gt;
+- Sofa: color: Cream or Beige; dimensions: 96" L x 37" W x 38" H (SEAT HT: 21", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Cream or Beige; dimensions: 70" L x 37" W x 38" H (SEAT HT: 21", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Cream or Beige&lt;br&gt;
+Weight: 285 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5074,19 +5074,19 @@
       </c>
       <c r="G35" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRAYFORD Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other and finished in Light Gray tones for a clean, cohesive look.
-Product Dimensions: 83.5"W X 38"D X 34.5"H (SEAT HT: 18.5", SEAT DP: 23")
-Features
-- Feather Blend Pillow Top Cushion and Back Pillow
-- Welt Trim
-- Wooden Legs
-- Narrow Track Arm Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 83.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional
-- Loveseat: color: Light Gray; dimensions: 67.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional
-Materials: Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other.
-Color: Light Gray
-Weight: 268.97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRAYFORD Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 83.5"W X 38"D X 34.5"H (SEAT HT: 18.5", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Feather Blend Pillow Top Cushion and Back Pillow&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- Narrow Track Arm Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 83.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 67.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 268.97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="32" t="inlineStr">
@@ -5208,19 +5208,19 @@
       </c>
       <c r="G36" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRAYFORD Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other, then finished in Taupe tones to suit a range of interiors.
-Product Dimensions: 83.5"W X 38"D X 34.5"H (SEAT HT: 18.5", SEAT DP: 23")
-Features
-- Feather Blend Pillow Top Cushion and Back Pillow
-- Welt Trim
-- Wooden Legs
-- Narrow Track Arm Included items and dimensions:
-- Sofa: color: Taupe; dimensions: 83.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional
-- Loveseat: color: Taupe; dimensions: 67.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional
-Materials: Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other.
-Color: Taupe
-Weight: 268.97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRAYFORD Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 83.5"W X 38"D X 34.5"H (SEAT HT: 18.5", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Feather Blend Pillow Top Cushion and Back Pillow&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- Narrow Track Arm Included items and dimensions:&lt;br&gt;
+- Sofa: color: Taupe; dimensions: 83.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Taupe; dimensions: 67.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 268.97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="32" t="inlineStr">
@@ -5341,20 +5341,20 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CROYDON Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.
-Features
-- Box Seat Cushions
-- Loose Pillow Back
-- Flared Rounded Arms
-- Tapered Block Plastic Leg
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 85" L x 34" W x 38 1 or 2" H; feature: Contemporary
-- Loveseat: color: Light Gray; dimensions: 62" L x 34" W x 38 1 or 2" H; feature: Contemporary
-Materials: Fabric, Solid Wood.
-Color: Light Gray
-Weight: 181 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CROYDON Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Flared Rounded Arms&lt;br&gt;
+- Tapered Block Plastic Leg&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 85" L x 34" W x 38 1 or 2" H; feature: Contemporary&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 62" L x 34" W x 38 1 or 2" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 181 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5467,19 +5467,19 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DELGADA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Chenille, Solid Wood, then finished in Beige tones to suit a range of interiors.
-Product Dimensions: 91"L X 37"W X 39"H (SEAT HT: 21 1/2", SEAT DP: 22")
-Features
-- Rolled Arms
-- Tapered Wood Feet
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige; dimensions: 91" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional
-- Loveseat: color: Beige; dimensions: 72" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Beige
-Weight: 220 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DELGADA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Chenille, Solid Wood, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 91"L X 37"W X 39"H (SEAT HT: 21 1/2", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Tapered Wood Feet&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 91" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 72" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 220 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
@@ -5601,19 +5601,19 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DELGADA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Graphite tones, it blends durability with visual warmth.
-Product Dimensions: 91"L X 37"W X 39"H (SEAT HT: 21 1/2", SEAT DP: 22")
-Features
-- Rolled Arms
-- Tapered Wood Feet
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Graphite; dimensions: 91" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional
-- Loveseat: color: Graphite; dimensions: 72" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Graphite
-Weight: 220 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DELGADA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Graphite tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 91"L X 37"W X 39"H (SEAT HT: 21 1/2", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Tapered Wood Feet&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Graphite; dimensions: 91" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Graphite; dimensions: 72" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Graphite&lt;br&gt;
+Weight: 220 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="G40" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIONYSUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.
-Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22-62") Included items and dimensions:
-- Manual Reclining Sofa w/ USB &amp; LED: color: Brown; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional
-- USB &amp; LED Manual Reclining Loveseat w/ Console: color: Brown; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional
-Weight: 348.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIONYSUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22-62") Included items and dimensions:&lt;br&gt;
+- Manual Reclining Sofa w/ USB &amp;amp; LED: color: Brown; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
+- USB &amp;amp; LED Manual Reclining Loveseat w/ Console: color: Brown; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
+Weight: 348.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" s="35" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="G41" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DIONYSUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.
-Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22"-62) Included items and dimensions:
-- Manual Reclining Sofa w/ USB &amp; LED: color: Gray; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22"-62); feature: Transitional
-- USB &amp; LED Manual Reclining Loveseat w/ Console: color: Gray; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional
-Weight: 350.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DIONYSUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22"-62) Included items and dimensions:&lt;br&gt;
+- Manual Reclining Sofa w/ USB &amp;amp; LED: color: Gray; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22"-62); feature: Transitional&lt;br&gt;
+- USB &amp;amp; LED Manual Reclining Loveseat w/ Console: color: Gray; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
+Weight: 350.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" s="35" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DORIPHEI Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room.
-Product Dimensions: 92"W X 35"D X 30"H (SEAT HT: 18.5", SEAT DP: 26") Included items and dimensions:
-- Sofa: color: Black Velvet or Gold; dimensions: 92" W x 35"D x 30" H (SEAT HT: 18.5", SEAT DP: 26"); feature: Glam
-- Loveseat: color: Black Velvet or Gold; dimensions: 66" W x 35"D x 30" H (SEAT HT: 18.5", SEAT DP: 26"); feature: Glam
-Weight: 380 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DORIPHEI Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 92"W X 35"D X 30"H (SEAT HT: 18.5", SEAT DP: 26") Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black Velvet or Gold; dimensions: 92" W x 35"D x 30" H (SEAT HT: 18.5", SEAT DP: 26"); feature: Glam&lt;br&gt;
+- Loveseat: color: Black Velvet or Gold; dimensions: 66" W x 35"D x 30" H (SEAT HT: 18.5", SEAT DP: 26"); feature: Glam&lt;br&gt;
+Weight: 380 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6058,22 +6058,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EALING Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Solid Wood, and finished in Light Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 98"L X 42"W X 38"H (SEAT HT: 20", SEAT DP: 27")
-Features
-- T Seat Cushion
-- Performance Fabric on Chair and Some Pillows
-- Welt Trim
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln-Dried Wooden Frame
-- Tapered Wooden Legs Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 98" L x 42" W x 38" H (SEAT HT: 20", SEAT DP: 27"); feature: Transitional
-- Loveseat: color: Light Gray; dimensions: 72" L x 42" W x 38" H (SEAT HT: 20", SEAT DP: 27"); feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Light Gray
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EALING Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Solid Wood, and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 98"L X 42"W X 38"H (SEAT HT: 20", SEAT DP: 27")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- Performance Fabric on Chair and Some Pillows&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln-Dried Wooden Frame&lt;br&gt;
+- Tapered Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 98" L x 42" W x 38" H (SEAT HT: 20", SEAT DP: 27"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 72" L x 42" W x 38" H (SEAT HT: 20", SEAT DP: 27"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6191,18 +6191,18 @@
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELICIA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Champagne or Turquoise tones to suit a range of interiors.
-Features
-- Champagne or Turquoise
-- Individual Nailhead Trim
-- Bench Style Cushion
-- Tapered Legs Included items and dimensions:
-- Sofa: color: Champagne or Turquoise; dimensions: 93" L x 39" W x 39" H; feature: Transitional
-- Loveseat: color: Champagne or Turquoise; dimensions: 67" L x 39" W x 39" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Champagne or Turquoise
-Weight: 285 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELICIA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Champagne or Turquoise tones to suit a range of interiors.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Champagne or Turquoise&lt;br&gt;
+- Individual Nailhead Trim&lt;br&gt;
+- Bench Style Cushion&lt;br&gt;
+- Tapered Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Champagne or Turquoise; dimensions: 93" L x 39" W x 39" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Champagne or Turquoise; dimensions: 67" L x 39" W x 39" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Champagne or Turquoise&lt;br&gt;
+Weight: 285 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="16" t="inlineStr">
@@ -6320,18 +6320,18 @@
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELICIA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Chenille, Solid Wood construction and Silver tones, it blends durability with visual warmth.
-Features
-- Individual Nailhead Trim
-- Bench Style Cushion
-- Chrome Legs
-- Tapered Legs Included items and dimensions:
-- Sofa: color: Silver; dimensions: 93" L x 39" W x 39" H; feature: Transitional
-- Loveseat: color: Silver; dimensions: 67" L x 39" W x 39" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Silver
-Weight: 289 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELICIA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Chenille, Solid Wood construction and Silver tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Individual Nailhead Trim&lt;br&gt;
+- Bench Style Cushion&lt;br&gt;
+- Chrome Legs&lt;br&gt;
+- Tapered Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Silver; dimensions: 93" L x 39" W x 39" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Silver; dimensions: 67" L x 39" W x 39" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Silver&lt;br&gt;
+Weight: 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -6448,21 +6448,21 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELLIS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Finished in Brown or Burgundy tones, the Fabric, Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 88"L X 35"W X 37"H
-Features
-- Traditional
-- Brown or Burgundy
-- Intricate Wood Trim
-- Loose Back Pillows
-- High-Density Foam Cushions
-- Pillows Included Included items and dimensions:
-- Sofa: color: Burgundy or Brown or Dark Cherry; dimensions: 88" L x 35" W x 37" H; feature: Traditional
-- Loveseat: color: Burgundy or Brown or Dark Cherry; dimensions: 69" L x 35" W x 37" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Brown or Burgundy
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELLIS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Finished in Brown or Burgundy tones, the Fabric, Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 35"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Brown or Burgundy&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Burgundy or Brown or Dark Cherry; dimensions: 88" L x 35" W x 37" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Burgundy or Brown or Dark Cherry; dimensions: 69" L x 35" W x 37" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown or Burgundy&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6579,22 +6579,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELPIS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Chenille, Leatherette, Solid Wood, and finished in Brown or Espresso tones for a clean, cohesive look.
-Product Dimensions: SOFA: 94"L X 37"W X 44"H
-Features
-- Traditional
-- Brown or Espresso
-- Intricate Wood Trim
-- Rolled Arms
-- High-Density Foam Cushions
-- Pillows Included
-- Victorian Print Included items and dimensions:
-- Sofa: color: Brown or Espresso; dimensions: 95 1 or 2" L x 37" W x 41 1 or 2" H; feature: Traditional
-- Loveseat: color: Brown or Espresso; dimensions: 73 1 or 2" L x 37" W x 41 1 or 2" H; feature: Traditional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Brown or Espresso
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELPIS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Chenille, Leatherette, Solid Wood, and finished in Brown or Espresso tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 44"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Brown or Espresso&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Victorian Print Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Espresso; dimensions: 95 1 or 2" L x 37" W x 41 1 or 2" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Brown or Espresso; dimensions: 73 1 or 2" L x 37" W x 41 1 or 2" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown or Espresso&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6712,22 +6712,22 @@
       </c>
       <c r="G48" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELVERUM Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Boucle, Solid Wood, then finished in Black tones to suit a range of interiors.
-Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")
-Features
-- Bench-style Seating
-- Loose PillowBack
-- Track Arms w/ Welt Trim
-- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)
-- High Density Foam w/ Pocket Coils
-- Kiln-driedHardwood
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Black; dimensions: 82 1 or 2" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary
-- Loveseat: color: Black; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary
-Materials: Boucle, Solid Wood.
-Color: Black
-Weight: 203 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELVERUM Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Boucle, Solid Wood, then finished in Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bench-style Seating&lt;br&gt;
+- Loose PillowBack&lt;br&gt;
+- Track Arms w/ Welt Trim&lt;br&gt;
+- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)&lt;br&gt;
+- High Density Foam w/ Pocket Coils&lt;br&gt;
+- Kiln-driedHardwood&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black; dimensions: 82 1 or 2" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Black; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 203 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" s="18" t="inlineStr">
@@ -6849,22 +6849,22 @@
       </c>
       <c r="G49" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELVERUM Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Boucle, Solid Wood, construction and Charcoal Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")
-Features
-- Bench-style Seating
-- Loose PillowBack
-- Track Arms w/ Welt Trim
-- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)
-- High Density Foam w/ Pocket Coils
-- Kiln-driedHardwood
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Charcoal Gray; dimensions: 82 1 or 2" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary
-- Loveseat: color: Charcoal Gray; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary
-Materials: Boucle, Solid Wood.
-Color: Charcoal Gray
-Weight: 203 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELVERUM Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Boucle, Solid Wood, construction and Charcoal Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bench-style Seating&lt;br&gt;
+- Loose PillowBack&lt;br&gt;
+- Track Arms w/ Welt Trim&lt;br&gt;
+- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)&lt;br&gt;
+- High Density Foam w/ Pocket Coils&lt;br&gt;
+- Kiln-driedHardwood&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Charcoal Gray; dimensions: 82 1 or 2" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Charcoal Gray; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
+Color: Charcoal Gray&lt;br&gt;
+Weight: 203 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" s="18" t="inlineStr">
@@ -6986,22 +6986,22 @@
       </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELVERUM Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Off-White tones, the Boucle, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")
-Features
-- Bench-style Seating
-- Loose PillowBack
-- Track Arms w/ Welt Trim
-- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)
-- High Density Foam w/ Pocket Coils
-- Kiln-driedHardwood
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Off-White; dimensions: 82 1 or 2" L x 34 1 or 2" W x 33" H (SEAT HT: 18 1 or 2", SEAT DP: 23"); feature: Contemporary
-- Loveseat: color: Off-White; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary
-Materials: Boucle, Solid Wood.
-Color: Off-White
-Weight: 203 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELVERUM Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Off-White tones, the Boucle, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bench-style Seating&lt;br&gt;
+- Loose PillowBack&lt;br&gt;
+- Track Arms w/ Welt Trim&lt;br&gt;
+- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)&lt;br&gt;
+- High Density Foam w/ Pocket Coils&lt;br&gt;
+- Kiln-driedHardwood&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White; dimensions: 82 1 or 2" L x 34 1 or 2" W x 33" H (SEAT HT: 18 1 or 2", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Off-White; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
+Color: Off-White&lt;br&gt;
+Weight: 203 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="18" t="inlineStr">
@@ -7122,23 +7122,23 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ENSENADA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Leatherette, Fabric, Solid Wood, construction and Dark Cherry or Brown tones, it blends durability with visual warmth.
-Product Dimensions: Sofa: 90.25"L X 39.5"W X 45.5"H
-Features
-- Traditional
-- Dark Cherry or Brown
-- Button Tufted Back
-- Carved Details
-- Bench Style Seat Cushion w/ Welt
-- Rolled Arms
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Dark Cherry or Brown; dimensions: 90" W x 39.5"D x 45.5" H; feature: Traditional
-- Loveseat: color: Dark Cherry or Brown; dimensions: 73.5" W x 39.5"D x 45.5" H; feature: Traditional
-Materials: Leatherette, Fabric, Solid Wood.
-Color: Dark Cherry or Brown
-Weight: 350.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ENSENADA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Leatherette, Fabric, Solid Wood, construction and Dark Cherry or Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Sofa: 90.25"L X 39.5"W X 45.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Brown&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Bench Style Seat Cushion w/ Welt&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Cherry or Brown; dimensions: 90" W x 39.5"D x 45.5" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Cherry or Brown; dimensions: 73.5" W x 39.5"D x 45.5" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Brown&lt;br&gt;
+Weight: 350.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7255,21 +7255,21 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EZRIN Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Small Weave Chenille, Solid Wood, construction and Light Brown tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 90"W X 39"D X 40"H
-Features
-- Medium Density Foam
-- Sloped Arms
-- Button Tufted Back
-- Single Cushion Seat
-- Nailhead Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Light Brown; dimensions: 90" W x 39"D x 40" H; feature: Transitional
-- Loveseat: color: Light Brown; dimensions: 65" W x 39"D x 40" H; feature: Transitional
-Materials: Small Weave Chenille, Solid Wood.
-Color: Light Brown
-Weight: 251 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EZRIN Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Small Weave Chenille, Solid Wood, construction and Light Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"W X 39"D X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Single Cushion Seat&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Brown; dimensions: 90" W x 39"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Brown; dimensions: 65" W x 39"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Small Weave Chenille, Solid Wood.&lt;br&gt;
+Color: Light Brown&lt;br&gt;
+Weight: 251 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7386,22 +7386,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FLETCHER Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Leatherette, Solid Wood, and finished in Brown or Tan tones for a clean, cohesive look.
-Product Dimensions: SOFA: 98 1/2"L X 40"W X 40"H
-Features
-- Brown or Tan
-- Medium Density Foam
-- Rolled Arms
-- Nailhead Trim
-- Loose Back Pillows
-- Round Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Brown or Tan; dimensions: 98 1 or 2" L x 40" W x 40" H; feature: Transitional
-- Loveseat: color: Brown or Tan; dimensions: 72 1 or 2" L x 40" W x 40" H; feature: Transitional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Brown or Tan
-Weight: 376 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FLETCHER Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Leatherette, Solid Wood, and finished in Brown or Tan tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 98 1/2"L X 40"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Brown or Tan&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Round Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Tan; dimensions: 98 1 or 2" L x 40" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown or Tan; dimensions: 72 1 or 2" L x 40" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown or Tan&lt;br&gt;
+Weight: 376 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7518,20 +7518,20 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FLINTSHIRE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Beige tones to suit a range of interiors.
-Product Dimensions: Sofa: 86"L X 44"W X 37"H
-Features
-- Removable Pillow Back
-- Accent Pillows Included
-- Track Arms
-- T-Seat Cushions
-- Bracket Feet Included items and dimensions:
-- Sofa: color: Beige; dimensions: 86" W x 44"D x 37" H; feature: Transitional
-- Loveseat: color: Beige; dimensions: 70" W x 44"D x 37" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Beige
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FLINTSHIRE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 86"L X 44"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Removable Pillow Back&lt;br&gt;
+- Accent Pillows Included&lt;br&gt;
+- Track Arms&lt;br&gt;
+- T-Seat Cushions&lt;br&gt;
+- Bracket Feet Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 86" W x 44"D x 37" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 70" W x 44"D x 37" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7649,21 +7649,21 @@
       </c>
       <c r="G55" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRANKLIN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Leatherette, Solid Wood, then finished in Dark Brown or Tan tones to suit a range of interiors.
-Product Dimensions: SOFA: 94"L X 37"W X 37.5"H
-Features
-- Traditional
-- Dark Brown or Tan
-- Rolled Arms
-- Pillows Included
-- Intricate Wood Trim
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Dark Brown or Tan; dimensions: 94" L x 37" W x 41" H; feature: Traditional
-- Loveseat: color: Dark Brown or Tan; dimensions: 72" L x 37" W x 41" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Dark Brown or Tan
-Weight: 295 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRANKLIN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Leatherette, Solid Wood, then finished in Dark Brown or Tan tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 37.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Brown or Tan&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Brown or Tan; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Brown or Tan; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Dark Brown or Tan&lt;br&gt;
+Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="37" t="inlineStr">
@@ -7785,21 +7785,21 @@
       </c>
       <c r="G56" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FRANKLIN Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Leatherette, Solid Wood, construction and Burgundy or Espresso tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 94"L X 37"W X 37.5"H
-Features
-- Traditional
-- Burgundy or Espresso
-- Rolled Arms
-- Pillows Included
-- Intricate Wood Trim
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Burgundy or Espresso; dimensions: 94" L x 37" W x 41" H; feature: Traditional
-- Loveseat: color: Burgundy or Espresso; dimensions: 72" L x 37" W x 41" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Burgundy or Espresso
-Weight: 295 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FRANKLIN Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Leatherette, Solid Wood, construction and Burgundy or Espresso tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 37.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Burgundy or Espresso&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Burgundy or Espresso; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Burgundy or Espresso; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Burgundy or Espresso&lt;br&gt;
+Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="37" t="inlineStr">
@@ -7920,22 +7920,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GERMAINE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood, construction and Ivory tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 101"L X 44"W X 40"H
-Features
-- Medium Density Foam
-- Sheltered Arms
-- T-Cushion Seats
-- Track Arms
-- Loose Back Pillows
-- Nailhead Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 101" L x 44" W x 40" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 75" L x 44" W x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Ivory
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GERMAINE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood, construction and Ivory tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 44"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sheltered Arms&lt;br&gt;
+- T-Cushion Seats&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 101" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 75" L x 44" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8052,22 +8052,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GILDA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Beige or Black tones to suit a range of interiors.
-Product Dimensions: SOFA: 100"L X 39"W X 37"H
-Features
-- Beige or Black
-- Chesterfield Design
-- Oversized Rolled Arms
-- High-Density Foam Cushion
-- Button Tufted Padding
-- Nailhead Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige or Black; dimensions: 100" L x 39" W x 37" H; feature: Glam
-- Loveseat: color: Beige or Black; dimensions: 76" L x 39" W x 37" H; feature: Glam
-Materials: Linen-like Fabric, Solid Wood.
-Color: Beige or Black
-Weight: 290 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GILDA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. Crafted with Linen-like Fabric, Solid Wood, then finished in Beige or Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 100"L X 39"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Black&lt;br&gt;
+- Chesterfield Design&lt;br&gt;
+- Oversized Rolled Arms&lt;br&gt;
+- High-Density Foam Cushion&lt;br&gt;
+- Button Tufted Padding&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Black; dimensions: 100" L x 39" W x 37" H; feature: Glam&lt;br&gt;
+- Loveseat: color: Beige or Black; dimensions: 76" L x 39" W x 37" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Beige or Black&lt;br&gt;
+Weight: 290 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8185,21 +8185,21 @@
       </c>
       <c r="G59" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GIOVANNI Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Linen-like Fabric construction and Beige or Blue tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 92 1/2"W X 40 1/2"D X 40 1/2"H
-Features
-- Beige or Blue
-- Nailhead Trim
-- Rolled Arms
-- Wooden Legs
-- High-Density Foam Cushions
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige or Blue; dimensions: 92 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional
-- Loveseat: color: Beige or Blue; dimensions: 66 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional
-Materials: Linen-like Fabric.
-Color: Beige or Blue
-Weight: 297 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GIOVANNI Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Linen-like Fabric construction and Beige or Blue tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 92 1/2"W X 40 1/2"D X 40 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Blue&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Blue; dimensions: 92 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige or Blue; dimensions: 66 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric.&lt;br&gt;
+Color: Beige or Blue&lt;br&gt;
+Weight: 297 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="20" t="inlineStr">
@@ -8321,20 +8321,20 @@
       </c>
       <c r="G60" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GIOVANNI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Gray tones, the Linen-like Fabric build keeps the look polished and practical.
-Product Dimensions: SOFA: 92 1/2"W X 40 1/2"D X 40 1/2"H
-Features
-- Nailhead Trim
-- Rolled Arms
-- Wooden Legs
-- High-Density Foam Cushions
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 92 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 66 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional
-Materials: Linen-like Fabric.
-Color: Gray
-Weight: 297 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GIOVANNI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Gray tones, the Linen-like Fabric build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 92 1/2"W X 40 1/2"D X 40 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 92 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 66 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 297 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="20" t="inlineStr">
@@ -8456,18 +8456,18 @@
       </c>
       <c r="G61" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GLARUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Powder Blue tones for a clean, cohesive look.
-Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H
-Features
-- Pillow Top Arms
-- Welt Trim
-- FSC Certified Included items and dimensions:
-- Sofa: color: Powder Blue; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional
-- Loveseat: color: Powder Blue; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional
-Materials: Leather Match, Metal.
-Color: Powder Blue
-Weight: 365.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GLARUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Powder Blue tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Sofa: color: Powder Blue; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Powder Blue; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
+Color: Powder Blue&lt;br&gt;
+Weight: 365.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="39" t="inlineStr">
@@ -8589,18 +8589,18 @@
       </c>
       <c r="G62" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GLARUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Metal, then finished in Dark Gray tones to suit a range of interiors.
-Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H
-Features
-- Pillow Top Arms
-- Welt Trim
-- FSC Certified Included items and dimensions:
-- Sofa: color: Dark Gray; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional
-- Loveseat: color: Dark Gray; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional
-Materials: Leather Match, Metal.
-Color: Dark Gray
-Weight: 378.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GLARUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Metal, then finished in Dark Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Gray; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Dark Gray; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 378.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="39" t="inlineStr">
@@ -8722,18 +8722,18 @@
       </c>
       <c r="G63" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GLARUS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leather Match, Metal, construction and White tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H
-Features
-- Pillow Top Arms
-- Welt Trim
-- FSC Certified Included items and dimensions:
-- Sofa: color: Off-White; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional
-- Loveseat: color: Off-White; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional
-Materials: Leather Match, Metal.
-Color: White
-Weight: 365.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GLARUS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leather Match, Metal, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Off-White; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 365.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="39" t="inlineStr">
@@ -8854,24 +8854,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GUSTAVO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Gray or Walnut tones, it blends durability with visual warmth.
-Product Dimensions: 90"L X 35"W X 31"H (SEAT HT: 22", SEAT DP: 22")
-Features
-- Traditional
-- Gray or Walnut
-- Faux Wood Carved Details
-- Box Seat Cushions
-- Loose Pillow Backs
-- Rolled Arms
-- Wooden Cabriole Legs
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Gray or Walnut; dimensions: 90" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional
-- Loveseat: color: Gray or Walnut; dimensions: 68" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Gray or Walnut
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GUSTAVO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Gray or Walnut tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 90"L X 35"W X 31"H (SEAT HT: 22", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Gray or Walnut&lt;br&gt;
+- Faux Wood Carved Details&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wooden Cabriole Legs&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray or Walnut; dimensions: 90" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Gray or Walnut; dimensions: 68" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray or Walnut&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8988,23 +8988,23 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HARSTAD Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Foam, Solid Wood, construction and Light Brown or Natural tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 93"W X 40"D X 35"H (SEAT HT: 26", SEAT DP: 16")
-Features
-- Light Brown or Natural
-- Ash Wood Trim
-- Reversible Loose Pillow Back
-- Spring Seat Suspension
-- Block Wooden Legs
-- Track Arms
-- Welt Trim
-- Feather Fiber Pillow Construction Included items and dimensions:
-- Sofa: color: Light Brown or Natural; dimensions: 93" W x 40"D x 35" H (SEAT HT: 26", SEAT DP: 16"); feature: Contemporary
-- Loveseat: color: Light Brown or Natural; dimensions: 70" W x 40"D x 35" H (SEAT HT: 26", SEAT DP: 16"); feature: Contemporary
-Materials: Fabric, Foam, Solid Wood.
-Color: Light Brown or Natural
-Weight: 318 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HARSTAD Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Foam, Solid Wood, construction and Light Brown or Natural tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 93"W X 40"D X 35"H (SEAT HT: 26", SEAT DP: 16")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Brown or Natural&lt;br&gt;
+- Ash Wood Trim&lt;br&gt;
+- Reversible Loose Pillow Back&lt;br&gt;
+- Spring Seat Suspension&lt;br&gt;
+- Block Wooden Legs&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Feather Fiber Pillow Construction Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Brown or Natural; dimensions: 93" W x 40"D x 35" H (SEAT HT: 26", SEAT DP: 16"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Light Brown or Natural; dimensions: 70" W x 40"D x 35" H (SEAT HT: 26", SEAT DP: 16"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
+Color: Light Brown or Natural&lt;br&gt;
+Weight: 318 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9121,20 +9121,20 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HERMILLY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25")
-Features
-- T-Seat Cushion
-- Channeled Fur Back and Pillows
-- Reversible Seat Cushions
-- Padded Arms
-- Wood Legs Included items and dimensions:
-- Sofa: color: Gray; dimensions: 98" L x 39" W x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Gray; dimensions: 72" L x 39" W x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Gray
-Weight: 292 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HERMILLY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Seat Cushion&lt;br&gt;
+- Channeled Fur Back and Pillows&lt;br&gt;
+- Reversible Seat Cushions&lt;br&gt;
+- Padded Arms&lt;br&gt;
+- Wood Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 98" L x 39" W x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 72" L x 39" W x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 292 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HIERONYMUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.
-Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46") Included items and dimensions:
-- Manual Sofa: color: Dark Brown; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional
-- Manual Loveseat w/ Console: color: Dark Brown; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional
-Weight: 444 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HIERONYMUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46") Included items and dimensions:&lt;br&gt;
+- Manual Sofa: color: Dark Brown; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
+- Manual Loveseat w/ Console: color: Dark Brown; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
+Weight: 444 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HIERONYMUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room.
-Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46") Included items and dimensions:
-- Manual Sofa: color: Dark Gray; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional
-- Manual Loveseat w/ Console: color: Dark Gray; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional
-Weight: 444 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HIERONYMUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46") Included items and dimensions:&lt;br&gt;
+- Manual Sofa: color: Dark Gray; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
+- Manual Loveseat w/ Console: color: Dark Gray; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
+Weight: 444 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -9474,21 +9474,21 @@
       </c>
       <c r="G69" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLBORN Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Beige tones, the Chenille, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 101"L X 44"W X 40"H
-Features
-- T-Seat Cushion
-- Loose Pillow Back
-- Wide Track Armrest
-- Low Flared Arms
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige; dimensions: 101" L x 44" W x 40" H; feature: Transitional
-- Loveseat: color: Beige; dimensions: 75" L x 44" W x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Beige
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLBORN Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Beige tones, the Chenille, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 44"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Wide Track Armrest&lt;br&gt;
+- Low Flared Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 101" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 75" L x 44" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" s="26" t="inlineStr">
@@ -9610,21 +9610,21 @@
       </c>
       <c r="G70" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HOLBORN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 101"L X 44"W X 40"H
-Features
-- T-Seat Cushion
-- Loose Pillow Back
-- Wide Track Armrest
-- Low Flared Arms
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 101" L x 44" W x 40" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 75" L x 44" W x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Gray
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HOLBORN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 44"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Wide Track Armrest&lt;br&gt;
+- Low Flared Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 101" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 75" L x 44" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" s="26" t="inlineStr">
@@ -9745,18 +9745,18 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HORGEN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, and finished in Off-White tones for a clean, cohesive look.
-Features
-- Bench-style Seating
-- Round Tapered Legs
-- USB Outlet
-- Bolster Pillows Included Included items and dimensions:
-- Sofa: color: Off-White; dimensions: 75 5 or 8" L x 31 1 or 8" W x 33 1 or 2" H (SEAT HT: 18 7 or 8", SEAT DP: 2 1 or 2"); feature: Mid-century Modern
-- Loveseat: color: Off-White; dimensions: 52 3 or 8" L x 31 3 or 8" W x 33 1 or 2" H (SEAT HT: 18 7 or 8", SEAT DP: 2 1 or 2"); feature: Mid-century Modern
-Materials: Leatherette, Solid Wood.
-Color: Off-White
-Weight: 185.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HORGEN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Mid-Century Modern styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, and finished in Off-White tones for a clean, cohesive look.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bench-style Seating&lt;br&gt;
+- Round Tapered Legs&lt;br&gt;
+- USB Outlet&lt;br&gt;
+- Bolster Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White; dimensions: 75 5 or 8" L x 31 1 or 8" W x 33 1 or 2" H (SEAT HT: 18 7 or 8", SEAT DP: 2 1 or 2"); feature: Mid-century Modern&lt;br&gt;
+- Loveseat: color: Off-White; dimensions: 52 3 or 8" L x 31 3 or 8" W x 33 1 or 2" H (SEAT HT: 18 7 or 8", SEAT DP: 2 1 or 2"); feature: Mid-century Modern&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Off-White&lt;br&gt;
+Weight: 185.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9868,21 +9868,21 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HUELVA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, Pine, Foam, Other construction and Beige or Dark Cherry tones, it blends durability with visual warmth.
-Product Dimensions: SF: 95"W X 36"D X 44"H, LV:73"W X 36"D X 44"H
-Features
-- Traditional
-- Beige or Dark Cherry
-- 100% Polyester Fabric
-- Ornate Carved Details
-- Rolled Arms
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige or Dark Cherry; dimensions: 95" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional
-- Loveseat: color: Beige or Dark Cherry; dimensions: 73" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional
-Materials: Fabric, Solid Wood, Pine, Foam, Other.
-Color: Beige or Dark Cherry
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HUELVA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, Pine, Foam, Other construction and Beige or Dark Cherry tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SF: 95"W X 36"D X 44"H, LV:73"W X 36"D X 44"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Beige or Dark Cherry&lt;br&gt;
+- 100% Polyester Fabric&lt;br&gt;
+- Ornate Carved Details&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Dark Cherry; dimensions: 95" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Beige or Dark Cherry; dimensions: 73" W x 36"D x 44" H (SEAT HT: 22", SEAT DP: 23"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Pine, Foam, Other.&lt;br&gt;
+Color: Beige or Dark Cherry&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9999,21 +9999,21 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ILSE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood construction and Off-White or Blue tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 90"L X 40"W X 38"H
-Features
-- Off-White or Blue
-- Track Arms
-- Fitted Back Pillows
-- Nailhead Trim
-- Wooden Block Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Off-White or Blue; dimensions: 90" L x 40" W x 38" H; feature: Contemporary
-- Loveseat: color: Off-White or Blue; dimensions: 66" L x 40" W x 38" H; feature: Contemporary
-Materials: Chenille, Solid Wood.
-Color: Off-White or Blue
-Weight: 291 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ILSE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood construction and Off-White or Blue tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 40"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Off-White or Blue&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Fitted Back Pillows&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Wooden Block Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White or Blue; dimensions: 90" L x 40" W x 38" H; feature: Contemporary&lt;br&gt;
+- Loveseat: color: Off-White or Blue; dimensions: 66" L x 40" W x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Off-White or Blue&lt;br&gt;
+Weight: 291 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10130,23 +10130,23 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JAMAEL Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Fabric, Leatherette, Solid Wood, construction and Brown or Espresso tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 94"L X 37"W X 44"H
-Features
-- Traditional
-- Brown or Espresso
-- Button Tufting
-- Intricate Wood Trim
-- Rolled Arms
-- High-Density Foam Cushions
-- Pillows Included
-- Victorian Print Included items and dimensions:
-- Sofa: color: Brown or Espresso; dimensions: 94" L x 37" W x 44" H; feature: Traditional
-- Loveseat: color: Brown or Espresso; dimensions: 72" L x 37" W x 44" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Brown or Espresso
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JAMAEL Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Fabric, Leatherette, Solid Wood, construction and Brown or Espresso tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 44"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Brown or Espresso&lt;br&gt;
+- Button Tufting&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Victorian Print Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Espresso; dimensions: 94" L x 37" W x 44" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Brown or Espresso; dimensions: 72" L x 37" W x 44" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown or Espresso&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10264,21 +10264,21 @@
       </c>
       <c r="G75" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JARROW Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Linen-like Fabric, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 98"L X 40"W X 38"H
-Features
-- Plush Back Cushions
-- Round-Flared Arms
-- Welted Cord Trim
-- Curved Shelter Arms
-- Accent Pillows
-- High Density Foam Cushions Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 98" L x 40" W x 38" H; feature: Transitional
-- Loveseat: color: Light Gray; dimensions: 74" L x 40" W x 38" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Light Gray
-Weight: 350 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JARROW Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Linen-like Fabric, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 98"L X 40"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plush Back Cushions&lt;br&gt;
+- Round-Flared Arms&lt;br&gt;
+- Welted Cord Trim&lt;br&gt;
+- Curved Shelter Arms&lt;br&gt;
+- Accent Pillows&lt;br&gt;
+- High Density Foam Cushions Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 98" L x 40" W x 38" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 74" L x 40" W x 38" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 350 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" s="30" t="inlineStr">
@@ -10400,21 +10400,21 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JARROW Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Linen-like Fabric, Solid Wood and finished in Ivory tones for a clean, cohesive look.
-Product Dimensions: SOFA: 98"L X 40"W X 38"H
-Features
-- Plush Back Cushions
-- Round-Flared Arms
-- Welted Cord Trim
-- Curved Shelter Arms
-- Accent Pillows
-- High Density Foam Cushions Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 98" L x 40" W x 38" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 74" L x 40" W x 38" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Ivory
-Weight: 350 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JARROW Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Linen-like Fabric, Solid Wood and finished in Ivory tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 98"L X 40"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plush Back Cushions&lt;br&gt;
+- Round-Flared Arms&lt;br&gt;
+- Welted Cord Trim&lt;br&gt;
+- Curved Shelter Arms&lt;br&gt;
+- Accent Pillows&lt;br&gt;
+- High Density Foam Cushions Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 98" L x 40" W x 38" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 74" L x 40" W x 38" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 350 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" s="30" t="inlineStr">
@@ -10535,18 +10535,18 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JODIE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Microfiber, Solid Wood, construction and Satin Blue or Silver tones, it blends durability with visual warmth.
-Features
-- Satin Blue or Silver
-- Chrome Legs
-- Track Arms
-- Bench Style Cushion Included items and dimensions:
-- Sofa: color: Satin Blue or Silver; dimensions: 96" L x 39" W x 39" H; feature: Contemporary
-- Loveseat: color: Satin Blue or Silver; dimensions: 67" L x 39" W x 39" H; feature: Contemporary
-Materials: Microfiber, Solid Wood.
-Color: Satin Blue or Silver
-Weight: 297 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JODIE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Microfiber, Solid Wood, construction and Satin Blue or Silver tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Satin Blue or Silver&lt;br&gt;
+- Chrome Legs&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Bench Style Cushion Included items and dimensions:&lt;br&gt;
+- Sofa: color: Satin Blue or Silver; dimensions: 96" L x 39" W x 39" H; feature: Contemporary&lt;br&gt;
+- Loveseat: color: Satin Blue or Silver; dimensions: 67" L x 39" W x 39" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Microfiber, Solid Wood.&lt;br&gt;
+Color: Satin Blue or Silver&lt;br&gt;
+Weight: 297 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10658,19 +10658,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KAYE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Green tones, the Microfiber, Solid Wood build keeps the look polished and practical.
-Features
-- Lined-texture Fabric
-- Button Tufted
-- Tapered Legs
-- Individual Nailhead Trim
-- Bench Cushion Included items and dimensions:
-- Sofa: color: Green; dimensions: 93" L x 39" W x 39" H; feature: Transitional
-- Loveseat: color: Green; dimensions: 67" L x 39" W x 39" H; feature: Transitional
-Materials: Microfiber, Solid Wood.
-Color: Green
-Weight: 280 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KAYE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Green tones, the Microfiber, Solid Wood build keeps the look polished and practical.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Lined-texture Fabric&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Tapered Legs&lt;br&gt;
+- Individual Nailhead Trim&lt;br&gt;
+- Bench Cushion Included items and dimensions:&lt;br&gt;
+- Sofa: color: Green; dimensions: 93" L x 39" W x 39" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Green; dimensions: 67" L x 39" W x 39" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Microfiber, Solid Wood.&lt;br&gt;
+Color: Green&lt;br&gt;
+Weight: 280 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10782,18 +10782,18 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KESWICK Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Charcoal tones, it blends durability with visual warmth.
-Features
-- Plush Pleated Arms
-- Tight Pillow Back
-- Tapered Block Plastic Leg
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Charcoal; dimensions: 86" L x 34" W x 35" H (SEAT HT: 19 1 or 2", SEAT DP: 19"); feature: Contemporary
-- Loveseat: color: Charcoal; dimensions: 63" L x 34" W x 35" H (SEAT HT: 19 1 or 2", SEAT DP: 19"); feature: Contemporary
-Materials: Fabric, Solid Wood.
-Color: Charcoal
-Weight: 190 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KESWICK Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Charcoal tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Plush Pleated Arms&lt;br&gt;
+- Tight Pillow Back&lt;br&gt;
+- Tapered Block Plastic Leg&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Charcoal; dimensions: 86" L x 34" W x 35" H (SEAT HT: 19 1 or 2", SEAT DP: 19"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Charcoal; dimensions: 63" L x 34" W x 35" H (SEAT HT: 19 1 or 2", SEAT DP: 19"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Charcoal&lt;br&gt;
+Weight: 190 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10905,18 +10905,18 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LANDOVERY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in White or Gold tones, the Boucle Fabric, Metal, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 91"L X 33 1/2"W X 29"H (SEAT HT: 19", SEAT DP: 25")
-Features
-- White or Gold
-- Horizontal Tufting
-- Bench-style Seating
-- Gold-plated Steel Legs
-- Pillows Included
-Materials: Boucle Fabric, Metal, Solid Wood.
-Color: White or Gold
-Weight: 247.28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LANDOVERY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in White or Gold tones, the Boucle Fabric, Metal, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 33 1/2"W X 29"H (SEAT HT: 19", SEAT DP: 25")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- White or Gold&lt;br&gt;
+- Horizontal Tufting&lt;br&gt;
+- Bench-style Seating&lt;br&gt;
+- Gold-plated Steel Legs&lt;br&gt;
+- Pillows Included&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Metal, Solid Wood.&lt;br&gt;
+Color: White or Gold&lt;br&gt;
+Weight: 247.28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11033,21 +11033,21 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LAREDO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Linen-like, Solid Wood construction and Beige tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 100"L X 44"W X 40"H
-Features
-- Box Seat Cushion
-- Loose Back Pillow
-- Nailhead Trim
-- Rolled Armrest
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Beige; dimensions: 100" L x 44" W x 40" H; feature: Transitional
-- Loveseat: color: Beige; dimensions: 75" L x 44"D x 40" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Beige
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LAREDO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Linen-like, Solid Wood construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 100"L X 44"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Loose Back Pillow&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Rolled Armrest&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 100" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 75" L x 44"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11165,22 +11165,22 @@
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LEYTONSTONE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Foam, Solid Wood, construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 92"L X 40"W X 37"H (SEAT HT: 20", SEAT DP: 25")
-Features
-- T Seat Cushion
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln-Dried Wooden Frame
-- 100% Polyster Body Fabric
-- Flared Arms
-- Gray Oak Bracket Fee Included items and dimensions:
-- Sofa: color: Gray; dimensions: 92" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Gray; dimensions: 67" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional
-Materials: Fabric, Foam, Solid Wood.
-Color: Gray
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LEYTONSTONE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Foam, Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 92"L X 40"W X 37"H (SEAT HT: 20", SEAT DP: 25")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln-Dried Wooden Frame&lt;br&gt;
+- 100% Polyster Body Fabric&lt;br&gt;
+- Flared Arms&lt;br&gt;
+- Gray Oak Bracket Fee Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 92" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 67" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" s="14" t="inlineStr">
@@ -11302,22 +11302,22 @@
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LEYTONSTONE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Cream tones, the Fabric, Foam, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 92"L X 40"W X 37"H (SEAT HT: 20", SEAT DP: 25")
-Features
-- T Seat Cushion
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln-Dried Wooden Frame
-- 100% Polyster Body Fabric
-- Flared Arms
-- Gray Oak Bracket Fee Included items and dimensions:
-- Sofa: color: Cream; dimensions: 92" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Cream; dimensions: 67" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional
-Materials: Fabric, Foam, Solid Wood.
-Color: Cream
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LEYTONSTONE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Cream tones, the Fabric, Foam, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 92"L X 40"W X 37"H (SEAT HT: 20", SEAT DP: 25")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln-Dried Wooden Frame&lt;br&gt;
+- 100% Polyster Body Fabric&lt;br&gt;
+- Flared Arms&lt;br&gt;
+- Gray Oak Bracket Fee Included items and dimensions:&lt;br&gt;
+- Sofa: color: Cream; dimensions: 92" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Cream; dimensions: 67" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
+Color: Cream&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H83" s="14" t="inlineStr">
@@ -11438,20 +11438,20 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LISTOWEL Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Bonded Leather Match, Solid Wood, then finished in Brown tones to suit a range of interiors.
-Product Dimensions: SOFA: 79"L X 36"W X 40 1/2"H
-Features
-- Stitched Detail
-- Recliners
-- Plush Cushions
-- Drop Down Table W
-- USB Outlet Included items and dimensions:
-- Sofa: color: Brown; dimensions: 79" L x 36" W x 40 1 or 2" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 59" L x 36" W x 40 1 or 2" H; feature: Transitional
-Materials: Bonded Leather Match, Solid Wood.
-Color: Brown
-Weight: 357.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LISTOWEL Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Bonded Leather Match, Solid Wood, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 79"L X 36"W X 40 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Stitched Detail&lt;br&gt;
+- Recliners&lt;br&gt;
+- Plush Cushions&lt;br&gt;
+- Drop Down Table W&lt;br&gt;
+- USB Outlet Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 79" L x 36" W x 40 1 or 2" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 59" L x 36" W x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Bonded Leather Match, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 357.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -11568,21 +11568,21 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LISTOWEL Sofa and Loveseat and Chair creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Bonded Leather Match, Solid Wood, construction and Brown tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 79"L X 36"W X 40 1/2"H
-Features
-- Stitched Detail
-- Recliners
-- Plush Cushions
-- Drop Down Table W
-- USB Outlet Included items and dimensions:
-- Sofa: color: Brown; dimensions: 79" L x 36" W x 40 1 or 2" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 59" L x 36" W x 40 1 or 2" H; feature: Transitional
-- Recliner: color: Brown; dimensions: 39" L x 36" W x 40 1 or 2" H; feature: Transitional
-Materials: Bonded Leather Match, Solid Wood.
-Color: Brown
-Weight: 452.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LISTOWEL Sofa and Loveseat and Chair creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Bonded Leather Match, Solid Wood, construction and Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 79"L X 36"W X 40 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Stitched Detail&lt;br&gt;
+- Recliners&lt;br&gt;
+- Plush Cushions&lt;br&gt;
+- Drop Down Table W&lt;br&gt;
+- USB Outlet Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 79" L x 36" W x 40 1 or 2" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 59" L x 36" W x 40 1 or 2" H; feature: Transitional&lt;br&gt;
+- Recliner: color: Brown; dimensions: 39" L x 36" W x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Bonded Leather Match, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 452.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11700,21 +11700,21 @@
       </c>
       <c r="G86" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOUGHLIN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Solid Wood and finished in Light Brown tones for a clean, cohesive look.
-Product Dimensions: Sofa: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25")
-Features
-- Ultra Soft Back Cushions and Accent Pillows w/ Channel Tufting
-- Bolt-on Removable Arms for Easy Door Access
-- Reversible Zippered Cushions
-- Padded Arms
-- T-Seat Cushions
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Light Brown; dimensions: 98" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Light Brown; dimensions: 72" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Light Brown
-Weight: 292 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOUGHLIN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Solid Wood and finished in Light Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Ultra Soft Back Cushions and Accent Pillows w/ Channel Tufting&lt;br&gt;
+- Bolt-on Removable Arms for Easy Door Access&lt;br&gt;
+- Reversible Zippered Cushions&lt;br&gt;
+- Padded Arms&lt;br&gt;
+- T-Seat Cushions&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Brown; dimensions: 98" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Brown; dimensions: 72" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Light Brown&lt;br&gt;
+Weight: 292 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H86" s="41" t="inlineStr">
@@ -11836,21 +11836,21 @@
       </c>
       <c r="G87" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOUGHLIN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Gun Metal tones to suit a range of interiors.
-Product Dimensions: Sofa: 98"L X 39"W X 38"H
-Features
-- Ultra Soft Back Cushions and Accent Pillows w/ Channel Tufting
-- Bolt-on Removable Arms for Easy Door Access
-- Reversible Zippered Cushions
-- Padded Arms
-- T-Seat Cushions
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Gun Metal; dimensions: 98" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Gun Metal; dimensions: 72" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Gun Metal
-Weight: 292 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOUGHLIN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Gun Metal tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 98"L X 39"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Ultra Soft Back Cushions and Accent Pillows w/ Channel Tufting&lt;br&gt;
+- Bolt-on Removable Arms for Easy Door Access&lt;br&gt;
+- Reversible Zippered Cushions&lt;br&gt;
+- Padded Arms&lt;br&gt;
+- T-Seat Cushions&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gun Metal; dimensions: 98" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gun Metal; dimensions: 72" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gun Metal&lt;br&gt;
+Weight: 292 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H87" s="41" t="inlineStr">
@@ -11972,19 +11972,19 @@
       </c>
       <c r="G88" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYNDA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Dark Gray tones to suit a range of interiors.
-Product Dimensions: SOFA: 75 5/8"L X 32 5/8"W X 34 5/8"H (SEAT HT: 17 3/4", SEAT DP: 20 1/2")
-Features
-- Biscuit Tufting
-- Loose Pillow Backs
-- Wooden Legs
-- Pillows Included Included items and dimensions:
-- Sofa w/ Pillows: color: Dark Gray; dimensions: 73 1 or 4" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary
-- Loveseat w/ Pillows: color: Dark Gray; dimensions: 51 1 or 2" L x 32 5 or 8" WX 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary
-Materials: Chenille, Solid Wood.
-Color: Dark Gray
-Weight: 206.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYNDA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Dark Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 75 5/8"L X 32 5/8"W X 34 5/8"H (SEAT HT: 17 3/4", SEAT DP: 20 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Biscuit Tufting&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa w/ Pillows: color: Dark Gray; dimensions: 73 1 or 4" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;br&gt;
+- Loveseat w/ Pillows: color: Dark Gray; dimensions: 51 1 or 2" L x 32 5 or 8" WX 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 206.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H88" s="35" t="inlineStr">
@@ -12106,19 +12106,19 @@
       </c>
       <c r="G89" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LYNDA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 75 5/8"L X 32 5/8"W X 34 5/8"H (SEAT HT: 17 3/4", SEAT DP: 20 1/2")
-Features
-- Biscuit Tufting
-- Loose Pillow Backs
-- Wooden Legs
-- Pillows Included Included items and dimensions:
-- Sofa w/ Pillows: color: Light Gray; dimensions: 73 1 or 4" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary
-- Loveseat w/ Pillows: color: Light Gray; dimensions: 51 1 or 2" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary
-Materials: Chenille, Solid Wood.
-Color: Light Gray
-Weight: 206.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LYNDA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 75 5/8"L X 32 5/8"W X 34 5/8"H (SEAT HT: 17 3/4", SEAT DP: 20 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Biscuit Tufting&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa w/ Pillows: color: Light Gray; dimensions: 73 1 or 4" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;br&gt;
+- Loveseat w/ Pillows: color: Light Gray; dimensions: 51 1 or 2" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 206.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H89" s="35" t="inlineStr">
@@ -12239,21 +12239,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARIELLA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Microfiber, Solid Wood, then finished in Gray or Beige or Teal or Olive tones to suit a range of interiors.
-Features
-- Gray or Beige or Teal or Olive
-- Microfiber Upholstering
-- Button Tufted
-- Individual Nailhead Trim
-- Turned Legs
-- Pillows Included
-- Bench Style Cushion Included items and dimensions:
-- Sofa: color: Gray or Beige or Teal or Olive; dimensions: 93" L x 42" W x 38" H; feature: Transitional
-- Loveseat: color: Gray or Beige or Teal or Olive; dimensions: 70" L x 42" W x 38" H; feature: Transitional
-Materials: Microfiber, Solid Wood.
-Color: Gray or Beige or Teal or Olive
-Weight: 313 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARIELLA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Microfiber, Solid Wood, then finished in Gray or Beige or Teal or Olive tones to suit a range of interiors.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gray or Beige or Teal or Olive&lt;br&gt;
+- Microfiber Upholstering&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Individual Nailhead Trim&lt;br&gt;
+- Turned Legs&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Bench Style Cushion Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray or Beige or Teal or Olive; dimensions: 93" L x 42" W x 38" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray or Beige or Teal or Olive; dimensions: 70" L x 42" W x 38" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Microfiber, Solid Wood.&lt;br&gt;
+Color: Gray or Beige or Teal or Olive&lt;br&gt;
+Weight: 313 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12365,20 +12365,20 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARINELLA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Royal Blue tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 88"W X 35"D X 37"H
-Features
-- Traditional
-- Loose Back Pillows
-- Intricately Wood-carved Trim
-- Classic Rolled Arms
-- High Density Foam Cushions Included items and dimensions:
-- Sofa: color: Royal Blue; dimensions: 88" W x 35"D x 37" H; feature: Traditional
-- Loveseat: color: Royal Blue; dimensions: 69" W x 35"D x 37" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Royal Blue
-Weight: 250 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARINELLA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Royal Blue tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 88"W X 35"D X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Intricately Wood-carved Trim&lt;br&gt;
+- Classic Rolled Arms&lt;br&gt;
+- High Density Foam Cushions Included items and dimensions:&lt;br&gt;
+- Sofa: color: Royal Blue; dimensions: 88" W x 35"D x 37" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Royal Blue; dimensions: 69" W x 35"D x 37" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Royal Blue&lt;br&gt;
+Weight: 250 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -12495,22 +12495,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARSICANO Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Real Italian Leather, Engineered Wood, then finished in Taupe tones to suit a range of interiors.
-Product Dimensions: Sofa: 85 3/4"L X 37"W X 39"H, LV: 70 1/8"L X 37"W X 39"H
-Features
-- Wide Seating &amp; Accent Stitching
-- Wide Track Arms w/ Welt
-- Tight Back Cushion
-- High Density Foam Seat and Back
-- Wood Bracket Feet
-- Fully Upholstered in Leather on all Sides
-- Made in Italy Included items and dimensions:
-- Sofa: color: Taupe; dimensions: 85.5" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional
-- Loveseat: color: Taupe; dimensions: 70" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional
-Materials: Real Italian Leather, Engineered Wood.
-Color: Taupe
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARSICANO Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Real Italian Leather, Engineered Wood, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 85 3/4"L X 37"W X 39"H, LV: 70 1/8"L X 37"W X 39"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Wide Seating &amp;amp; Accent Stitching&lt;br&gt;
+- Wide Track Arms w/ Welt&lt;br&gt;
+- Tight Back Cushion&lt;br&gt;
+- High Density Foam Seat and Back&lt;br&gt;
+- Wood Bracket Feet&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;br&gt;
+- Made in Italy Included items and dimensions:&lt;br&gt;
+- Sofa: color: Taupe; dimensions: 85.5" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Taupe; dimensions: 70" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -12627,22 +12627,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARSICANO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Real Italian Leather, Engineered Wood, construction and Cognac tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 85 3/4"L X 37"W X 39"H (SEAT HT: 19", SEAT DP: 22 1/2")
-Features
-- Wide Seating &amp; Accent Stitching
-- High Density Foam Seat
-- Tight Back Cushion
-- Wide Track Arms w/ Welt
-- Wood Bracket Feet
-- 100% Made In Italy
-- Fully Upholstered in Leather on all Sides Included items and dimensions:
-- Sofa: color: Cognac; dimensions: 85.5" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional
-- Loveseat: color: Cognac; dimensions: 70" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional
-Materials: Real Italian Leather, Engineered Wood.
-Color: Cognac
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARSICANO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Real Italian Leather, Engineered Wood, construction and Cognac tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 85 3/4"L X 37"W X 39"H (SEAT HT: 19", SEAT DP: 22 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Wide Seating &amp;amp; Accent Stitching&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Tight Back Cushion&lt;br&gt;
+- Wide Track Arms w/ Welt&lt;br&gt;
+- Wood Bracket Feet&lt;br&gt;
+- 100% Made In Italy&lt;br&gt;
+- Fully Upholstered in Leather on all Sides Included items and dimensions:&lt;br&gt;
+- Sofa: color: Cognac; dimensions: 85.5" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Cognac; dimensions: 70" W x 37"D x 39" H (SEAT HT: 19", SEAT DP: 22.5"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Cognac&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -12759,21 +12759,21 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARTINIQUE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Blue tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.
-Features
-- Camelback Design
-- Deep Button Tufting
-- Nailhead Trim
-- Arrow Feet
-- Bench-style Cushion
-- Welt Trim
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Blue; dimensions: 91" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Blue; dimensions: 68" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional
-Materials: Velvet-like, Solid Wood.
-Color: Blue
-Weight: 255 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARTINIQUE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Blue tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Camelback Design&lt;br&gt;
+- Deep Button Tufting&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Arrow Feet&lt;br&gt;
+- Bench-style Cushion&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Blue; dimensions: 91" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Blue; dimensions: 68" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -12885,21 +12885,21 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MARVIN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Built from Small Weave Chenille, Solid Wood, and finished in Pewter tones for a clean, cohesive look.
-Product Dimensions: SOFA: 99"L X 38"W X 36"H
-Features
-- Medium Density Foam
-- Shell Tufting
-- Rolled Arms
-- Single Cushion Seat
-- Round Bun Feet
-- Lumbar Pillows Included Included items and dimensions:
-- Sofa: color: Pewter; dimensions: 99" L x 38" W x 36" H; feature: Glam
-- Loveseat: color: Pewter; dimensions: 74" L x 38" W x 36" H; feature: Glam
-Materials: Small Weave Chenille, Solid Wood.
-Color: Pewter
-Weight: 257 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MARVIN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Glam character adds definition without feeling heavy. Built from Small Weave Chenille, Solid Wood, and finished in Pewter tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 99"L X 38"W X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Shell Tufting&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Single Cushion Seat&lt;br&gt;
+- Round Bun Feet&lt;br&gt;
+- Lumbar Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Pewter; dimensions: 99" L x 38" W x 36" H; feature: Glam&lt;br&gt;
+- Loveseat: color: Pewter; dimensions: 74" L x 38" W x 36" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Small Weave Chenille, Solid Wood.&lt;br&gt;
+Color: Pewter&lt;br&gt;
+Weight: 257 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13016,19 +13016,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MATTEO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Burgundy or Brown tones to suit a range of interiors.
-Features
-- Traditional
-- Burgundy or Brown
-- Ornate Details
-- Pillows Included
-- Rolled Arms Included items and dimensions:
-- Sofa: color: Burgundy or Brown; dimensions: 94" L x 37" W x 44" H; feature: Traditional
-- Loveseat: color: Burgundy or Brown; dimensions: 72" L x 37" W x 44" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Burgundy or Brown
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MATTEO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Burgundy or Brown tones to suit a range of interiors.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Burgundy or Brown&lt;br&gt;
+- Ornate Details&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Rolled Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Burgundy or Brown; dimensions: 94" L x 37" W x 44" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Burgundy or Brown; dimensions: 72" L x 37" W x 44" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Burgundy or Brown&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -13141,20 +13141,20 @@
       </c>
       <c r="G97" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MEZZANOTTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Real Italian Leather, Engineered Wood, construction and Midnight Blue tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 90"L X 38 1/2"W X 32 1/2"H (SEAT HT: 17", SEAT DP: 23 1/2")
-Features
-- Wide Seating w/ Metal Leg &amp; Track Arms
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- Webbing Back and Ring Seat Suspension
-- Attached Seat and Back Cushions w/ Welt
-- 100% Made in Italy
-- Fully Upholstered in Leather on all Sides
-Materials: Real Italian Leather, Engineered Wood.
-Color: Midnight Blue
-Weight: 264 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MEZZANOTTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Real Italian Leather, Engineered Wood, construction and Midnight Blue tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 38 1/2"W X 32 1/2"H (SEAT HT: 17", SEAT DP: 23 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Wide Seating w/ Metal Leg &amp;amp; Track Arms&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- Webbing Back and Ring Seat Suspension&lt;br&gt;
+- Attached Seat and Back Cushions w/ Welt&lt;br&gt;
+- 100% Made in Italy&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Midnight Blue&lt;br&gt;
+Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" s="16" t="inlineStr">
@@ -13276,20 +13276,20 @@
       </c>
       <c r="G98" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MEZZANOTTE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Real Italian Leather, Engineered Wood, build keeps the look polished and practical.
-Product Dimensions: Sofa: 90"L X 38 1/2"W X 32 1/2"H, LV: 77.2"L X 38 1/2"W X 32 1/2"H
-Features
-- Wide Seating w/ Metal Leg &amp; Track Arms
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- Webbing Back and Ring Seat Suspension
-- Attached Seat and Back Cushions w/ Welt
-- Fully Upholstered in Leather on all Sides
-- Made in Italy
-Materials: Real Italian Leather, Engineered Wood.
-Color: Gray
-Weight: 260.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MEZZANOTTE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Real Italian Leather, Engineered Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Sofa: 90"L X 38 1/2"W X 32 1/2"H, LV: 77.2"L X 38 1/2"W X 32 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Wide Seating w/ Metal Leg &amp;amp; Track Arms&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- Webbing Back and Ring Seat Suspension&lt;br&gt;
+- Attached Seat and Back Cushions w/ Welt&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;br&gt;
+- Made in Italy&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 260.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" s="16" t="inlineStr">
@@ -13410,22 +13410,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MIRAMAR Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Beige or Charcoal tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: 94"L X 37"W X 40"H
-Features
-- Beige or Charcoal
-- T-Seat Cushions
-- Loose Back Cushions
-- Low Rolled Arms
-- Turned Bun Legs
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Beige or Charcoal; dimensions: 94" L x 37" W x 40" H; feature: Transitional
-- Loveseat: color: Beige or Charcoal; dimensions: 71" L x 37" W x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Beige or Charcoal
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MIRAMAR Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Beige or Charcoal tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 94"L X 37"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Charcoal&lt;br&gt;
+- T-Seat Cushions&lt;br&gt;
+- Loose Back Cushions&lt;br&gt;
+- Low Rolled Arms&lt;br&gt;
+- Turned Bun Legs&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Charcoal; dimensions: 94" L x 37" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige or Charcoal; dimensions: 71" L x 37" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige or Charcoal&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -13542,19 +13542,19 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MISTY Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Solid Wood and finished in Blue Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 88"L X 38"W X 37"H
-Features
-- Rolled Arms
-- Loose Back Pillows
-- Tapered Legs
-- Sun &amp; Stain Resistant Revolution Fabric Included items and dimensions:
-- Sofa: color: Blue Gray; dimensions: 88" L x 38" W x 37" H; feature: Transitional
-- Loveseat: color: Blue Gray; dimensions: 65" L x 38" W x 37" H; feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Blue Gray
-Weight: 207 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MISTY Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Solid Wood and finished in Blue Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 38"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Tapered Legs&lt;br&gt;
+- Sun &amp;amp; Stain Resistant Revolution Fabric Included items and dimensions:&lt;br&gt;
+- Sofa: color: Blue Gray; dimensions: 88" L x 38" W x 37" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Blue Gray; dimensions: 65" L x 38" W x 37" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Blue Gray&lt;br&gt;
+Weight: 207 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -13671,24 +13671,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOLFETTA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Light Brown or Black tones, it blends durability with visual warmth.
-Product Dimensions: 90"L X 35"W X 31"H (SEAT HT: 22", SEAT DP: 22")
-Features
-- Traditional
-- Light Brown or Black
-- Faux Wood Carved Details
-- Box Seat Cushions
-- Loose Pillow Backs
-- Rolled Arms
-- Wooden Cabriole Legs
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Light Brown or Black; dimensions: 90" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional
-- Loveseat: color: Light Brown or Black; dimensions: 68" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Light Brown or Black
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOLFETTA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Light Brown or Black tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 90"L X 35"W X 31"H (SEAT HT: 22", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Light Brown or Black&lt;br&gt;
+- Faux Wood Carved Details&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wooden Cabriole Legs&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Brown or Black; dimensions: 90" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Light Brown or Black; dimensions: 68" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Light Brown or Black&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -13805,24 +13805,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MONTECELIO Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Velvet-like, Solid Wood, and finished in Light Gray or Navy tones for a clean, cohesive look.
-Product Dimensions: 91"L X 39"W X 38"H (SEAT HT: 19", SEAT DP: 25")
-Features
-- Light Gray or Navy
-- Single Tight Back Cushion
-- Box Seat Cushions
-- Contoured Armrest
-- Pillows w/ Hypo-allergenic Synthetic Down
-- Frame Corner Blocked &amp; Glued
-- Individual Nailheads
-- Welt Trim &amp; Tapered Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Light Gray or Navy; dimensions: 91" L x 39" W x 38" H (SEAT HT: 19", SEAT DP: 25"); feature: Transitional
-- Loveseat: color: Light Gray or Navy; dimensions: 64" L x 39" W x 38" H (SEAT HT: 19", SEAT DP: 25"); feature: Transitional
-Materials: Velvet-like, Solid Wood.
-Color: Light Gray or Navy
-Weight: 252 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MONTECELIO Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Velvet-like, Solid Wood, and finished in Light Gray or Navy tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 91"L X 39"W X 38"H (SEAT HT: 19", SEAT DP: 25")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Gray or Navy&lt;br&gt;
+- Single Tight Back Cushion&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Contoured Armrest&lt;br&gt;
+- Pillows w/ Hypo-allergenic Synthetic Down&lt;br&gt;
+- Frame Corner Blocked &amp;amp; Glued&lt;br&gt;
+- Individual Nailheads&lt;br&gt;
+- Welt Trim &amp;amp; Tapered Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray or Navy; dimensions: 91" L x 39" W x 38" H (SEAT HT: 19", SEAT DP: 25"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray or Navy; dimensions: 64" L x 39" W x 38" H (SEAT HT: 19", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
+Color: Light Gray or Navy&lt;br&gt;
+Weight: 252 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -13939,21 +13939,21 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOORPARK Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Boucle Fabric, Solid Wood, construction and Off-White tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 102"L X 48"W X 41"H (SEAT HT: 18", SEAT DP: 31")
-Features
-- T-Seats Cushions
-- Reversible Seat and Back Cushions
-- Spring Seat and Webbed Back Frame Suspension
-- Wide Sloped Track Arms
-- Padded Sides and Back
-- Down Fiber Blend Pillows Included items and dimensions:
-- Sofa: color: Off-White; dimensions: 102" L x 48" W x 41" H (SEAT HT: 18", SEAT DP: 31"); feature: Contemporary
-- Loveseat: color: Off-White; dimensions: 84" L x 48" W x 41" H (SEAT HT: 18", SEAT DP: 31"); feature: Contemporary
-Materials: Boucle Fabric, Solid Wood.
-Color: Off-White
-Weight: 367 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOORPARK Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Boucle Fabric, Solid Wood, construction and Off-White tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 102"L X 48"W X 41"H (SEAT HT: 18", SEAT DP: 31")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Seats Cushions&lt;br&gt;
+- Reversible Seat and Back Cushions&lt;br&gt;
+- Spring Seat and Webbed Back Frame Suspension&lt;br&gt;
+- Wide Sloped Track Arms&lt;br&gt;
+- Padded Sides and Back&lt;br&gt;
+- Down Fiber Blend Pillows Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White; dimensions: 102" L x 48" W x 41" H (SEAT HT: 18", SEAT DP: 31"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Off-White; dimensions: 84" L x 48" W x 41" H (SEAT HT: 18", SEAT DP: 31"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood.&lt;br&gt;
+Color: Off-White&lt;br&gt;
+Weight: 367 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -14067,14 +14067,14 @@
       </c>
       <c r="G104" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORETAINE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:
-- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H
-- Beige Sofa Arm &amp; Pillows: dimensions: 85" W x 34"D x 35" H
-- Beige Loveseat Base: dimensions: 61" W x 34"D x 35" H
-- Beige Loveseat Arm &amp; Pillows: dimensions: 61" W x 34"D x 35" H
-Weight: 211 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORETAINE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Beige Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 211 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="37" t="inlineStr">
@@ -14180,14 +14180,14 @@
       </c>
       <c r="G105" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORETAINE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:
-- Black Sofa Base: dimensions: 85" W x 34"D x 35" H
-- Black Sofa Arm &amp; Pillows: dimensions: 85" W x 34"D x 35" H
-- Black Loveseat Base: dimensions: 61" W x 34"D x 35" H
-- Black Loveseat Arm &amp; Pillows: dimensions: 61" W x 34"D x 35" H
-Weight: 197.22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORETAINE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+- Black Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Black Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Black Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Black Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 197.22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" s="37" t="inlineStr">
@@ -14293,14 +14293,14 @@
       </c>
       <c r="G106" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORETAINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room.
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:
-- Dark Gray Sofa Base: dimensions: 85" W x 34"D x 35" H
-- Dark Gray Sofa Arm &amp; Pillows: dimensions: 85" W x 34"D x 35" H
-- Dark Gray Loveseat Base: dimensions: 61" W x 34"D x 35" H
-- Dark Gray Loveseat Arm &amp; Pillows: dimensions: 61" W x 34"D x 35" H
-Weight: 195.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORETAINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+- Dark Gray Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Dark Gray Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Dark Gray Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Dark Gray Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 195.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" s="37" t="inlineStr">
@@ -14409,21 +14409,21 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOSSLEY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Ivory tones, the Fabric, Foam, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 93"L X 41"W X 36"H (SEAT HT: 20", SEAT DP: 24")
-Features
-- T Seat and Back Cushions
-- Spring Seat and Webbed Back Frame Suspension
-- Padded Back and Sides
-- English Pleated Arms
-- Stain Resistantant Fabric
-- Welt Trim Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 93" L x 41" W x 36" H (SEAT HT: 20", SEAT DP: 24"); feature: Transitional
-- Loveseat: color: Ivory; dimensions: 65" L x 41" W x 36" H (SEAT HT: 20", SEAT DP: 24"); feature: Transitional
-Materials: Fabric, Foam, Solid Wood.
-Color: Ivory
-Weight: 297 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOSSLEY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Ivory tones, the Fabric, Foam, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 41"W X 36"H (SEAT HT: 20", SEAT DP: 24")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T Seat and Back Cushions&lt;br&gt;
+- Spring Seat and Webbed Back Frame Suspension&lt;br&gt;
+- Padded Back and Sides&lt;br&gt;
+- English Pleated Arms&lt;br&gt;
+- Stain Resistantant Fabric&lt;br&gt;
+- Welt Trim Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 93" L x 41" W x 36" H (SEAT HT: 20", SEAT DP: 24"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 65" L x 41" W x 36" H (SEAT HT: 20", SEAT DP: 24"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 297 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -14540,21 +14540,21 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOTT Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 96"L X 40"W X 44"H
-Features
-- Medium Density Foam
-- Rolled Arms
-- Box Cushion Seating
-- Loose Back Pillows
-- Nailhead Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 96" L x 40" W x 44" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 73" L x 40" W x 44" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Gray
-Weight: 258 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOTT Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 96"L X 40"W X 44"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Box Cushion Seating&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 96" L x 40" W x 44" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 73" L x 40" W x 44" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 258 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -14671,20 +14671,20 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NADENE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Linen, Wood, and finished in Ivory tones for a clean, cohesive look.
-Product Dimensions: SOFA: 80"L X 38"W X 39"H
-Features
-- Sloped Arms
-- Fixed Back Pillows
-- Box Cushion Seat
-- Pillows Included
-- Tapered Legs Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 80" L x 38" W x 39" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 56" L x 38" W x 39" H; feature: Transitional
-Materials: Chenille, Linen, Wood.
-Color: Ivory
-Weight: 256 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NADENE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Linen, Wood, and finished in Ivory tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 80"L X 38"W X 39"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- Fixed Back Pillows&lt;br&gt;
+- Box Cushion Seat&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Tapered Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 80" L x 38" W x 39" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 56" L x 38" W x 39" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Linen, Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -14801,21 +14801,21 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NASH Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Linen-like Fabric, Solid Wood, construction and Ivory tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 96"L X 42"W X 40"H
-Features
-- Medium Density Foam
-- Rolled Arms
-- T-Cushion Seats
-- Fitted Back Cushions
-- Tapered Wooden Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 96" L x 42" W x 40" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 78" L x 42" W x 40" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Ivory
-Weight: 256 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NASH Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Linen-like Fabric, Solid Wood, construction and Ivory tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 96"L X 42"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- T-Cushion Seats&lt;br&gt;
+- Fitted Back Cushions&lt;br&gt;
+- Tapered Wooden Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 96" L x 42" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 78" L x 42" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14933,20 +14933,20 @@
       </c>
       <c r="G111" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEFYN Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Ivory tones, the Burlap Weave, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 90"W X 41"D X 40"H
-Features
-- Medium Density Foam
-- Sloped Arms
-- Single Cushion Seat
-- Turned Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 90" W x 41"D x 40" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 65" W x 41"D x 40" H; feature: Transitional
-Materials: Burlap Weave, Solid Wood.
-Color: Ivory
-Weight: 289 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEFYN Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Ivory tones, the Burlap Weave, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 90"W X 41"D X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- Single Cushion Seat&lt;br&gt;
+- Turned Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 90" W x 41"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 65" W x 41"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Burlap Weave, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H111" s="20" t="inlineStr">
@@ -15068,20 +15068,20 @@
       </c>
       <c r="G112" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEFYN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Burlap Weave, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 90"W X 41"D X 40"H
-Features
-- Medium Density Foam
-- Sloped Arms
-- Single Cushion Seat
-- Tapered Block Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 90" W x 41"D x 40" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 65" W x 41"D x 40" H; feature: Transitional
-Materials: Burlap Weave, Solid Wood.
-Color: Gray
-Weight: 289 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEFYN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Burlap Weave, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 90"W X 41"D X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- Single Cushion Seat&lt;br&gt;
+- Tapered Block Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 90" W x 41"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 65" W x 41"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Burlap Weave, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H112" s="20" t="inlineStr">
@@ -15203,22 +15203,22 @@
       </c>
       <c r="G113" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEW MEADOWS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Ash Green or Ivory tones, the Fabric, Leatherette, Foam, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 101"L X 44"W X 40"H (SEAT HT: 21", SEAT DP: 30")
-Features
-- Ash Green or Ivory
-- T Seat Cushion
-- 100% Polyester Body Fabric
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln-Dried Wooden Frame
-- Bracket Wooden Feet Included items and dimensions:
-- MEADOWS Sofa: color: Ash Green or Ivory; dimensions: 101" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional
-- MEADOWS Loveseat: color: Ash Green or Ivory; dimensions: 75" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional
-Materials: Fabric, Leatherette, Foam, Solid Wood.
-Color: Ash Green or Ivory
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEW MEADOWS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Ash Green or Ivory tones, the Fabric, Leatherette, Foam, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 44"W X 40"H (SEAT HT: 21", SEAT DP: 30")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Ash Green or Ivory&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- 100% Polyester Body Fabric&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln-Dried Wooden Frame&lt;br&gt;
+- Bracket Wooden Feet Included items and dimensions:&lt;br&gt;
+- MEADOWS Sofa: color: Ash Green or Ivory; dimensions: 101" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;br&gt;
+- MEADOWS Loveseat: color: Ash Green or Ivory; dimensions: 75" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
+Color: Ash Green or Ivory&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H113" s="39" t="inlineStr">
@@ -15340,22 +15340,22 @@
       </c>
       <c r="G114" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEW MEADOWS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Leatherette, Foam, Solid Wood, and finished in Sand or Caramel tones for a clean, cohesive look.
-Product Dimensions: SOFA: 101"L X 44"W X 40"H (SEAT HT: 21", SEAT DP: 30")
-Features
-- Sand or Caramel
-- T Seat Cushion
-- 100% Polyester Body Fabric
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln-Dried Wooden Frame
-- Bracket Wooden Feet Included items and dimensions:
-- MEADOWS Sofa: color: Sand or Caramel; dimensions: 101" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional
-- MEADOWS Loveseat: color: Sand or Caramel; dimensions: 75" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional
-Materials: Fabric, Leatherette, Foam, Solid Wood.
-Color: Sand or Caramel
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEW MEADOWS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Leatherette, Foam, Solid Wood, and finished in Sand or Caramel tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 44"W X 40"H (SEAT HT: 21", SEAT DP: 30")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Sand or Caramel&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- 100% Polyester Body Fabric&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln-Dried Wooden Frame&lt;br&gt;
+- Bracket Wooden Feet Included items and dimensions:&lt;br&gt;
+- MEADOWS Sofa: color: Sand or Caramel; dimensions: 101" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;br&gt;
+- MEADOWS Loveseat: color: Sand or Caramel; dimensions: 75" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
+Color: Sand or Caramel&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H114" s="39" t="inlineStr">
@@ -15477,23 +15477,23 @@
       </c>
       <c r="G115" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEWDALE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 93"L X 36"W X 40"H
-Features
-- Traditional
-- Medium Density Foam
-- Rolled Arms
-- Wood Trim
-- Box Cushion Seating
-- Arched Black Design
-- Round Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 93" L x 36" W x 40" H; feature: Traditional
-- Loveseat: color: Gray; dimensions: 70" L x 36" W x 40" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Gray
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEWDALE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 36"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wood Trim&lt;br&gt;
+- Box Cushion Seating&lt;br&gt;
+- Arched Black Design&lt;br&gt;
+- Round Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 93" L x 36" W x 40" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 70" L x 36" W x 40" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H115" s="45" t="inlineStr">
@@ -15615,23 +15615,23 @@
       </c>
       <c r="G116" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEWDALE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Finished in Ivory tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 93"L X 36"W X 40"H
-Features
-- Traditional
-- Medium Density Foam
-- Rolled Arms
-- Wood Trim
-- Box Cushion Seating
-- Arched Black Design
-- Round Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 93" L x 36" W x 40" H; feature: Traditional
-- Loveseat: color: Ivory; dimensions: 70" L x 36" W x 40" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Ivory
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEWDALE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Finished in Ivory tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 36"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wood Trim&lt;br&gt;
+- Box Cushion Seating&lt;br&gt;
+- Arched Black Design&lt;br&gt;
+- Round Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 93" L x 36" W x 40" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 70" L x 36" W x 40" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" s="45" t="inlineStr">
@@ -15753,24 +15753,24 @@
       </c>
       <c r="G117" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEWDALE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood, and finished in Brown or Gold tones for a clean, cohesive look.
-Product Dimensions: SOFA: 93"L X 36"W X 40"H
-Features
-- Traditional
-- Brown or Gold
-- Medium Density Foam
-- Rolled Arms
-- Wood Trim
-- Box Cushion Seating
-- Arched Black Design
-- Round Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Brown or Gold; dimensions: 93" L x 36" W x 40" H; feature: Traditional
-- Loveseat: color: Brown or Gold; dimensions: 70" L x 36" W x 40" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Brown or Gold
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEWDALE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood, and finished in Brown or Gold tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 36"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Brown or Gold&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wood Trim&lt;br&gt;
+- Box Cushion Seating&lt;br&gt;
+- Arched Black Design&lt;br&gt;
+- Round Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Gold; dimensions: 93" L x 36" W x 40" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Brown or Gold; dimensions: 70" L x 36" W x 40" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Brown or Gold&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" s="45" t="inlineStr">
@@ -15891,21 +15891,21 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NEWRY Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Fabric, Foam, Solid Wood, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: SOFA: 101"L X 39"W X 38"H (SEAT HT: 18", SEAT DP: 26")
-Features
-- Reversible Back Pillows and Seat Cushions
-- Spring Seat and Webbed Back Frame Suspension
-- Padded Sides and Back
-- Wide Track Arms
-- Welt Trim
-- Block Wooden Legs Included items and dimensions:
-- Sofa: color: Gray; dimensions: 101" L x 39" W x 38" H (SEAT HT: 18", SEAT DP: 26"); feature: Transitional
-- Loveseat: color: Gray; dimensions: 75" L x 39" W x 38" H (SEAT HT: 18", SEAT DP: 26"); feature: Transitional
-Materials: Fabric, Foam, Solid Wood.
-Color: Gray
-Weight: 317 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NEWRY Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Fabric, Foam, Solid Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 39"W X 38"H (SEAT HT: 18", SEAT DP: 26")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Reversible Back Pillows and Seat Cushions&lt;br&gt;
+- Spring Seat and Webbed Back Frame Suspension&lt;br&gt;
+- Padded Sides and Back&lt;br&gt;
+- Wide Track Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Block Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 101" L x 39" W x 38" H (SEAT HT: 18", SEAT DP: 26"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 75" L x 39" W x 38" H (SEAT HT: 18", SEAT DP: 26"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 317 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -16022,22 +16022,22 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NICANOR Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Chenille, Leatherette, Solid Wood, construction and Tan or Gold tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 94"L X 37"W X 41"H
-Features
-- Traditional
-- Tan or Gold
-- Loose Back Pillows
-- Rolled Arms
-- High-Density Foam Cushions
-- Pillows Included
-- Gold &amp; Bronze Included items and dimensions:
-- Sofa: color: Tan or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional
-- Loveseat: color: Tan or Gold; dimensions: 73" L x 37" W x 41" H; feature: Traditional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Tan or Gold
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NICANOR Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Chenille, Leatherette, Solid Wood, construction and Tan or Gold tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Tan or Gold&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Gold &amp;amp; Bronze Included items and dimensions:&lt;br&gt;
+- Sofa: color: Tan or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Tan or Gold; dimensions: 73" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Tan or Gold&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -16155,23 +16155,23 @@
       </c>
       <c r="G120" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALENCIA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, and finished in Dark Cherry or Beige tones for a clean, cohesive look.
-Product Dimensions: 94 1/2" X 41 3/4" X 26"
-Features
-- Traditional
-- Dark Cherry or Beige
-- Button Tufted Back
-- Carved Details
-- Reversible Seat Cushion w/ Welt
-- Rolled Arms
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Dark Cherry or Beige; dimensions: 94 1 or 2" x 41 3 or 4" x 26"; feature: Traditional
-- Loveseat: color: Dark Cherry or Beige; dimensions: 69 3 or 4" x 41 3 or 4" x 26"; feature: Traditional
-Materials: Fabric, Solid Wood.
-Color: Dark Cherry or Beige
-Weight: 414.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALENCIA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, and finished in Dark Cherry or Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 94 1/2" X 41 3/4" X 26"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Beige&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Reversible Seat Cushion w/ Welt&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Cherry or Beige; dimensions: 94 1 or 2" x 41 3 or 4" x 26"; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Cherry or Beige; dimensions: 69 3 or 4" x 41 3 or 4" x 26"; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Beige&lt;br&gt;
+Weight: 414.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" s="22" t="inlineStr">
@@ -16293,23 +16293,23 @@
       </c>
       <c r="G121" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALENCIA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.
-Product Dimensions: 94 1/2" X 41 3/4" X 26"
-Features
-- Traditional
-- Dark Cherry or Brown
-- Button Tufted Back
-- Carved Details
-- Reversible Seat Cushion w/ Welt
-- Rolled Arms
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Dark Cherry or Brown; dimensions: 94 1 or 2" x 41 3 or 4" x 26"; feature: Traditional
-- Loveseat: color: Dark Cherry or Brown; dimensions: 69 3 or 4" x 41 3 or 4" x 26"; feature: Traditional
-Materials: Leatherette, Solid Wood.
-Color: Dark Cherry or Brown
-Weight: 426.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALENCIA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 94 1/2" X 41 3/4" X 26"&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Brown&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Reversible Seat Cushion w/ Welt&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Cherry or Brown; dimensions: 94 1 or 2" x 41 3 or 4" x 26"; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Cherry or Brown; dimensions: 69 3 or 4" x 41 3 or 4" x 26"; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Brown&lt;br&gt;
+Weight: 426.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" s="22" t="inlineStr">
@@ -16430,24 +16430,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PANOZZO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Beige or Walnut tones to suit a range of interiors.
-Product Dimensions: 90"L X 35"W X 31"H (SEAT HT: 22", SEAT DP: 22")
-Features
-- Traditional
-- Beige or Walnut
-- Faux Wood Carved Details
-- Box Seat Cushions
-- Loose Pillow Backs
-- Rolled Arms
-- Wooden Cabriole Legs
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Beige or Walnut; dimensions: 90" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional
-- Loveseat: color: Beige or Walnut; dimensions: 68" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Beige or Walnut
-Weight: 210 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PANOZZO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Beige or Walnut tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 90"L X 35"W X 31"H (SEAT HT: 22", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Beige or Walnut&lt;br&gt;
+- Faux Wood Carved Details&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Wooden Cabriole Legs&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Walnut; dimensions: 90" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional&lt;br&gt;
+- Loveseat: color: Beige or Walnut; dimensions: 68" L x 35" W x 31" H (SEAT HT: 22", SEAT DP: 22"); feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige or Walnut&lt;br&gt;
+Weight: 210 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -16564,20 +16564,20 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PARKER Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Linen-like, Solid Wood construction and Ivory tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 86"L X 41"W X 35"H
-Features
-- Middle Leg for Structural Support
-- Diamond &amp; Crystal Patterns
-- Accent Pillows Included
-- High-Density Foam Cushions
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 86" L x 41" W x 35" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 68" L x 41" W x 35" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Ivory
-Weight: 220 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PARKER Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Linen-like, Solid Wood construction and Ivory tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 86"L X 41"W X 35"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Middle Leg for Structural Support&lt;br&gt;
+- Diamond &amp;amp; Crystal Patterns&lt;br&gt;
+- Accent Pillows Included&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 86" L x 41" W x 35" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 68" L x 41" W x 35" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 220 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -16694,23 +16694,23 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PICOTEE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Linen-like, Solid Wood, then finished in Light Gray or Charcoal tones to suit a range of interiors.
-Product Dimensions: SOFA: 101"L X 44"W X 40"H
-Features
-- Light Gray or Charcoal
-- Nailhead Trim
-- T-Seat Cushion
-- Loose Pillow Back
-- Wide Track Armrest
-- Block Legs
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Light Gray or Charcoal; dimensions: 101" L x 44" W x 40" H; feature: Transitional
-- Loveseat: color: Light Gray or Charcoal; dimensions: 75" L x 44" W x 40" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Light Gray or Charcoal
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PICOTEE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Linen-like, Solid Wood, then finished in Light Gray or Charcoal tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 101"L X 44"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Gray or Charcoal&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- T-Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Wide Track Armrest&lt;br&gt;
+- Block Legs&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray or Charcoal; dimensions: 101" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray or Charcoal; dimensions: 75" L x 44" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Light Gray or Charcoal&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -16827,22 +16827,22 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PLAISTOW Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: 94"L X 40"W X 38"H (SEAT HT: 21", SEAT DP: 24 1/2")
-Features
-- Bolted Frames
-- Box Seat Cushions
-- Loose Pillow Back
-- Rounded Low Padded Arms
-- Zippered Reversible Cushions
-- Tapered Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 94" L x 40" W x 38" H (SEAT HT: 21", SEAT DP: 24 1 or 2"); feature: Transitional
-- Loveseat: color: Gray; dimensions: 67" L x 40" W x 38" H (SEAT HT: 21", SEAT DP: 24 1 or 2"); feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Gray
-Weight: 296 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PLAISTOW Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 94"L X 40"W X 38"H (SEAT HT: 21", SEAT DP: 24 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Bolted Frames&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Rounded Low Padded Arms&lt;br&gt;
+- Zippered Reversible Cushions&lt;br&gt;
+- Tapered Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 94" L x 40" W x 38" H (SEAT HT: 21", SEAT DP: 24 1 or 2"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 67" L x 40" W x 38" H (SEAT HT: 21", SEAT DP: 24 1 or 2"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 296 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -16959,18 +16959,18 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PORTHCAWL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Ivory tones, the Chenille, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 88"L X 39"W X 37"H
-Features
-- Rounded Arms
-- Welt-Cord Trim
-- Stain Resistant Included items and dimensions:
-- Sofa: color: Ivory; dimensions: 88" L x 39" W x 37" H; feature: Transitional
-- Loveseat: color: Ivory; dimensions: 70" L x 39" W x 37" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Ivory
-Weight: 220 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PORTHCAWL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Ivory tones, the Chenille, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 39"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Rounded Arms&lt;br&gt;
+- Welt-Cord Trim&lt;br&gt;
+- Stain Resistant Included items and dimensions:&lt;br&gt;
+- Sofa: color: Ivory; dimensions: 88" L x 39" W x 37" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Ivory; dimensions: 70" L x 39" W x 37" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Ivory&lt;br&gt;
+Weight: 220 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -17088,22 +17088,22 @@
       </c>
       <c r="G127" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-QUIRINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Chenille, Leatherette, Solid Wood, then finished in Burgundy or Dark Brown tones to suit a range of interiors.
-Product Dimensions: SOFA: 93"L X 38"W X 42"H
-Features
-- Traditional
-- Burgundy or Dark Brown
-- Intricate Wood Trim
-- Rolled Arms
-- High-Density Foam Cushions
-- Loose Back Pillows
-- Pillows Included Included items and dimensions:
-- Sofa: color: Burgundy or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional
-- Loveseat: color: Burgundy or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Burgundy or Dark Brown
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+QUIRINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Chenille, Leatherette, Solid Wood, then finished in Burgundy or Dark Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 38"W X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Burgundy or Dark Brown&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Burgundy or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Burgundy or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Burgundy or Dark Brown&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H127" s="26" t="inlineStr">
@@ -17225,22 +17225,22 @@
       </c>
       <c r="G128" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-QUIRINO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Leatherette, Solid Wood construction and Light Brown or Dark Brown tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 93"L X 38"W X 42"H
-Features
-- Traditional
-- Light Brown or Dark Brown
-- Intricate Wood Trim
-- Rolled Arms
-- High-Density Foam Cushions
-- Loose Back Pillows
-- Pillows Included Included items and dimensions:
-- Sofa: color: Light Brown or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional
-- Loveseat: color: Light Brown or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Light Brown or Dark Brown
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+QUIRINO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Leatherette, Solid Wood construction and Light Brown or Dark Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 38"W X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Light Brown or Dark Brown&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Brown or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Light Brown or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Light Brown or Dark Brown&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H128" s="26" t="inlineStr">
@@ -17362,22 +17362,22 @@
       </c>
       <c r="G129" s="26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-QUIRINO Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Tan or Dark Brown tones, the Chenille, Leatherette, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 93"L X 38"W X 42"H
-Features
-- Traditional
-- Tan or Dark Brown
-- Intricate Wood Trim
-- Rolled Arms
-- High-Density Foam Cushions
-- Loose Back Pillows
-- Pillows Included Included items and dimensions:
-- Sofa: color: Tan or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional
-- Loveseat: color: Tan or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Tan or Dark Brown
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+QUIRINO Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Tan or Dark Brown tones, the Chenille, Leatherette, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 38"W X 42"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Tan or Dark Brown&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Tan or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Tan or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Tan or Dark Brown&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H129" s="26" t="inlineStr">
@@ -17499,22 +17499,22 @@
       </c>
       <c r="G130" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RONJA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Dark Brown tones, it blends durability with visual warmth.
-Features
-- Traditional
-- Damask Fabric
-- Button Tufting
-- Tight Back
-- Reversible Box Cushion
-- Darl Brown Welting
-- Rolled Arms With Wood Trim
-- Round Bun Feet Included items and dimensions:
-- Sofa: color: Dark Brown; dimensions: 94" L x 37" W x 44" H; feature: Traditional
-- Loveseat: color: Dark Brown; dimensions: 72" L x 37" W x 44" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Dark Brown
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RONJA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Dark Brown tones, it blends durability with visual warmth.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Damask Fabric&lt;br&gt;
+- Button Tufting&lt;br&gt;
+- Tight Back&lt;br&gt;
+- Reversible Box Cushion&lt;br&gt;
+- Darl Brown Welting&lt;br&gt;
+- Rolled Arms With Wood Trim&lt;br&gt;
+- Round Bun Feet Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Brown; dimensions: 94" L x 37" W x 44" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Brown; dimensions: 72" L x 37" W x 44" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Dark Brown&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H130" s="28" t="inlineStr">
@@ -17632,22 +17632,22 @@
       </c>
       <c r="G131" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-RONJA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Dark Brown tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Features
-- Traditional
-- Damask Fabric
-- Button Tufting
-- Tight Back
-- Reversible Box Cushion
-- Darl Brown Welting
-- Rolled Arms With Wood Trim
-- Round Bun Feet Included items and dimensions:
-- Sofa: color: Black; dimensions: 94" L x 37" W x 44" H; feature: Traditional
-- Loveseat: color: Black; dimensions: 72" L x 37" W x 44" H; feature: Traditional
-Materials: Chenille, Solid Wood.
-Color: Dark Brown
-Weight: 330 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+RONJA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Dark Brown tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Damask Fabric&lt;br&gt;
+- Button Tufting&lt;br&gt;
+- Tight Back&lt;br&gt;
+- Reversible Box Cushion&lt;br&gt;
+- Darl Brown Welting&lt;br&gt;
+- Rolled Arms With Wood Trim&lt;br&gt;
+- Round Bun Feet Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black; dimensions: 94" L x 37" W x 44" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Black; dimensions: 72" L x 37" W x 44" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Dark Brown&lt;br&gt;
+Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H131" s="28" t="inlineStr">
@@ -17764,21 +17764,21 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SAN ROQUE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Fabric, Leatherette, Solid Wood, construction and Crosshatch Brown or Espresso or Dark Cherry tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 88"L X 35"W X 37"H
-Features
-- Traditional
-- Crosshatch Brown or Espresso or Dark Cherry
-- Rolled Arms
-- Pillows Included
-- Intricate Wood Trim
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- ROQUE Sofa: color: Crosshatch Brown or Espresso or Dark Cherry; dimensions: 88" L x 35" W x 37" H; feature: Traditional
-- ROQUE Loveseat: color: Crosshatch Brown or Espresso or Dark Cherry; dimensions: 69" L x 35" W x 37" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Crosshatch Brown or Espresso or Dark Cherry
-Weight: 250 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SAN ROQUE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Fabric, Leatherette, Solid Wood, construction and Crosshatch Brown or Espresso or Dark Cherry tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 35"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Crosshatch Brown or Espresso or Dark Cherry&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- ROQUE Sofa: color: Crosshatch Brown or Espresso or Dark Cherry; dimensions: 88" L x 35" W x 37" H; feature: Traditional&lt;br&gt;
+- ROQUE Loveseat: color: Crosshatch Brown or Espresso or Dark Cherry; dimensions: 69" L x 35" W x 37" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Crosshatch Brown or Espresso or Dark Cherry&lt;br&gt;
+Weight: 250 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -17895,21 +17895,21 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SILVAN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Velvet-like Fabric, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 93"L X 37"W X 33"H
-Features
-- Medium Density Foam
-- Tuxedo Design
-- Track Arms
-- Button Tufted
-- Single Cushion Seat
-- Lumbar Pillows Included Included items and dimensions:
-- Sofa: color: Gray; dimensions: 93" L x 37" W x 33" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 73" L x 37" W x 33" H; feature: Transitional
-Materials: Velvet-like Fabric, Solid Wood.
-Color: Gray
-Weight: 260 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SILVAN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Velvet-like Fabric, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 93"L X 37"W X 33"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Tuxedo Design&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Button Tufted&lt;br&gt;
+- Single Cushion Seat&lt;br&gt;
+- Lumbar Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 93" L x 37" W x 33" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 73" L x 37" W x 33" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like Fabric, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 260 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -18026,21 +18026,21 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINATRA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Linen-like Fabric, Solid Wood construction and Light Mocha or Navy or Champagne tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 91"L X 41 1/2"W X 42 1/2"H
-Features
-- Light Mocha or Navy or Champagne
-- Nailhead Trim
-- Rolled Arms
-- Loose Back Pillows
-- 1.8 Density Gel Cushion Layer
-- Pillows Included Included items and dimensions:
-- Sofa: color: Light Mocha or Navy or Champagne; dimensions: 91" L x 41 1 or 2" W x 42 1 or 2" H; feature: Transitional
-- Loveseat: color: Light Mocha or Navy or Champagne; dimensions: 68" L x 41 1 or 2" W x 42 1 or 2" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Light Mocha or Navy or Champagne
-Weight: 332 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINATRA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Linen-like Fabric, Solid Wood construction and Light Mocha or Navy or Champagne tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 41 1/2"W X 42 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Mocha or Navy or Champagne&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- 1.8 Density Gel Cushion Layer&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Mocha or Navy or Champagne; dimensions: 91" L x 41 1 or 2" W x 42 1 or 2" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Mocha or Navy or Champagne; dimensions: 68" L x 41 1 or 2" W x 42 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Light Mocha or Navy or Champagne&lt;br&gt;
+Weight: 332 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -18158,22 +18158,22 @@
       </c>
       <c r="G135" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SISSETON Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 91"L X 37"W X 36"H
-Features
-- Medium Density Foam
-- Sloped Arms
-- T-Cushion Seats
-- Nailhead trim
-- Loose Back Pillows
-- Cabriole Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 91" L x 37" W x 36" H; feature: Transitional
-- Loveseat: color: Light Gray; dimensions: 71" L x 37" W x 36" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Light Gray
-Weight: 276 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SISSETON Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 37"W X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- T-Cushion Seats&lt;br&gt;
+- Nailhead trim&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Cabriole Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 91" L x 37" W x 36" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 71" L x 37" W x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 276 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H135" s="32" t="inlineStr">
@@ -18295,22 +18295,22 @@
       </c>
       <c r="G136" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SISSETON Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood, and finished in Purple tones for a clean, cohesive look.
-Product Dimensions: SOFA: 91"L X 37"W X 36"H
-Features
-- Medium Density Foam
-- Sloped Arms
-- T-Cushion Seats
-- Nailhead trim
-- Loose Back Pillows
-- Cabriole Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Purple; dimensions: 91" L x 37" W x 36" H; feature: Transitional
-- Loveseat: color: Purple; dimensions: 71" L x 37" W x 36" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Purple
-Weight: 276 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SISSETON Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood, and finished in Purple tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 37"W X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- T-Cushion Seats&lt;br&gt;
+- Nailhead trim&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Cabriole Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Purple; dimensions: 91" L x 37" W x 36" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Purple; dimensions: 71" L x 37" W x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Purple&lt;br&gt;
+Weight: 276 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H136" s="32" t="inlineStr">
@@ -18432,22 +18432,22 @@
       </c>
       <c r="G137" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SISSETON Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Small Weave Chenille, Solid Wood, then finished in Navy tones to suit a range of interiors.
-Product Dimensions: SOFA: 91"L X 37"W X 36"H
-Features
-- Medium Density Foam
-- Sloped Arms
-- T-Cushion Seats
-- Nailhead trim
-- Loose Back Pillows
-- Cabriole Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Navy; dimensions: 91" L x 37" W x 36" H; feature: Transitional
-- Loveseat: color: Navy; dimensions: 71" L x 37" W x 36" H; feature: Transitional
-Materials: Small Weave Chenille, Solid Wood.
-Color: Navy
-Weight: 276 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SISSETON Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Small Weave Chenille, Solid Wood, then finished in Navy tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 37"W X 36"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Sloped Arms&lt;br&gt;
+- T-Cushion Seats&lt;br&gt;
+- Nailhead trim&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Cabriole Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Navy; dimensions: 91" L x 37" W x 36" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Navy; dimensions: 71" L x 37" W x 36" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Small Weave Chenille, Solid Wood.&lt;br&gt;
+Color: Navy&lt;br&gt;
+Weight: 276 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H137" s="32" t="inlineStr">
@@ -18569,23 +18569,23 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SKYLINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Light Gray or Brown tones, the Fabric, Leatherette, Foam, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 96"L X 44"W X 40"H (SEAT HT: 22", SEAT DP: 30")
-Features
-- Light Gray or Brown
-- Oversized Sofa
-- T Seat Cushion
-- Sloped Track Arms w/ Welt
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln Dried Wooden Frame
-- Bracket Wooden Fee Included items and dimensions:
-- Sofa: color: Light Gray or Brown; dimensions: 96" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional
-- Loveseat: color: Light Gray or Brown; dimensions: 71" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional
-Materials: Fabric, Leatherette, Foam, Solid Wood.
-Color: Light Gray or Brown
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SKYLINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Light Gray or Brown tones, the Fabric, Leatherette, Foam, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 96"L X 44"W X 40"H (SEAT HT: 22", SEAT DP: 30")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Gray or Brown&lt;br&gt;
+- Oversized Sofa&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- Sloped Track Arms w/ Welt&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln Dried Wooden Frame&lt;br&gt;
+- Bracket Wooden Fee Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray or Brown; dimensions: 96" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray or Brown; dimensions: 71" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
+Color: Light Gray or Brown&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
@@ -18707,23 +18707,23 @@
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SKYLINE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Leatherette, Foam, Solid Wood, and finished in Pewter or Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 96"L X 44"W X 40"H (SEAT HT: 22", SEAT DP: 30")
-Features
-- Pewter or Gray
-- Oversized Sofa
-- T Seat Cushion
-- Sloped Track Arms w/ Welt
-- Spring Seat &amp; Webbing Back Suspension
-- Reversible Back Pillows &amp; Accent Pillows w/ Fiber Fill
-- Kiln Dried Wooden Frame
-- Bracket Wooden Fee Included items and dimensions:
-- Sofa: color: Pewter or Gray; dimensions: 96" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional
-- Loveseat: color: Pewter or Gray; dimensions: 71" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional
-Materials: Fabric, Leatherette, Foam, Solid Wood.
-Color: Pewter or Gray
-Weight: 225 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SKYLINE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Leatherette, Foam, Solid Wood, and finished in Pewter or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 96"L X 44"W X 40"H (SEAT HT: 22", SEAT DP: 30")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pewter or Gray&lt;br&gt;
+- Oversized Sofa&lt;br&gt;
+- T Seat Cushion&lt;br&gt;
+- Sloped Track Arms w/ Welt&lt;br&gt;
+- Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
+- Kiln Dried Wooden Frame&lt;br&gt;
+- Bracket Wooden Fee Included items and dimensions:&lt;br&gt;
+- Sofa: color: Pewter or Gray; dimensions: 96" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Pewter or Gray; dimensions: 71" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
+Color: Pewter or Gray&lt;br&gt;
+Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
@@ -18844,23 +18844,23 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STEPHNEY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray or Gold tones, the Linen-like, Foam, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 87"L X 42"W X 36 1/2"H (SEAT HT: 20 1/2", SEAT DP: 24")
-Features
-- Gray or Gold
-- Stain-Resistant Revolution Fabric
-- T-Cushion Seat
-- Loose Back Pillows
-- Sloped Armrest
-- Tapered Wooden Legs
-- Welt Trim
-- Pillows Included Included items and dimensions:
-- Sofa: color: Gray or Gold; dimensions: 87" L x 42" W x 36 1 or 2" H (SEAT HT: 20 1 or 2", SEAT DP: 24"); feature: Transitional
-- Loveseat: color: Gray or Gold; dimensions: 67" L x 42" W x 36 1 or 2" H (SEAT HT: 20 1 or 2", SEAT DP: 24"); feature: Transitional
-Materials: Linen-like, Foam, Solid Wood.
-Color: Gray or Gold
-Weight: 300 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STEPHNEY Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray or Gold tones, the Linen-like, Foam, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 87"L X 42"W X 36 1/2"H (SEAT HT: 20 1/2", SEAT DP: 24")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gray or Gold&lt;br&gt;
+- Stain-Resistant Revolution Fabric&lt;br&gt;
+- T-Cushion Seat&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Sloped Armrest&lt;br&gt;
+- Tapered Wooden Legs&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray or Gold; dimensions: 87" L x 42" W x 36 1 or 2" H (SEAT HT: 20 1 or 2", SEAT DP: 24"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray or Gold; dimensions: 67" L x 42" W x 36 1 or 2" H (SEAT HT: 20 1 or 2", SEAT DP: 24"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Foam, Solid Wood.&lt;br&gt;
+Color: Gray or Gold&lt;br&gt;
+Weight: 300 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -18977,23 +18977,23 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-STICKNEY Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Light Gray or Navy tones for a clean, cohesive look.
-Product Dimensions: 83"L X 37"W X 40"H
-Features
-- Light Gray or Navy
-- Box Seat Cushions
-- Loose Back Cushions
-- Sloped Track Arms
-- Individual Nailheads
-- Pillows Included
-- Tapered Legs
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Light Gray or Navy; dimensions: 83" L x 37" W x 40" H; feature: Transitional
-- Loveseat: color: Light Gray or Navy; dimensions: 60" L x 37" W x 40" H; feature: Transitional
-Materials: Linen-like, Solid Wood.
-Color: Light Gray or Navy
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+STICKNEY Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Light Gray or Navy tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 83"L X 37"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Light Gray or Navy&lt;br&gt;
+- Box Seat Cushions&lt;br&gt;
+- Loose Back Cushions&lt;br&gt;
+- Sloped Track Arms&lt;br&gt;
+- Individual Nailheads&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Tapered Legs&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray or Navy; dimensions: 83" L x 37" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray or Navy; dimensions: 60" L x 37" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
+Color: Light Gray or Navy&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -19111,21 +19111,21 @@
       </c>
       <c r="G142" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TABITHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Leatherette, Solid Wood, construction and Brown or Gold tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 94"L X 37"W X 37.5"H
-Features
-- Traditional
-- Brown or Gold
-- Rolled Arms
-- Intricate Wood Trim
-- High-Density Foam Cushions
-- Pillows Included Included items and dimensions:
-- Sofa: color: Brown or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional
-- Loveseat: color: Brown or Gold; dimensions: 72" L x 37" W x 41" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Brown or Gold
-Weight: 295 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TABITHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Leatherette, Solid Wood, construction and Brown or Gold tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 37.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Brown or Gold&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Brown or Gold; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown or Gold&lt;br&gt;
+Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="35" t="inlineStr">
@@ -19247,21 +19247,21 @@
       </c>
       <c r="G143" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TABITHA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Finished in Wine or Gold tones, the Fabric, Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 94"L X 37"W X 37.5"H
-Features
-- Traditional
-- Wine or Gold
-- Rolled Arms
-- Intricate Wood Trim
-- High-Density Foam Cushions
-- Pillows Included Included items and dimensions:
-- Sofa: color: Wine or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional
-- Loveseat: color: Wine or Gold; dimensions: 72" L x 37" W x 41" H; feature: Traditional
-Materials: Fabric, Leatherette, Solid Wood.
-Color: Wine or Gold
-Weight: 295 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TABITHA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Finished in Wine or Gold tones, the Fabric, Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 94"L X 37"W X 37.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Wine or Gold&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Intricate Wood Trim&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Wine or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Wine or Gold; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
+Color: Wine or Gold&lt;br&gt;
+Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H143" s="35" t="inlineStr">
@@ -19382,20 +19382,20 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TEPIC Manual Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Contemporary build keeps the look polished and practical.
-Product Dimensions: SF: 85.8"L X 39.8"W X 42.1"H, LV:79"L X 39.8"W X 42.1"H
-Features
-- Pillow Top Arms
-- Nailheads
-- Drop-Down Table w/ Cup Holders in Sofa
-- Console w/ Cup Holders in Loveseat
-- USB &amp; Power Outlet Included items and dimensions:
-- Manual Sofa w/ Drop Down Table w/ Usb Charging (Metal Cup): color: Brown; dimensions: 85.8" W x 39.75"D x 42.1" H; feature: Transitional
-- Manual Loveseat w/ Console w/ Glider w/ Usb Charging (Metal Cup Holder and Plastic Storage Box): color: Brown; dimensions: 79" W x 39.75"D x 42.1" H; feature: Transitional
-Materials: Contemporary.
-Color: Brown
-Weight: 469.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TEPIC Manual Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Brown tones, the Contemporary build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SF: 85.8"L X 39.8"W X 42.1"H, LV:79"L X 39.8"W X 42.1"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Nailheads&lt;br&gt;
+- Drop-Down Table w/ Cup Holders in Sofa&lt;br&gt;
+- Console w/ Cup Holders in Loveseat&lt;br&gt;
+- USB &amp;amp; Power Outlet Included items and dimensions:&lt;br&gt;
+- Manual Sofa w/ Drop Down Table w/ Usb Charging (Metal Cup): color: Brown; dimensions: 85.8" W x 39.75"D x 42.1" H; feature: Transitional&lt;br&gt;
+- Manual Loveseat w/ Console w/ Glider w/ Usb Charging (Metal Cup Holder and Plastic Storage Box): color: Brown; dimensions: 79" W x 39.75"D x 42.1" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Contemporary.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 469.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -19512,22 +19512,22 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TILDE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Chenille, Leatherette, Solid Wood, and finished in Brown or Dark Walnut tones for a clean, cohesive look.
-Features
-- Traditional
-- Brown or Dark Walnut
-- Loose Pillow Back
-- Reversible Box Cushion
-- Brown Welting
-- Rolled Arms With Wood Trim
-- Bun Feet
-- Pillows Included Included items and dimensions:
-- Sofa: color: Brown or Dark Walnut; dimensions: 94" L x 37" W x 41" H; feature: Traditional
-- Loveseat: color: Brown or Dark Walnut; dimensions: 73" L x 37" W x 41" H; feature: Traditional
-Materials: Chenille, Leatherette, Solid Wood.
-Color: Brown or Dark Walnut
-Weight: 275 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TILDE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Chenille, Leatherette, Solid Wood, and finished in Brown or Dark Walnut tones for a clean, cohesive look.&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Brown or Dark Walnut&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Reversible Box Cushion&lt;br&gt;
+- Brown Welting&lt;br&gt;
+- Rolled Arms With Wood Trim&lt;br&gt;
+- Bun Feet&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Dark Walnut; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Brown or Dark Walnut; dimensions: 73" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown or Dark Walnut&lt;br&gt;
+Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -19639,23 +19639,23 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ULVERY Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Boucle, Leatherette, Solid Wood and finished in Beige or Brown tones for a clean, cohesive look.
-Product Dimensions: Sofa: 91"L X 38"W X 38"H (SEAT HT: 19", SEAT DP: 20")
-Features
-- Beige or Brown
-- Contrasting Welt Trim
-- Reversible Back Pillows and Seat Cushions
-- Wooden Legs
-- Bolt-on Removable Arms for Easy Door Access
-- Basketweave Leatherette
-- Padded Arms
-- Reversible Accent Pillows Included items and dimensions:
-- Sofa: color: Beige or Brown; dimensions: 91" W x 38"D x 38" H (SEAT HT: 19", SEAT DP: 20"); feature: Transitional
-- Love Seat: color: Beige or Brown; dimensions: 81" W x 38"D x 38" H (SEAT HT: 19", SEAT DP: 20"); feature: Transitional
-Materials: Boucle, Leatherette, Solid Wood.
-Color: Beige or Brown
-Weight: 285 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ULVERY Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Boucle, Leatherette, Solid Wood and finished in Beige or Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 91"L X 38"W X 38"H (SEAT HT: 19", SEAT DP: 20")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Beige or Brown&lt;br&gt;
+- Contrasting Welt Trim&lt;br&gt;
+- Reversible Back Pillows and Seat Cushions&lt;br&gt;
+- Wooden Legs&lt;br&gt;
+- Bolt-on Removable Arms for Easy Door Access&lt;br&gt;
+- Basketweave Leatherette&lt;br&gt;
+- Padded Arms&lt;br&gt;
+- Reversible Accent Pillows Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Brown; dimensions: 91" W x 38"D x 38" H (SEAT HT: 19", SEAT DP: 20"); feature: Transitional&lt;br&gt;
+- Love Seat: color: Beige or Brown; dimensions: 81" W x 38"D x 38" H (SEAT HT: 19", SEAT DP: 20"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Leatherette, Solid Wood.&lt;br&gt;
+Color: Beige or Brown&lt;br&gt;
+Weight: 285 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VALDOSTA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces.
-Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 25.5") Included items and dimensions:
-- Sofa: color: Beige or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam
-- Loveseat: color: Beige or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam
-Weight: 344 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VALDOSTA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 25.5") Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam&lt;br&gt;
+- Loveseat: color: Beige or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam&lt;br&gt;
+Weight: 344 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="18" t="inlineStr">
@@ -19880,12 +19880,12 @@
       </c>
       <c r="G148" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VALDOSTA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room.
-Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 26") Included items and dimensions:
-- Sofa: color: Black or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam
-- Loveseat: color: Black or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam
-Weight: 343 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VALDOSTA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 26") Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam&lt;br&gt;
+- Loveseat: color: Black or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam&lt;br&gt;
+Weight: 343 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="18" t="inlineStr">
@@ -19995,23 +19995,23 @@
       </c>
       <c r="G149" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERACRUZ Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in Dark Cherry or Beige tones to suit a range of interiors.
-Product Dimensions: Sofa: 89.75"L X 38"W X 45"H
-Features
-- Traditional
-- Dark Cherry or Beige
-- Button Tufted Back
-- Carved Details
-- Jacquard Pattern Box Seat Cushion w/ Welt
-- Rolled Arms
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Dark Cherry or Beige; dimensions: 90" W x 38"D x 44.5" H; feature: Traditional
-- Loveseat: color: Dark Cherry or Beige; dimensions: 69.5" W x 38"D x 44.5" H; feature: Traditional
-Materials: Fabric, Solid Wood.
-Color: Dark Cherry or Beige
-Weight: 350.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERACRUZ Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in Dark Cherry or Beige tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 89.75"L X 38"W X 45"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Beige&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Jacquard Pattern Box Seat Cushion w/ Welt&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Cherry or Beige; dimensions: 90" W x 38"D x 44.5" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Cherry or Beige; dimensions: 69.5" W x 38"D x 44.5" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Beige&lt;br&gt;
+Weight: 350.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="20" t="inlineStr">
@@ -20133,23 +20133,23 @@
       </c>
       <c r="G150" s="20" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERACRUZ Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, construction and Dark Cherry or Light Brown tones, it blends durability with visual warmth.
-Product Dimensions: Sofa: 89.75"L X 38"W X 45"H
-Features
-- Traditional
-- Dark Cherry or Light Brown
-- Button Tufted Back
-- Carved Details
-- Jacquard Pattern Box Seat Cushion w/ Welt
-- Rolled Arms
-- Nailhead Trim
-- Accent Pillows Included Included items and dimensions:
-- Sofa: color: Dark Cherry or Light Brown; dimensions: 90" W x 38"D x 44.5" H; feature: Traditional
-- Loveseat: color: Dark Cherry or Light Brown; dimensions: 69.5" W x 38"D x 44.5" H; feature: Traditional
-Materials: Fabric, Solid Wood.
-Color: Dark Cherry or Light Brown
-Weight: 350.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERACRUZ Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, construction and Dark Cherry or Light Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Sofa: 89.75"L X 38"W X 45"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Light Brown&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Jacquard Pattern Box Seat Cushion w/ Welt&lt;br&gt;
+- Rolled Arms&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Cherry or Light Brown; dimensions: 90" W x 38"D x 44.5" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Dark Cherry or Light Brown; dimensions: 69.5" W x 38"D x 44.5" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Light Brown&lt;br&gt;
+Weight: 350.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="20" t="inlineStr">
@@ -20271,22 +20271,22 @@
       </c>
       <c r="G151" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERDAL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black tones, the Boucle, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")
-Features
-- Tuxedo-inspired Design
-- Box Seat Cushion
-- Welt Trim
-- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)
-- High Density Foam w/ Pocket Coils
-- Kiln-dried Hardwood
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Black; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary
-- Loveseat: color: Black; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary
-Materials: Boucle, Solid Wood.
-Color: Black
-Weight: 256 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERDAL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black tones, the Boucle, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Tuxedo-inspired Design&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)&lt;br&gt;
+- High Density Foam w/ Pocket Coils&lt;br&gt;
+- Kiln-dried Hardwood&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Black; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Black; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="39" t="inlineStr">
@@ -20408,22 +20408,22 @@
       </c>
       <c r="G152" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERDAL Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Boucle, Solid Wood, and finished in Charcoal Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")
-Features
-- Tuxedo-inspired Design
-- Box Seat Cushion
-- Welt Trim
-- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)
-- High Density Foam w/ Pocket Coils
-- Kiln-dried Hardwood
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Charcoal Gray; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary
-- Loveseat: color: Charcoal Gray; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary
-Materials: Boucle, Solid Wood.
-Color: Charcoal Gray
-Weight: 256 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERDAL Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Boucle, Solid Wood, and finished in Charcoal Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Tuxedo-inspired Design&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)&lt;br&gt;
+- High Density Foam w/ Pocket Coils&lt;br&gt;
+- Kiln-dried Hardwood&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Charcoal Gray; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Charcoal Gray; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
+Color: Charcoal Gray&lt;br&gt;
+Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="39" t="inlineStr">
@@ -20545,22 +20545,22 @@
       </c>
       <c r="G153" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERDAL Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Boucle, Solid Wood, then finished in Off-White tones to suit a range of interiors.
-Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")
-Features
-- Tuxedo-inspired Design
-- Box Seat Cushion
-- Welt Trim
-- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)
-- High Density Foam w/ Pocket Coils
-- Kiln-dried Hardwood
-- Wooden Legs Included items and dimensions:
-- Sofa: color: Off-White; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary
-- Loveseat: color: Off-White; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary
-Materials: Boucle, Solid Wood.
-Color: Off-White
-Weight: 256 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERDAL Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Boucle, Solid Wood, then finished in Off-White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Tuxedo-inspired Design&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Exclusive BoucleFabric w/ Metallic Undertones (100% Polyester)&lt;br&gt;
+- High Density Foam w/ Pocket Coils&lt;br&gt;
+- Kiln-dried Hardwood&lt;br&gt;
+- Wooden Legs Included items and dimensions:&lt;br&gt;
+- Sofa: color: Off-White; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Off-White; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
+Color: Off-White&lt;br&gt;
+Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="39" t="inlineStr">
@@ -20681,21 +20681,21 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERDANTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Microfiber, Solid Wood construction and Emerald Green or Gold tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 91"L X 39"W X 38"H
-Features
-- Emerald Green or Gold
-- Nailhead Trim
-- Cushion Seating
-- Gold Finished Legs
-- High-Density Foam Cushions
-- Pillows Included Included items and dimensions:
-- Sofa: color: Emerald Green or Gold; dimensions: 93" L x 41" W x 40" H; feature: Transitional
-- Loveseat: color: Emerald Green or Gold; dimensions: 66" L x 41" W x 40" H; feature: Transitional
-Materials: Microfiber, Solid Wood.
-Color: Emerald Green or Gold
-Weight: 252 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERDANTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Microfiber, Solid Wood construction and Emerald Green or Gold tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 39"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Emerald Green or Gold&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Cushion Seating&lt;br&gt;
+- Gold Finished Legs&lt;br&gt;
+- High-Density Foam Cushions&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Emerald Green or Gold; dimensions: 93" L x 41" W x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Emerald Green or Gold; dimensions: 66" L x 41" W x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Microfiber, Solid Wood.&lt;br&gt;
+Color: Emerald Green or Gold&lt;br&gt;
+Weight: 252 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -20812,22 +20812,22 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VERNE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Bluish Gray tones, the Linen-like Fabric, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 89"L X 40"W X 38"H
-Features
-- Medium Density Foam
-- Wide Track Arms
-- T-Cushion Seats
-- Loose Back Pillows
-- Stain Resistant Fabric
-- Tapered Wooden Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Bluish Gray; dimensions: 89" L x 40" W x 38" H; feature: Transitional
-- Loveseat: color: Bluish Gray; dimensions: 64" L x 40" W x 38" H; feature: Transitional
-Materials: Linen-like Fabric, Solid Wood.
-Color: Bluish Gray
-Weight: 230 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VERNE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Bluish Gray tones, the Linen-like Fabric, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 89"L X 40"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Medium Density Foam&lt;br&gt;
+- Wide Track Arms&lt;br&gt;
+- T-Cushion Seats&lt;br&gt;
+- Loose Back Pillows&lt;br&gt;
+- Stain Resistant Fabric&lt;br&gt;
+- Tapered Wooden Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Bluish Gray; dimensions: 89" L x 40" W x 38" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Bluish Gray; dimensions: 64" L x 40" W x 38" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Bluish Gray&lt;br&gt;
+Weight: 230 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -20944,21 +20944,21 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VISCONTTI Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Velvet-like Fabric, Solid Wood and finished in Gold or Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 91"L X 40"W X 38"H
-Features
-- Traditional
-- Gold or Gray
-- T-Cushion Seating
-- Nailhead Trim
-- Pillows Included
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Gold or Gray; dimensions: 91" L x 40" W x 38" H; feature: Traditional
-- Loveseat: color: Gold or Gray; dimensions: 71" L x 40" W x 38" H; feature: Traditional
-Materials: Velvet-like Fabric, Solid Wood.
-Color: Gold or Gray
-Weight: 233 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VISCONTTI Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Built from Velvet-like Fabric, Solid Wood and finished in Gold or Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 40"W X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Gold or Gray&lt;br&gt;
+- T-Cushion Seating&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gold or Gray; dimensions: 91" L x 40" W x 38" H; feature: Traditional&lt;br&gt;
+- Loveseat: color: Gold or Gray; dimensions: 71" L x 40" W x 38" H; feature: Traditional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like Fabric, Solid Wood.&lt;br&gt;
+Color: Gold or Gray&lt;br&gt;
+Weight: 233 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -21075,23 +21075,23 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VIVIANA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Linen-like Fabric, Solid Wood, then finished in Gray or Black tones to suit a range of interiors.
-Product Dimensions: SOFA: 100"L X 39"W X 37"H
-Features
-- Gray or Black
-- Deep Tufted Back &amp; Arms
-- Oversized Arms
-- Individually Attached Nailheads
-- Pleated Front Seat Panels w/ Buttons
-- Pillows Included
-- Gray Fabric
-- US-Made (Incl. Foreign Materials) Included items and dimensions:
-- Sofa: color: Gray or Black; dimensions: 100" L x 39" W x 37" H; feature: Glam
-- Loveseat: color: Gray or Black; dimensions: 76" L x 39" W x 37" H; feature: Glam
-Materials: Linen-like Fabric, Solid Wood.
-Color: Gray or Black
-Weight: 290 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VIVIANA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Crafted with Linen-like Fabric, Solid Wood, then finished in Gray or Black tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 100"L X 39"W X 37"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Gray or Black&lt;br&gt;
+- Deep Tufted Back &amp;amp; Arms&lt;br&gt;
+- Oversized Arms&lt;br&gt;
+- Individually Attached Nailheads&lt;br&gt;
+- Pleated Front Seat Panels w/ Buttons&lt;br&gt;
+- Pillows Included&lt;br&gt;
+- Gray Fabric&lt;br&gt;
+- US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray or Black; dimensions: 100" L x 39" W x 37" H; feature: Glam&lt;br&gt;
+- Loveseat: color: Gray or Black; dimensions: 76" L x 39" W x 37" H; feature: Glam&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
+Color: Gray or Black&lt;br&gt;
+Weight: 290 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -21208,22 +21208,22 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WALDSTONE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Microfiber, Solid Wood, and finished in Navy tones for a clean, cohesive look.
-Product Dimensions: 92"L X 43"W X 41"H (SEAT HT: 23", SEAT DP: 23")
-Features
-- T-Seat Cushion
-- Round Arms
-- Super Plush Fabric
-- Reversible Zipper Cushions
-- Padded Arms
-- Wood Legs
-- Pillows Included Included items and dimensions:
-- Sofa: color: Navy; dimensions: 92" L x 43" W x 41" H (SEAT HT: 23", SEAT DP: 23"); feature: Transitional
-- Loveseat: color: Navy; dimensions: 69" L x 43" W x 41" H (SEAT HT: 23", SEAT DP: 23"); feature: Transitional
-Materials: Microfiber, Solid Wood.
-Color: Navy
-Weight: 282 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WALDSTONE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Microfiber, Solid Wood, and finished in Navy tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 92"L X 43"W X 41"H (SEAT HT: 23", SEAT DP: 23")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- T-Seat Cushion&lt;br&gt;
+- Round Arms&lt;br&gt;
+- Super Plush Fabric&lt;br&gt;
+- Reversible Zipper Cushions&lt;br&gt;
+- Padded Arms&lt;br&gt;
+- Wood Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- Sofa: color: Navy; dimensions: 92" L x 43" W x 41" H (SEAT HT: 23", SEAT DP: 23"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Navy; dimensions: 69" L x 43" W x 41" H (SEAT HT: 23", SEAT DP: 23"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Microfiber, Solid Wood.&lt;br&gt;
+Color: Navy&lt;br&gt;
+Weight: 282 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -21341,21 +21341,21 @@
       </c>
       <c r="G159" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WEST ACTION Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Chocolate tones, the Chenille, Solid Wood build keeps the look polished and practical.
-Product Dimensions: SOFA: 83"L X 36"W X 39"H (SEAT HT: 20", SEAT DP: 21")
-Features
-- Box Seat Cushion
-- Loose Pillow Back
-- Welt Trim
-- Track Arms
-- Tapered Block Legs
-- Accent Pillows Included Included items and dimensions:
-- ACTION Sofa: color: Chocolate; dimensions: 83" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary
-- ACTION Loveseat: color: Chocolate; dimensions: 61" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary
-Materials: Chenille, Solid Wood.
-Color: Chocolate
-Weight: 202 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WEST ACTION Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Chocolate tones, the Chenille, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 83"L X 36"W X 39"H (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Tapered Block Legs&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- ACTION Sofa: color: Chocolate; dimensions: 83" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;br&gt;
+- ACTION Loveseat: color: Chocolate; dimensions: 61" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Chocolate&lt;br&gt;
+Weight: 202 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="45" t="inlineStr">
@@ -21477,21 +21477,21 @@
       </c>
       <c r="G160" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WEST ACTION Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood and finished in Beige tones for a clean, cohesive look.
-Product Dimensions: SOFA: 83"L X 36"W X 39"H (SEAT HT: 20", SEAT DP: 21")
-Features
-- Box Seat Cushion
-- Loose Pillow Back
-- Welt Trim
-- Track Arms
-- Tapered Block Legs
-- Accent Pillows Included Included items and dimensions:
-- ACTION Sofa: color: Beige; dimensions: 83" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary
-- ACTION Loveseat: color: Beige; dimensions: 61" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary
-Materials: Chenille, Solid Wood.
-Color: Beige
-Weight: 202 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WEST ACTION Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 83"L X 36"W X 39"H (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Box Seat Cushion&lt;br&gt;
+- Loose Pillow Back&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Tapered Block Legs&lt;br&gt;
+- Accent Pillows Included Included items and dimensions:&lt;br&gt;
+- ACTION Sofa: color: Beige; dimensions: 83" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;br&gt;
+- ACTION Loveseat: color: Beige; dimensions: 61" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 202 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" s="45" t="inlineStr">
@@ -21612,22 +21612,22 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WEST BROMPTON Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Velvet-like Fabric, Foam, Solid Wood, then finished in Navy or Yellow tones to suit a range of interiors.
-Product Dimensions: SOFA: 91"L X 40"W X 38"H (SEAT HT: 20.5", SEAT DP: 22")
-Features
-- Navy or Yellow
-- Bench Seat Cushion
-- Loose Pillow Backs
-- Track Arms
-- Welt Trim
-- Tapered Wooden Legs
-- Pillows Included Included items and dimensions:
-- BROMPTON Sofa: color: Navy or Yellow; dimensions: 91" L x 40" W x 38" H (SEAT HT: 20.5", SEAT DP: 22"); feature: Transitional
-- BROMPTON Loveseat: color: Navy or Yellow; dimensions: 65" L x 40" W x 38" H (SEAT HT: 20.5", SEAT DP: 22"); feature: Transitional
-Materials: Velvet-like Fabric, Foam, Solid Wood.
-Color: Navy or Yellow
-Weight: 260 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WEST BROMPTON Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Velvet-like Fabric, Foam, Solid Wood, then finished in Navy or Yellow tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 91"L X 40"W X 38"H (SEAT HT: 20.5", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Navy or Yellow&lt;br&gt;
+- Bench Seat Cushion&lt;br&gt;
+- Loose Pillow Backs&lt;br&gt;
+- Track Arms&lt;br&gt;
+- Welt Trim&lt;br&gt;
+- Tapered Wooden Legs&lt;br&gt;
+- Pillows Included Included items and dimensions:&lt;br&gt;
+- BROMPTON Sofa: color: Navy or Yellow; dimensions: 91" L x 40" W x 38" H (SEAT HT: 20.5", SEAT DP: 22"); feature: Transitional&lt;br&gt;
+- BROMPTON Loveseat: color: Navy or Yellow; dimensions: 65" L x 40" W x 38" H (SEAT HT: 20.5", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like Fabric, Foam, Solid Wood.&lt;br&gt;
+Color: Navy or Yellow&lt;br&gt;
+Weight: 260 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -21744,21 +21744,21 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-YUCATAN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, then finished in Dark Cherry or Beige tones to suit a range of interiors.
-Product Dimensions: Sofa: 88"L X 37.5"W X 47.5"H
-Features
-- Traditional
-- Dark Cherry or Beige
-- Button Tufted Back
-- Carved Details
-- Bench Seat Jacquard Cushion w/ Welt
-- Rolled Arms w/ Nailhead Trim
-- Edge Bracket Feet
-- Accent Pillows Included
-Materials: Fabric, Solid Wood.
-Color: Dark Cherry or Beige
-Weight: 357.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+YUCATAN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Fabric, Solid Wood, then finished in Dark Cherry or Beige tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 88"L X 37.5"W X 47.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Traditional&lt;br&gt;
+- Dark Cherry or Beige&lt;br&gt;
+- Button Tufted Back&lt;br&gt;
+- Carved Details&lt;br&gt;
+- Bench Seat Jacquard Cushion w/ Welt&lt;br&gt;
+- Rolled Arms w/ Nailhead Trim&lt;br&gt;
+- Edge Bracket Feet&lt;br&gt;
+- Accent Pillows Included&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Cherry or Beige&lt;br&gt;
+Weight: 357.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -21876,18 +21876,18 @@
       </c>
       <c r="G163" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AGATA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H
-Features
-- Drop-Down Table With Cup Holders on Sofa
-- Storage Console and Cupholders on Love Seat
-- Contrast Welt Included items and dimensions:
-- Sofa: color: Brown; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 79" W x 38.5"D x 41" H; feature: Transitional
-Materials: Leatherette, Solid Wood.
-Color: Brown
-Weight: 428.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AGATA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Drop-Down Table With Cup Holders on Sofa&lt;br&gt;
+- Storage Console and Cupholders on Love Seat&lt;br&gt;
+- Contrast Welt Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 79" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 428.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" s="41" t="inlineStr">
@@ -22009,17 +22009,17 @@
       </c>
       <c r="G164" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AGATA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, and finished in Dark Gray tones for a clean, cohesive look.
-Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H
-Features
-- Double Stitching
-- Plush Cushions
-- Recliners
-- Console w/ Cup Holders
-Materials: Leatherette, Solid Wood.
-Color: Dark Gray
-Weight: 430 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AGATA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, and finished in Dark Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Double Stitching&lt;br&gt;
+- Plush Cushions&lt;br&gt;
+- Recliners&lt;br&gt;
+- Console w/ Cup Holders&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 430 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" s="41" t="inlineStr">
@@ -22141,19 +22141,19 @@
       </c>
       <c r="G165" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AGATA Sofa and Loveseat and Chair offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, then finished in Brown tones to suit a range of interiors.
-Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H
-Features
-- Drop-Down Table With Cup Holders on Sofa
-- Storage Console and Cupholders on Love Seat
-- Contrast Welt Included items and dimensions:
-- Sofa: color: Brown; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 79" W x 38.5"D x 41" H; feature: Transitional
-- Glider Recliner: color: Brown; dimensions: 41.5" W x 38.5"D x 41" H; feature: Transitional
-Materials: Leatherette, Solid Wood.
-Color: Brown
-Weight: 535.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AGATA Sofa and Loveseat and Chair offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Drop-Down Table With Cup Holders on Sofa&lt;br&gt;
+- Storage Console and Cupholders on Love Seat&lt;br&gt;
+- Contrast Welt Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 79" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Glider Recliner: color: Brown; dimensions: 41.5" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 535.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H165" s="35" t="inlineStr">
@@ -22275,17 +22275,17 @@
       </c>
       <c r="G166" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AGATA Sofa and Loveseat and Chair creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, construction and Dark Gray tones, it blends durability with visual warmth.
-Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H
-Features
-- Double Stitching
-- Plush Cushions
-- Recliners
-- Console w/ Cup Holders
-Materials: Leatherette, Solid Wood.
-Color: Dark Gray
-Weight: 537.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AGATA Sofa and Loveseat and Chair creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, construction and Dark Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Double Stitching&lt;br&gt;
+- Plush Cushions&lt;br&gt;
+- Recliners&lt;br&gt;
+- Console w/ Cup Holders&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 537.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H166" s="35" t="inlineStr">
@@ -22407,20 +22407,20 @@
       </c>
       <c r="G167" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALTAMURA Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Real Italian Leather, Engineered Wood, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: SOFA: 80"L X 39"W X 39 1/4"H (SEAT HT: 20", SEAT DP: 21")
-Features
-- Power Recliners
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- S-Spring Suspension
-- Pillow Top Arm &amp; Accent Stitching
-- 100% Made in Italy
-- Fully Upholstered in Leather on all Sides
-Materials: Real Italian Leather, Engineered Wood.
-Color: Gray
-Weight: 149 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALTAMURA Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Real Italian Leather, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 80"L X 39"W X 39 1/4"H (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- S-Spring Suspension&lt;br&gt;
+- Pillow Top Arm &amp;amp; Accent Stitching&lt;br&gt;
+- 100% Made in Italy&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 149 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H167" s="37" t="inlineStr">
@@ -22542,20 +22542,20 @@
       </c>
       <c r="G168" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALTAMURA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Real Italian Leather, Engineered Wood, construction and Taupe tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 80"L X 39"W X 39 1/4"H (SEAT HT: 20", SEAT DP: 21")
-Features
-- Power Recliners
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- S-Spring Suspension
-- Pillow Top Arm &amp; Accent Stitching
-- 100% Made in Italy
-- Fully Upholstered in Leather on all Sides
-Materials: Real Italian Leather, Engineered Wood.
-Color: Taupe
-Weight: 149 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALTAMURA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Real Italian Leather, Engineered Wood, construction and Taupe tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 80"L X 39"W X 39 1/4"H (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- S-Spring Suspension&lt;br&gt;
+- Pillow Top Arm &amp;amp; Accent Stitching&lt;br&gt;
+- 100% Made in Italy&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 149 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H168" s="37" t="inlineStr">
@@ -22676,21 +22676,21 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AMIRAH Sofa and Glider Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Durable Heavy-Weight Fabric, Solid Wood, and finished in Dark Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 83"L X 39 1/2"W X 40 1/2"H
-Features
-- Channel Back &amp; Seat Design
-- Cup Holders
-- Drop-down Center Table
-- Reading Light
-- USB Charger &amp; Power Outlet
-- Lift-up Armrest Storage Included items and dimensions:
-- Sofa: color: Dark Gray; dimensions: 83" L x 39 1 or 2" W x 40 1 or 2" H; feature: Transitional
-- Glider Loveseat: color: Dark Gray; dimensions: 74" L x 39 1 or 2" W x 40 1 or 2" H; feature: Transitional
-Materials: Durable Heavy-Weight Fabric, Solid Wood.
-Color: Dark Gray
-Weight: 504.42 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AMIRAH Sofa and Glider Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Durable Heavy-Weight Fabric, Solid Wood, and finished in Dark Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 83"L X 39 1/2"W X 40 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Channel Back &amp;amp; Seat Design&lt;br&gt;
+- Cup Holders&lt;br&gt;
+- Drop-down Center Table&lt;br&gt;
+- Reading Light&lt;br&gt;
+- USB Charger &amp;amp; Power Outlet&lt;br&gt;
+- Lift-up Armrest Storage Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Gray; dimensions: 83" L x 39 1 or 2" W x 40 1 or 2" H; feature: Transitional&lt;br&gt;
+- Glider Loveseat: color: Dark Gray; dimensions: 74" L x 39 1 or 2" W x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Durable Heavy-Weight Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 504.42 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -22807,20 +22807,20 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTENOR Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Top Grain Leather Match, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 86"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Pillow Top Arms
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Cornerblocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Brown; dimensions: 86" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Brown
-Weight: 270 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTENOR Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Top Grain Leather Match, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 86"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Cornerblocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Brown; dimensions: 86" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 270 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -22937,19 +22937,19 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTONIUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Foam, Metal, Wood, then finished in Gray tones to suit a range of interiors.
-Product Dimensions: Sofa: 87"L X 38.6"W X 40.9"H
-Features
-- Contour Arm
-- Wide Seats
-- 100% Polyester Fiber
-- Solid Wood Frame Included items and dimensions:
-- Sofa: color: Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Contemporary
-- Loveseat: color: Gray; dimensions: 78" W x 38.5"D x 41" H; feature: Contemporary
-Materials: Fabric, Foam, Metal, Wood.
-Color: Gray
-Weight: 444 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTONIUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Fabric, Foam, Metal, Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 87"L X 38.6"W X 40.9"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arm&lt;br&gt;
+- Wide Seats&lt;br&gt;
+- 100% Polyester Fiber&lt;br&gt;
+- Solid Wood Frame Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Contemporary&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 78" W x 38.5"D x 41" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Metal, Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 444 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -23067,21 +23067,21 @@
       </c>
       <c r="G172" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMIA Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Light Taupe tones, the Breathable Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 89"L X 40"W X 41"H (EXTENDED: 71"W)
-Features
-- Zero Gravity Power Recline Footrest &amp; Headrest
-- Extendable Footrest
-- Sofa Dropdown Table w/ Reading Light
-- Cupholders &amp; Wireless Charging
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Light Taupe; dimensions: 89" L x 40" W x 41" H (EXTENDED: 71" W); feature: Transitional
-Materials: Breathable Leatherette, Solid Wood.
-Color: Light Taupe
-Weight: 246 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMIA Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Light Taupe tones, the Breathable Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 89"L X 40"W X 41"H (EXTENDED: 71"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrest&lt;br&gt;
+- Sofa Dropdown Table w/ Reading Light&lt;br&gt;
+- Cupholders &amp;amp; Wireless Charging&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Light Taupe; dimensions: 89" L x 40" W x 41" H (EXTENDED: 71" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
+Color: Light Taupe&lt;br&gt;
+Weight: 246 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H172" s="39" t="inlineStr">
@@ -23203,21 +23203,21 @@
       </c>
       <c r="G173" s="39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARTEMIA Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Breathable Leatherette, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 89"L X 40"W X 41"H (EXTENDED: 71"W)
-Features
-- Zero Gravity Power Recline Footrest &amp; Headrest
-- Extendable Footrest
-- Sofa Dropdown Table w/ Reading Light
-- Cupholders &amp; Wireless Charging
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Gray; dimensions: 89" L x 40" W x 41" H (EXTENDED: 71" W); feature: Transitional
-Materials: Breathable Leatherette, Solid Wood.
-Color: Gray
-Weight: 246 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARTEMIA Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Breathable Leatherette, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 89"L X 40"W X 41"H (EXTENDED: 71"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrest&lt;br&gt;
+- Sofa Dropdown Table w/ Reading Light&lt;br&gt;
+- Cupholders &amp;amp; Wireless Charging&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Gray; dimensions: 89" L x 40" W x 41" H (EXTENDED: 71" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 246 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H173" s="39" t="inlineStr">
@@ -23339,22 +23339,22 @@
       </c>
       <c r="G174" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ASCONA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Breathable Leatherette, Metal, Solid Wood, construction and Black tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 88"L X 42"W X 31"H (EXTENDED: 63"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Extendable Footrest &amp; Articulating Headrest
-- Wide Pillow Top Arms &amp; Metal Legs
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Black; dimensions: 88" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary
-- Power Loveseat: color: Black; dimensions: 72" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary
-Materials: Breathable Leatherette, Metal, Solid Wood.
-Color: Black
-Weight: 249.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ASCONA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Breathable Leatherette, Metal, Solid Wood, construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 42"W X 31"H (EXTENDED: 63"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrest &amp;amp; Articulating Headrest&lt;br&gt;
+- Wide Pillow Top Arms &amp;amp; Metal Legs&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Black; dimensions: 88" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Black; dimensions: 72" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Metal, Solid Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 249.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H174" s="45" t="inlineStr">
@@ -23476,22 +23476,22 @@
       </c>
       <c r="G175" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ASCONA Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Light Taupe tones, the Breathable Leatherette, Metal, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 88"L X 42"W X 31"H (EXTENDED: 63"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Extendable Footrest &amp; Articulating Headrest
-- Wide Pillow Top Arms &amp; Metal Legs
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Light Taupe; dimensions: 88" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary
-- Power Loveseat: color: Light Taupe; dimensions: 72" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary
-Materials: Breathable Leatherette, Metal, Solid Wood.
-Color: Light Taupe
-Weight: 249.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ASCONA Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Light Taupe tones, the Breathable Leatherette, Metal, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 42"W X 31"H (EXTENDED: 63"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrest &amp;amp; Articulating Headrest&lt;br&gt;
+- Wide Pillow Top Arms &amp;amp; Metal Legs&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Light Taupe; dimensions: 88" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Light Taupe; dimensions: 72" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Metal, Solid Wood.&lt;br&gt;
+Color: Light Taupe&lt;br&gt;
+Weight: 249.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H175" s="45" t="inlineStr">
@@ -23612,20 +23612,20 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BALDERICO Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Real Italian Leather, Engineered Wood, then finished in Taupe tones to suit a range of interiors.
-Product Dimensions: SOFA: 86 1/2"L X 36 4/5"W X 37 1/2"H (SEAT HT: 18 3/4", SEAT DP: 21 1/2")
-Features
-- Power Recliners
-- High Density Foam Seat
-- Foam and Fiber-filled Back Pillow
-- Ring Suspension on Back and Seats
-- Wide Pillow Top Arm &amp; Accent Stitching
-- 100% Made in Italy
-- Fully Upholstered in Leather on all Sides
-Materials: Real Italian Leather, Engineered Wood.
-Color: Taupe
-Weight: 651.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BALDERICO Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Real Italian Leather, Engineered Wood, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 86 1/2"L X 36 4/5"W X 37 1/2"H (SEAT HT: 18 3/4", SEAT DP: 21 1/2")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Foam and Fiber-filled Back Pillow&lt;br&gt;
+- Ring Suspension on Back and Seats&lt;br&gt;
+- Wide Pillow Top Arm &amp;amp; Accent Stitching&lt;br&gt;
+- 100% Made in Italy&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 651.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -23742,16 +23742,16 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COSIMO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Mocha tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 88"L X 40"W X 40"H
-Features
-- Pillow Top Arms Included items and dimensions:
-- Sofa: color: Mocha; dimensions: 88" W x 40"D x 40" H; feature: Transitional
-- Loveseat: color: Mocha; dimensions: 78" W x 40"D x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Mocha
-Weight: 390.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COSIMO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Mocha tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 40"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Mocha; dimensions: 88" W x 40"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Mocha; dimensions: 78" W x 40"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Mocha&lt;br&gt;
+Weight: 390.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -23868,17 +23868,17 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-COSIMO Sofa and Loveseat and Chair brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Mocha tones, the Chenille, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 88"L X 40"W X 40"H
-Features
-- Pillow Top Arms Included items and dimensions:
-- Sofa: color: Mocha; dimensions: 88" W x 40"D x 40" H; feature: Transitional
-- Loveseat: color: Mocha; dimensions: 78" W x 40"D x 40" H; feature: Transitional
-- Recliner: color: Mocha; dimensions: 42" W x 40"D x 40" H; feature: Transitional
-Materials: Chenille, Solid Wood.
-Color: Mocha
-Weight: 495 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+COSIMO Sofa and Loveseat and Chair brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Mocha tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 40"W X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Mocha; dimensions: 88" W x 40"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Mocha; dimensions: 78" W x 40"D x 40" H; feature: Transitional&lt;br&gt;
+- Recliner: color: Mocha; dimensions: 42" W x 40"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+Color: Mocha&lt;br&gt;
+Weight: 495 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -23992,13 +23992,13 @@
       </c>
       <c r="G179" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DEMETRIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor.
-Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:
-- Laf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H
-- Raf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H
-- Armless Chair Texas Slate: dimensions: 24" W x 39"D x 40" H
-Weight: 232 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DEMETRIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:&lt;br&gt;
+- Laf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
+- Raf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
+- Armless Chair Texas Slate: dimensions: 24" W x 39"D x 40" H&lt;br&gt;
+Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" s="41" t="inlineStr">
@@ -24104,13 +24104,13 @@
       </c>
       <c r="G180" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DEMETRIUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces.
-Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:
-- Laf Power Recliner Texas Granite: dimensions: 33" W x 39"D x 40" H
-- Raf Power Recliner Texas Granite: dimensions: 33" W x 39"D x 40" H
-- Armless Chair Texas Granite: dimensions: 24" W x 39"D x 40" H
-Weight: 232 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DEMETRIUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:&lt;br&gt;
+- Laf Power Recliner Texas Granite: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
+- Raf Power Recliner Texas Granite: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
+- Armless Chair Texas Granite: dimensions: 24" W x 39"D x 40" H&lt;br&gt;
+Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" s="41" t="inlineStr">
@@ -24219,19 +24219,19 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-EZEKIUS Manual Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Leatherette, Foam, Fiber, Other, then finished in Brown tones to suit a range of interiors.
-Product Dimensions: 81.5"W X 39"D X 38"H (SEAT HT: 20.5", SEAT DP: 30.5 - 66.5")
-Features
-- Recliner
-- Drop-Down Table w/ USB-A &amp; USB-C Chargers
-- Storage Console w/ Stainless Steel Cup Holders
-- Pillow Top Arms Included items and dimensions:
-- Sofa: color: Brown; dimensions: 81.5" W x 39"D x 38" H (SEAT HT: 20.5", SEAT DP: 30.5 - 66.5"); feature: Transitional
-- Loveseat: color: Brown; dimensions: 70" W x 39"D x 38" H (SEAT HT: 20.5", SEAT DP: 30.5 - 66.5"); feature: Transitional
-Materials: Leatherette, Foam, Fiber, Other.
-Color: Brown
-Weight: 394.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+EZEKIUS Manual Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Leatherette, Foam, Fiber, Other, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 81.5"W X 39"D X 38"H (SEAT HT: 20.5", SEAT DP: 30.5 - 66.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Recliner&lt;br&gt;
+- Drop-Down Table w/ USB-A &amp;amp; USB-C Chargers&lt;br&gt;
+- Storage Console w/ Stainless Steel Cup Holders&lt;br&gt;
+- Pillow Top Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 81.5" W x 39"D x 38" H (SEAT HT: 20.5", SEAT DP: 30.5 - 66.5"); feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 70" W x 39"D x 38" H (SEAT HT: 20.5", SEAT DP: 30.5 - 66.5"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Foam, Fiber, Other.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 394.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -24348,22 +24348,22 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FLORINE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Leatherette, construction and Light Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 87 1/4"L X 38 3/4"W X 41 7/8"H, RECLINED: 87 1/4"L X 64 1/2"W X 33 3/4"H (SEAT HT: 20 1/4", SEAT DP: 22")
-Features
-- Power Recliner on Sofa and Loveseat
-- USB Port
-- Stainless Steel Cup Holders on Loveseat
-- Storage Console on Loveseat
-- Power Glider Recliner on Chair
-- Nailhead Trim
-- Removable Tray and Tablet Holder Included items and dimensions:
-- Power Sofa: color: Light Gray; dimensions: 87 1 or 4" L x 38 3 or 4" W x 41 7 or 8" H, RECLINED: 87 1 or 4" L x 64 1 or 2" W x 33 3 or 4" H (SEAT HT: 20 1 or 4", SEAT DP: 22"); feature: Transitional
-- Power Loveseat: color: Light Gray; dimensions: 76 5 or 8" L x 38 3 or 4" W x 41 7 or 8" H, RECLINED: 76 5 or 8" L x 64 1 or 2" W x 33 3 or 4" H (SEAT HT: 20 1 or 4", SEAT DP: 22"); feature: Transitional
-Materials: Leatherette.
-Color: Light Gray
-Weight: 447.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FLORINE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Leatherette, construction and Light Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 87 1/4"L X 38 3/4"W X 41 7/8"H, RECLINED: 87 1/4"L X 64 1/2"W X 33 3/4"H (SEAT HT: 20 1/4", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliner on Sofa and Loveseat&lt;br&gt;
+- USB Port&lt;br&gt;
+- Stainless Steel Cup Holders on Loveseat&lt;br&gt;
+- Storage Console on Loveseat&lt;br&gt;
+- Power Glider Recliner on Chair&lt;br&gt;
+- Nailhead Trim&lt;br&gt;
+- Removable Tray and Tablet Holder Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Light Gray; dimensions: 87 1 or 4" L x 38 3 or 4" W x 41 7 or 8" H, RECLINED: 87 1 or 4" L x 64 1 or 2" W x 33 3 or 4" H (SEAT HT: 20 1 or 4", SEAT DP: 22"); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Light Gray; dimensions: 76 5 or 8" L x 38 3 or 4" W x 41 7 or 8" H, RECLINED: 76 5 or 8" L x 64 1 or 2" W x 33 3 or 4" H (SEAT HT: 20 1 or 4", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 447.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -24480,19 +24480,19 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GIRALDUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, and finished in Beige tones for a clean, cohesive look.
-Product Dimensions: Sofa: 88.2"L X 37.8"W X 40.2"H
-Features
-- Contour Arm
-- Wide Seats
-- 100% Polyester Fiber
-- Solid Wood Frame Included items and dimensions:
-- Sofa: color: Beige; dimensions: 88" W x 38"D x 40" H; feature: Transitional
-- Loveseat: color: Beige; dimensions: 78.5" W x 38"D x 40" H; feature: Transitional
-Materials: Fabric.
-Color: Beige
-Weight: 180.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GIRALDUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 88.2"L X 37.8"W X 40.2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arm&lt;br&gt;
+- Wide Seats&lt;br&gt;
+- 100% Polyester Fiber&lt;br&gt;
+- Solid Wood Frame Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 88" W x 38"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 78.5" W x 38"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 180.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -24610,20 +24610,20 @@
       </c>
       <c r="G184" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GORGIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather Match, Solid Wood, then finished in Espresso tones to suit a range of interiors.
-Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 67 1/2"W)
-Features
-- Power Recline Footrest
-- Manual Recline Armless Chair
-- Pillow Top Arms
-- Wallhugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Cornerblocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Espresso
-Weight: 232 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GORGIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather Match, Solid Wood, then finished in Espresso tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest&lt;br&gt;
+- Manual Recline Armless Chair&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Wallhugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Cornerblocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Espresso&lt;br&gt;
+Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" s="45" t="inlineStr">
@@ -24745,20 +24745,20 @@
       </c>
       <c r="G185" s="45" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GORGIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Top Grain Leather Match, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.
-Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 65 1/2"W)
-Features
-- Power Recline Footrest
-- Manual Recline Armless Chair
-- Pillow Top Arms
-- Wallhugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Cornerblocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Light Gray
-Weight: 232 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GORGIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Top Grain Leather Match, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 65 1/2"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest&lt;br&gt;
+- Manual Recline Armless Chair&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Wallhugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Cornerblocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H185" s="45" t="inlineStr">
@@ -24879,20 +24879,20 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GRANUCCI Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Real Italian Leather, Engineered Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: Sofa: 74 3/4"L X 39 3/4"W X 41"H, LV: 63"L X 39 3/4"W X 41"H
-Features
-- Power Recliners
-- High Density Foam Seat
-- Tight Back Cushion w/ Horizontal Tufting
-- Flared Arms
-- Hidden Recliner Controls
-- Fully Upholstered in Leather on all Sides
-- Made in Italy
-Materials: Real Italian Leather, Engineered Wood.
-Color: Gray
-Weight: 487.14 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GRANUCCI Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Real Italian Leather, Engineered Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 74 3/4"L X 39 3/4"W X 41"H, LV: 63"L X 39 3/4"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- High Density Foam Seat&lt;br&gt;
+- Tight Back Cushion w/ Horizontal Tufting&lt;br&gt;
+- Flared Arms&lt;br&gt;
+- Hidden Recliner Controls&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;br&gt;
+- Made in Italy&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 487.14 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -25010,19 +25010,19 @@
       </c>
       <c r="G187" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JACOBUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Top Grain Leather and finished in Beige tones for a clean, cohesive look.
-Product Dimensions: Sofa: 41.3"L X 38.6"W X 40.9"H
-Features
-- Contour Arm
-- Wide Seats
-- 100% Polyester Fiber
-- Solid Wood Frame Included items and dimensions:
-- Sofa: color: Beige; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional
-- Loveseat: color: Beige; dimensions: 78" W x 38.5"D x 41" H; feature: Transitional
-Materials: Top Grain Leather.
-Color: Beige
-Weight: 443.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JACOBUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Top Grain Leather and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 41.3"L X 38.6"W X 40.9"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arm&lt;br&gt;
+- Wide Seats&lt;br&gt;
+- 100% Polyester Fiber&lt;br&gt;
+- Solid Wood Frame Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 78" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 443.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H187" s="28" t="inlineStr">
@@ -25144,19 +25144,19 @@
       </c>
       <c r="G188" s="28" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JACOBUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather, then finished in Light Gray tones to suit a range of interiors.
-Product Dimensions: Sofa: 38.6"L X 38.6"W X 40.9"H
-Features
-- Contour Arm
-- Wide Seats
-- 100% Polyester Fiber
-- Solid Wood Frame Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional
-- Loveseat: color: Light Gray; dimensions: 78" W x 38.5"D x 41" H; feature: Transitional
-Materials: Top Grain Leather.
-Color: Light Gray
-Weight: 443.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JACOBUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather, then finished in Light Gray tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: Sofa: 38.6"L X 38.6"W X 40.9"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arm&lt;br&gt;
+- Wide Seats&lt;br&gt;
+- 100% Polyester Fiber&lt;br&gt;
+- Solid Wood Frame Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Light Gray; dimensions: 78" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 443.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H188" s="28" t="inlineStr">
@@ -25277,19 +25277,19 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LEOLINUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather, then finished in Brown tones to suit a range of interiors.
-Product Dimensions: SOFA: 88"W X 38"D X 40"H
-Features
-- Contour Arm
-- Wide Seats
-- 100% Polyester Fiber
-- Solid Wood Frame Included items and dimensions:
-- Sofa: color: Brown; dimensions: 88" W x 38"D x 40" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 78.5" W x 38"D x 40" H; feature: Transitional
-Materials: Top Grain Leather.
-Color: Brown
-Weight: 396.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LEOLINUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 88"W X 38"D X 40"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arm&lt;br&gt;
+- Wide Seats&lt;br&gt;
+- 100% Polyester Fiber&lt;br&gt;
+- Solid Wood Frame Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 88" W x 38"D x 40" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 78.5" W x 38"D x 40" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 396.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -25406,16 +25406,16 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LETHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Breathable Leather, Solid Wood, construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: 81.5"L X 37.5"W X 39"H
-Features
-- Pillow Top Arms Included items and dimensions:
-- Sofa: color: Gray; dimensions: 81.5" W x 37.5"D x 39" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 60" W x 37.5"D x 39" H; feature: Transitional
-Materials: Breathable Leather, Solid Wood.
-Color: Gray
-Weight: 348.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LETHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Breathable Leather, Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 81.5"L X 37.5"W X 39"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 81.5" W x 37.5"D x 39" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 60" W x 37.5"D x 39" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leather, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 348.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -25532,19 +25532,19 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MATTHIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Fabric construction and Gray tones, it blends durability with visual warmth.
-Product Dimensions: Sofa: 47.2"L X 47.2"W X 40.2"H
-Features
-- Modern Scroll Arm w/ Welt Trim
-- Wide Seats
-- 100% Polyester Fiber
-- Solid Wood Frame Included items and dimensions:
-- Sofa: color: Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 64" W x 38.5"D x 41" H; feature: Transitional
-Materials: Fabric.
-Color: Gray
-Weight: 36 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MATTHIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Fabric construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: Sofa: 47.2"L X 47.2"W X 40.2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modern Scroll Arm w/ Welt Trim&lt;br&gt;
+- Wide Seats&lt;br&gt;
+- 100% Polyester Fiber&lt;br&gt;
+- Solid Wood Frame Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 64" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -25662,22 +25662,22 @@
       </c>
       <c r="G192" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORCOTE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Boucle Fabric, Solid Wood, construction and Beige tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21")
-Features
-- Power Recliners
-- S-Spring Seat and Webbing Back Suspension
-- Pillow Top Arms
-- Accent Stitching
-- Contoured Seat Cushion
-- 100% Polyester
-- High Density Foam Pocketed Coil Included items and dimensions:
-- Power Sofa: color: Beige; dimensions: 90" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional
-- Power Loveseat: color: Beige; dimensions: 67" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional
-Materials: Boucle Fabric, Solid Wood.
-Color: Beige
-Weight: 199 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORCOTE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Boucle Fabric, Solid Wood, construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- S-Spring Seat and Webbing Back Suspension&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Accent Stitching&lt;br&gt;
+- Contoured Seat Cushion&lt;br&gt;
+- 100% Polyester&lt;br&gt;
+- High Density Foam Pocketed Coil Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Beige; dimensions: 90" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Beige; dimensions: 67" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 199 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" s="18" t="inlineStr">
@@ -25799,19 +25799,19 @@
       </c>
       <c r="G193" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORCOTE Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gray tones, the Boucle Fabric, Solid Wood, Engineered Wood, Other build keeps the look polished and practical.
-Product Dimensions: 82.5"W X 39"D X 38"H
-Features
-- Pillow Top Arms
-- Console with Stainless Steel Cup Holders on Loveseat
-- USB-A &amp; USB-C Charger
-- Envelope Arms Included items and dimensions:
-- Power Sofa: color: Gray; dimensions: 82.5" W x 39"D x 38" H; feature: Contemporary
-- Power Loveseat w/ Console: color: Gray; dimensions: 72.5" W x 39"D x 38" H; feature: Contemporary
-Materials: Boucle Fabric, Solid Wood, Engineered Wood, Other.
-Color: Gray
-Weight: 408.41 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORCOTE Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gray tones, the Boucle Fabric, Solid Wood, Engineered Wood, Other build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 82.5"W X 39"D X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Console with Stainless Steel Cup Holders on Loveseat&lt;br&gt;
+- USB-A &amp;amp; USB-C Charger&lt;br&gt;
+- Envelope Arms Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Gray; dimensions: 82.5" W x 39"D x 38" H; feature: Contemporary&lt;br&gt;
+- Power Loveseat w/ Console: color: Gray; dimensions: 72.5" W x 39"D x 38" H; feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood, Engineered Wood, Other.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 408.41 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H193" s="18" t="inlineStr">
@@ -25933,22 +25933,22 @@
       </c>
       <c r="G194" s="18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORCOTE Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Boucle Fabric, Solid Wood, and finished in Light Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21")
-Features
-- Power Recliners
-- S-Spring Seat and Webbing Back Suspension
-- Pillow Top Arms
-- Accent Stitching
-- Contoured Seat Cushion
-- 100% Polyester
-- High Density Foam Pocketed Coil Included items and dimensions:
-- Power Sofa: color: Light Gray; dimensions: 90" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional
-- Power Loveseat: color: Light Gray; dimensions: 67" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional
-Materials: Boucle Fabric, Solid Wood.
-Color: Light Gray
-Weight: 199 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORCOTE Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Boucle Fabric, Solid Wood, and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- S-Spring Seat and Webbing Back Suspension&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Accent Stitching&lt;br&gt;
+- Contoured Seat Cushion&lt;br&gt;
+- 100% Polyester&lt;br&gt;
+- High Density Foam Pocketed Coil Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Light Gray; dimensions: 90" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Light Gray; dimensions: 67" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 199 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H194" s="18" t="inlineStr">
@@ -26069,19 +26069,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ONORIA Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood and finished in Brown tones for a clean, cohesive look.
-Product Dimensions: 88"W X 38"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
-Features
-- Recliners
-- Pillow Top Arms w/ Flange Trim
-- 2.0 LB High Density Foam w/ Pocketed Coil Spring
-- FSC Certified Included items and dimensions:
-- Sofa: color: Brown; dimensions: 88" W x 38"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Contemporary
-- Loveseat: color: Brown; dimensions: 64" W x 38"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Contemporary
-Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood.
-Color: Brown
-Weight: 385.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ONORIA Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood and finished in Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 88"W X 38"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Recliners&lt;br&gt;
+- Pillow Top Arms w/ Flange Trim&lt;br&gt;
+- 2.0 LB High Density Foam w/ Pocketed Coil Spring&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 88" W x 38"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Contemporary&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 64" W x 38"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 385.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -26198,17 +26198,17 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OSIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Leatherette, Solid Wood, construction and Brown tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 83.88"L X 37"W X 41.75"H
-Features
-- Diamond Stitching
-- Pillow Top Arms Included items and dimensions:
-- Sofa: color: Brown; dimensions: 84" W x 37"D x 41.5" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 72.5" W x 37"D x 41.5" H; feature: Transitional
-Materials: Leatherette, Solid Wood.
-Color: Brown
-Weight: 414.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OSIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Leatherette, Solid Wood, construction and Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 83.88"L X 37"W X 41.75"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Diamond Stitching&lt;br&gt;
+- Pillow Top Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 84" W x 37"D x 41.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 72.5" W x 37"D x 41.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 414.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -26325,18 +26325,18 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OSIAS Sofa and Loveseat and Chair brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 83.88"L X 37"W X 41.75"H
-Features
-- Diamond Stitching
-- Pillow Top Arms Included items and dimensions:
-- Sofa: color: Brown; dimensions: 84" W x 37"D x 41.5" H; feature: Transitional
-- Loveseat: color: Brown; dimensions: 72.5" W x 37"D x 41.5" H; feature: Transitional
-- Glider Recliner: color: Brown; dimensions: 36.5" W x 37"D x 41.5" H; feature: Transitional
-Materials: Leatherette, Solid Wood.
-Color: Brown
-Weight: 522.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OSIAS Sofa and Loveseat and Chair brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 83.88"L X 37"W X 41.75"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Diamond Stitching&lt;br&gt;
+- Pillow Top Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown; dimensions: 84" W x 37"D x 41.5" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Brown; dimensions: 72.5" W x 37"D x 41.5" H; feature: Transitional&lt;br&gt;
+- Glider Recliner: color: Brown; dimensions: 36.5" W x 37"D x 41.5" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 522.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -26454,21 +26454,21 @@
       </c>
       <c r="G198" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PHINEAS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Top Grain Leather Match, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Zero Gravity Power Recline Footrest &amp; Headrest
-- Extendable Footrests
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Gray; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-- Power Loveseat: color: Gray; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Gray
-Weight: 247 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PHINEAS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Top Grain Leather Match, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrests&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Gray; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Gray; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 247 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H198" s="24" t="inlineStr">
@@ -26590,21 +26590,21 @@
       </c>
       <c r="G199" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PHINEAS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Top Grain Leather Match, Solid Wood, then finished in Pale Blue tones to suit a range of interiors.
-Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Zero Gravity Power Recline Footrest &amp; Headrest
-- Extendable Footrests
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Pale Blue; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-- Power Loveseat: color: Pale Blue; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Pale Blue
-Weight: 247 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PHINEAS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Top Grain Leather Match, Solid Wood, then finished in Pale Blue tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrests&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Pale Blue; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Pale Blue; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Pale Blue&lt;br&gt;
+Weight: 247 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H199" s="24" t="inlineStr">
@@ -26726,21 +26726,21 @@
       </c>
       <c r="G200" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PHINEAS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Top Grain Leather Match, Solid Wood, construction and Beige tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Zero Gravity Power Recline Footrest &amp; Headrest
-- Extendable Footrests
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Beige; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-- Power Loveseat: color: Beige; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Beige
-Weight: 247 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PHINEAS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Top Grain Leather Match, Solid Wood, construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Extendable Footrests&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Beige; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Beige; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 247 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H200" s="24" t="inlineStr">
@@ -26861,18 +26861,18 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANDBACH Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Light Gray tones, the Fabric, Foam, Solid Wood, Engineered Wood build keeps the look polished and practical.
-Product Dimensions: 79.5"W X 39"D X 37.8"H (SEAT HT: 19", SEAT DP: 30 - 54")
-Features
-- Recliners
-- Console w/ 2 Cup Holders
-- Padded Track Arms Included items and dimensions:
-- Sofa: color: Light Gray; dimensions: 79.5" W x 39"D x 37.8" H (SEAT HT: 19", SEAT DP: 30 - 54"); feature: Contemporary
-- Loveseat w/ Console: color: Light Gray; dimensions: 68" W x 39"D x 38" H (SEAT HT: 19", SEAT DP: 30 - 54"); feature: Contemporary
-Materials: Fabric, Foam, Solid Wood, Engineered Wood.
-Color: Light Gray
-Weight: 354.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANDBACH Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Light Gray tones, the Fabric, Foam, Solid Wood, Engineered Wood build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 79.5"W X 39"D X 37.8"H (SEAT HT: 19", SEAT DP: 30 - 54")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Recliners&lt;br&gt;
+- Console w/ 2 Cup Holders&lt;br&gt;
+- Padded Track Arms Included items and dimensions:&lt;br&gt;
+- Sofa: color: Light Gray; dimensions: 79.5" W x 39"D x 37.8" H (SEAT HT: 19", SEAT DP: 30 - 54"); feature: Contemporary&lt;br&gt;
+- Loveseat w/ Console: color: Light Gray; dimensions: 68" W x 39"D x 38" H (SEAT HT: 19", SEAT DP: 30 - 54"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood, Engineered Wood.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 354.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -26990,18 +26990,18 @@
       </c>
       <c r="G202" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SCHLIEREN Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Foam, Other, then finished in Beige tones to suit a range of interiors.
-Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")
-Features
-- Contour Arms
-- USB-A &amp; USB-C Chargers
-- Flange Trim Included items and dimensions:
-- Power Sofa: color: Beige; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-- Power Loveseat: color: Beige; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-Materials: Leatherette, Foam, Other.
-Color: Beige
-Weight: 357.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Foam, Other, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arms&lt;br&gt;
+- USB-A &amp;amp; USB-C Chargers&lt;br&gt;
+- Flange Trim Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Beige; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Beige; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 357.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" s="30" t="inlineStr">
@@ -27123,18 +27123,18 @@
       </c>
       <c r="G203" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SCHLIEREN Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Leatherette, Foam, Other construction and Black tones, it blends durability with visual warmth.
-Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")
-Features
-- Contour Arms
-- USB-A &amp; USB-C Chargers
-- Flange Trim Included items and dimensions:
-- Power Sofa: color: Black; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-- Power Loveseat: color: Black; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-Materials: Leatherette, Foam, Other.
-Color: Black
-Weight: 346.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Leatherette, Foam, Other construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arms&lt;br&gt;
+- USB-A &amp;amp; USB-C Chargers&lt;br&gt;
+- Flange Trim Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Black; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Black; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 346.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" s="30" t="inlineStr">
@@ -27256,18 +27256,18 @@
       </c>
       <c r="G204" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SCHLIEREN Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Leatherette, Foam, Other build keeps the look polished and practical.
-Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")
-Features
-- Contour Arms
-- USB-A &amp; USB-C Chargers
-- Flange Trim Included items and dimensions:
-- Power Sofa: color: Gray; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-- Power Loveseat: color: Gray; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-Materials: Leatherette, Foam, Other.
-Color: Gray
-Weight: 374.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Leatherette, Foam, Other build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arms&lt;br&gt;
+- USB-A &amp;amp; USB-C Chargers&lt;br&gt;
+- Flange Trim Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Gray; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Gray; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 374.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" s="30" t="inlineStr">
@@ -27389,18 +27389,18 @@
       </c>
       <c r="G205" s="30" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SCHLIEREN Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leatherette, Foam, Other and finished in Light Brown tones for a clean, cohesive look.
-Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")
-Features
-- Contour Arms
-- USB-A &amp; USB-C Chargers
-- Flange Trim Included items and dimensions:
-- Power Sofa: color: Light Brown; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-- Power Loveseat: color: Light Brown; dimensions: 57"D x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary
-Materials: Leatherette, Foam, Other.
-Color: Light Brown
-Weight: 369.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leatherette, Foam, Other and finished in Light Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Contour Arms&lt;br&gt;
+- USB-A &amp;amp; USB-C Chargers&lt;br&gt;
+- Flange Trim Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Light Brown; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Light Brown; dimensions: 57"D x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
+Color: Light Brown&lt;br&gt;
+Weight: 369.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" s="30" t="inlineStr">
@@ -27522,22 +27522,22 @@
       </c>
       <c r="G206" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOTERIOS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Top Grain Leather Match, Solid Wood, then finished in Charcoal tones to suit a range of interiors.
-Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Contrast Stitching
-- High Density Foam Seat Cushions
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Charcoal; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-- Power Loveseat: color: Charcoal; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Charcoal
-Weight: 255 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOTERIOS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Top Grain Leather Match, Solid Wood, then finished in Charcoal tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Contrast Stitching&lt;br&gt;
+- High Density Foam Seat Cushions&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Charcoal; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Charcoal; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Charcoal&lt;br&gt;
+Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H206" s="41" t="inlineStr">
@@ -27659,22 +27659,22 @@
       </c>
       <c r="G207" s="41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOTERIOS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Top Grain Leather Match, Solid Wood, construction and Medium Brown tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Contrast Stitching
-- High Density Foam Seat Cushions
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Medium Brown; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-- Power Loveseat: color: Medium Brown; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-Materials: Top Grain Leather Match, Solid Wood.
-Color: Medium Brown
-Weight: 255 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOTERIOS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Top Grain Leather Match, Solid Wood, construction and Medium Brown tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Contrast Stitching&lt;br&gt;
+- High Density Foam Seat Cushions&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Medium Brown; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Medium Brown; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
+Color: Medium Brown&lt;br&gt;
+Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H207" s="41" t="inlineStr">
@@ -27796,22 +27796,22 @@
       </c>
       <c r="G208" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TERENTIUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension and finished in Caramel Brown tones for a clean, cohesive look.
-Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 19", SEAT DP: 22")
-Features
-- Power Recliner
-- 2" Wall Clearance
-- Flare w/ Welt Trim Arms
-- Storage Console w/ 2 Cup Holders on Loveseat
-- Single Power
-- 2.0 LB High Density Foam w/ Pocketed Coil Spring
-- FSC Certified Included items and dimensions:
-- Power Sofa: color: Caramel Brown; dimensions: 86" W x 35.5"D x 40.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Contemporary
-- Power Loveseat: color: Caramel Brown; dimensions: 62.5" W x 35.5"D x 40.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Contemporary
-Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension.
-Color: Caramel Brown
-Weight: 420.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TERENTIUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension and finished in Caramel Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 19", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliner&lt;br&gt;
+- 2" Wall Clearance&lt;br&gt;
+- Flare w/ Welt Trim Arms&lt;br&gt;
+- Storage Console w/ 2 Cup Holders on Loveseat&lt;br&gt;
+- Single Power&lt;br&gt;
+- 2.0 LB High Density Foam w/ Pocketed Coil Spring&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Caramel Brown; dimensions: 86" W x 35.5"D x 40.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Caramel Brown; dimensions: 62.5" W x 35.5"D x 40.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension.&lt;br&gt;
+Color: Caramel Brown&lt;br&gt;
+Weight: 420.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H208" s="16" t="inlineStr">
@@ -27937,22 +27937,22 @@
       </c>
       <c r="G209" s="16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TERENTIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension, then finished in Taupe tones to suit a range of interiors.
-Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 18.5", SEAT DP: 21 - 61")
-Features
-- Power Recliner
-- 2" Wall Clearance
-- Flare w/ Welt Trim Arms
-- Storage Console w/ 2 Cup Holders on Loveseat
-- Single Power
-- 2.0 LB High Density Foam w/ Pocketed Coil Spring
-- FSC Certified Included items and dimensions:
-- Power Sofa: color: Taupe; dimensions: 86" W x 35.5"D x 40.5" H (SEAT HT: 18.5", SEAT DP: 21 - 61"); feature: Contemporary
-- Power Loveseat: color: Taupe; dimensions: 62.5" W x 35.5"D x 40.5" H (SEAT HT: 18.5", SEAT DP: 21 - 61"); feature: Contemporary
-Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension.
-Color: Taupe
-Weight: 433.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TERENTIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 18.5", SEAT DP: 21 - 61")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliner&lt;br&gt;
+- 2" Wall Clearance&lt;br&gt;
+- Flare w/ Welt Trim Arms&lt;br&gt;
+- Storage Console w/ 2 Cup Holders on Loveseat&lt;br&gt;
+- Single Power&lt;br&gt;
+- 2.0 LB High Density Foam w/ Pocketed Coil Spring&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Taupe; dimensions: 86" W x 35.5"D x 40.5" H (SEAT HT: 18.5", SEAT DP: 21 - 61"); feature: Contemporary&lt;br&gt;
+- Power Loveseat: color: Taupe; dimensions: 62.5" W x 35.5"D x 40.5" H (SEAT HT: 18.5", SEAT DP: 21 - 61"); feature: Contemporary&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 433.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" s="16" t="inlineStr">
@@ -28068,14 +28068,14 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-THADDEA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor.
-Product Dimensions: 94"W X 44"D X 32"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:
-- Armless Chair: dimensions: 24" W x 44"D x 32" H
-- Laf Phr Recliner: dimensions: 35" W x 44"D x 32" H
-- Raf Phr Recliner: dimensions: 35" W x 44"D x 32" H
-- Marble Console w/ Drawer &amp; Wc: dimensions: 13" W x 44"D x 28" H
-Weight: 174 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+THADDEA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 94"W X 44"D X 32"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:&lt;br&gt;
+- Armless Chair: dimensions: 24" W x 44"D x 32" H&lt;br&gt;
+- Laf Phr Recliner: dimensions: 35" W x 44"D x 32" H&lt;br&gt;
+- Raf Phr Recliner: dimensions: 35" W x 44"D x 32" H&lt;br&gt;
+- Marble Console w/ Drawer &amp;amp; Wc: dimensions: 13" W x 44"D x 28" H&lt;br&gt;
+Weight: 174 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -28177,18 +28177,18 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-THEMIS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Gray tones, the Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: Sofa: 91.5"L X 40.5"W X 41"H
-Features
-- Pillow Top Arms
-- Contrast Welt
-- Drop-Down Table With Cup Holders Included items and dimensions:
-- Sofa: color: Gray; dimensions: 91.5" W x 40.5"D x 41" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 81" W x 40.5"D x 41" H; feature: Transitional
-Materials: Leatherette, Solid Wood.
-Color: Gray
-Weight: 436.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+THEMIS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Gray tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: Sofa: 91.5"L X 40.5"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Contrast Welt&lt;br&gt;
+- Drop-Down Table With Cup Holders Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 91.5" W x 40.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 81" W x 40.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 436.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -28305,19 +28305,19 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-THEOLA Sofa and Loveseat and Chair is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Leatherette, Solid Wood, and finished in Gray tones for a clean, cohesive look.
-Product Dimensions: Sofa: 91.5"L X 40.5"W X 41"H
-Features
-- Pillow Top Arms
-- Contrast Welt
-- Drop-Down Table With Cup Holders Included items and dimensions:
-- Sofa: color: Gray; dimensions: 91.5" W x 40.5"D x 41" H; feature: Transitional
-- Loveseat: color: Gray; dimensions: 81" W x 40.5"D x 41" H; feature: Transitional
-- Recliner: color: Gray; dimensions: 44" W x 40.5"D x 41" H; feature: Transitional
-Materials: Leatherette, Solid Wood.
-Color: Gray
-Weight: 542 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+THEOLA Sofa and Loveseat and Chair is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Leatherette, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 91.5"L X 40.5"W X 41"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Contrast Welt&lt;br&gt;
+- Drop-Down Table With Cup Holders Included items and dimensions:&lt;br&gt;
+- Sofa: color: Gray; dimensions: 91.5" W x 40.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Loveseat: color: Gray; dimensions: 81" W x 40.5"D x 41" H; feature: Transitional&lt;br&gt;
+- Recliner: color: Gray; dimensions: 44" W x 40.5"D x 41" H; feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 542 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -28434,20 +28434,20 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TREHARRIS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in White tones to suit a range of interiors.
-Product Dimensions: SOFA: 112"L X 40"W X 30"H (EXTENDED: 61"W) (SEAT HT: 17", SEAT DP: 22")
-Features
-- Modular Design
-- Power Recliner and Power Headrest
-- S-Spring Seat &amp; Webbing Back Suspension
-- Wide Track Arms
-- Flange Trim
-- USB Port
-- 100% Polyester
-Materials: Fabric, Solid Wood.
-Color: White
-Weight: 284 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TREHARRIS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in White tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 112"L X 40"W X 30"H (EXTENDED: 61"W) (SEAT HT: 17", SEAT DP: 22")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Modular Design&lt;br&gt;
+- Power Recliner and Power Headrest&lt;br&gt;
+- S-Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
+- Wide Track Arms&lt;br&gt;
+- Flange Trim&lt;br&gt;
+- USB Port&lt;br&gt;
+- 100% Polyester&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 284 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -28565,22 +28565,22 @@
       </c>
       <c r="G214" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VASILIOS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Breathable Leatherette, Solid Wood, build keeps the look polished and practical.
-Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Contrast Stitching
-- High Density Foam Seat Cushions
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Gray; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-- Power Loveseat: color: Gray; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-Materials: Breathable Leatherette, Solid Wood.
-Color: Gray
-Weight: 255 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VASILIOS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Breathable Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Contrast Stitching&lt;br&gt;
+- High Density Foam Seat Cushions&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Gray; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Gray; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H214" s="37" t="inlineStr">
@@ -28702,22 +28702,22 @@
       </c>
       <c r="G215" s="37" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VASILIOS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Breathable Leatherette, Solid Wood, and finished in Taupe tones for a clean, cohesive look.
-Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)
-Features
-- Power Recline Footrest &amp; Headrest
-- Contrast Stitching
-- High Density Foam Seat Cushions
-- Wall-hugger Design Requires Only 3-inches Off Wall
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps Included items and dimensions:
-- Power Sofa: color: Taupe; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-- Power Loveseat: color: Taupe; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional
-Materials: Breathable Leatherette, Solid Wood.
-Color: Taupe
-Weight: 255 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VASILIOS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Breathable Leatherette, Solid Wood, and finished in Taupe tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
+- Contrast Stitching&lt;br&gt;
+- High Density Foam Seat Cushions&lt;br&gt;
+- Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Taupe; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
+- Power Loveseat: color: Taupe; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
+Color: Taupe&lt;br&gt;
+Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H215" s="37" t="inlineStr">
@@ -28839,22 +28839,22 @@
       </c>
       <c r="G216" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HENRICUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Solid Wood, and finished in Beige tones for a clean, cohesive look.
-Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Manual Recline Sofa and Loveseat
-- Pillow Top Arms
-- Contrast Welt and Stitching
-- Stand-alone Glider Recliner
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered EvenUnder Back Flaps Included items and dimensions:
-- Sofa: color: Beige; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-- Loveseat: color: Beige; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Beige
-Weight: 218 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HENRICUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Solid Wood, and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Manual Recline Sofa and Loveseat&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Contrast Welt and Stitching&lt;br&gt;
+- Stand-alone Glider Recliner&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered EvenUnder Back Flaps Included items and dimensions:&lt;br&gt;
+- Sofa: color: Beige; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
+- Loveseat: color: Beige; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 218 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H216" s="22" t="inlineStr">
@@ -28976,22 +28976,22 @@
       </c>
       <c r="G217" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HENRICUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery uphostery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, then finished in Dark Brown tones to suit a range of interiors.
-Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Manual Recline Sofa and Loveseat
-- Pillow Top Arms
-- Contrast Welt and Stitching
-- Stand-alone Glider Recliner
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered EvenUnder Back Flaps Included items and dimensions:
-- Sofa: color: Dark Brown; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-- Loveseat: color: Dark Brown; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Dark Brown
-Weight: 218 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HENRICUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery uphostery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, then finished in Dark Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Manual Recline Sofa and Loveseat&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Contrast Welt and Stitching&lt;br&gt;
+- Stand-alone Glider Recliner&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered EvenUnder Back Flaps Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Brown; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
+- Loveseat: color: Dark Brown; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Brown&lt;br&gt;
+Weight: 218 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H217" s="22" t="inlineStr">
@@ -29113,22 +29113,22 @@
       </c>
       <c r="G218" s="22" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HENRICUS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery uphostery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Fabric, Solid Wood, construction and Dark Gray tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)
-Features
-- Manual Recline Sofa and Loveseat
-- Pillow Top Arms
-- Contrast Welt and Stitching
-- Stand-alone Glider Recliner
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered EvenUnder Back Flaps Included items and dimensions:
-- Sofa: color: Dark Gray; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-- Loveseat: color: Dark Gray; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional
-Materials: Fabric, Solid Wood.
-Color: Dark Gray
-Weight: 218 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HENRICUS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery uphostery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Fabric, Solid Wood, construction and Dark Gray tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Manual Recline Sofa and Loveseat&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Contrast Welt and Stitching&lt;br&gt;
+- Stand-alone Glider Recliner&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered EvenUnder Back Flaps Included items and dimensions:&lt;br&gt;
+- Sofa: color: Dark Gray; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
+- Loveseat: color: Dark Gray; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 218 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H218" s="22" t="inlineStr">
@@ -29250,19 +29250,19 @@
       </c>
       <c r="G219" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOSIAS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Breathable Leatherette, Solid Wood, then finished in Dark Gray Leatherette tones to suit a range of interiors.
-Product Dimensions: SOFA: 88"L X 39"W X 40"H (EXTENDED: 65"W)
-Features
-- Manual Recline Sofa
-- Pillow Top Arms w/ Contrast Welt Trim
-- Stand-alone Glider Recliner
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps
-Materials: Breathable Leatherette, Solid Wood.
-Color: Dark Gray Leatherette
-Weight: 234 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOSIAS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Breathable Leatherette, Solid Wood, then finished in Dark Gray Leatherette tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 39"W X 40"H (EXTENDED: 65"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Manual Recline Sofa&lt;br&gt;
+- Pillow Top Arms w/ Contrast Welt Trim&lt;br&gt;
+- Stand-alone Glider Recliner&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
+Color: Dark Gray Leatherette&lt;br&gt;
+Weight: 234 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H219" s="32" t="inlineStr">
@@ -29384,19 +29384,19 @@
       </c>
       <c r="G220" s="32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOSIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery sofa is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Light Gray Fabric tones, it blends durability with visual warmth.
-Product Dimensions: SOFA: 88"L X 39"W X 40"H (EXTENDED: 65"W)
-Features
-- Manual Recline Sofa
-- Pillow Top Arms w/ Contrast Welt Trim
-- Stand-alone Glider Recliner
-- No Sag Suspension w/ Sinuous Wire
-- Corner-blocked Kiln-dried Hardwood Frame
-- Fully Upholstered Even Under Back Flaps
-Materials: Fabric, Solid Wood.
-Color: Light Gray Fabric
-Weight: 234 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOSIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery sofa is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Light Gray Fabric tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 88"L X 39"W X 40"H (EXTENDED: 65"W)&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Manual Recline Sofa&lt;br&gt;
+- Pillow Top Arms w/ Contrast Welt Trim&lt;br&gt;
+- Stand-alone Glider Recliner&lt;br&gt;
+- No Sag Suspension w/ Sinuous Wire&lt;br&gt;
+- Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
+- Fully Upholstered Even Under Back Flaps&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
+Color: Light Gray Fabric&lt;br&gt;
+Weight: 234 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H220" s="32" t="inlineStr">

--- a/FOA SETS/Upholstery-Set.xlsx
+++ b/FOA SETS/Upholstery-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD220"/>
+  <dimension ref="A1:AG220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +745,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -869,7 +884,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ABERPORTH</t>
+          <t>Upholstery, Upholstery Set, ABERPORTH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1038,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ACAPULCO</t>
+          <t>Upholstery, Upholstery Set, ACAPULCO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1191,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ACAPULCO</t>
+          <t>Upholstery, Upholstery Set, ACAPULCO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1308,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ADELPHA</t>
+          <t>Upholstery, Upholstery Set, ADELPHA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1460,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ALBACETE</t>
+          <t>Upholstery, Upholstery Set, ALBACETE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1612,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ALBACETE</t>
+          <t>Upholstery, Upholstery Set, ALBACETE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1765,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ALESUND</t>
+          <t>Upholstery, Upholstery Set, ALESUND, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1918,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ALESUND</t>
+          <t>Upholstery, Upholstery Set, ALESUND, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -1930,7 +2065,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, AMAYA</t>
+          <t>Upholstery, Upholstery Set, AMAYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2213,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ANDALUSIA</t>
+          <t>Upholstery, Upholstery Set, ANDALUSIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2357,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ANTOINETTE</t>
+          <t>Upholstery, Upholstery Set, ANTOINETTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2501,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ANTOINETTE</t>
+          <t>Upholstery, Upholstery Set, ANTOINETTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2645,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ATTWELL</t>
+          <t>Upholstery, Upholstery Set, ATTWELL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2793,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, AZULETTI</t>
+          <t>Upholstery, Upholstery Set, AZULETTI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2940,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BASIE</t>
+          <t>Upholstery, Upholstery Set, BASIE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2853,7 +3093,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BELSIZE</t>
+          <t>Upholstery, Upholstery Set, BELSIZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -2991,7 +3246,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BELSIZE</t>
+          <t>Upholstery, Upholstery Set, BELSIZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3399,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BELSIZE</t>
+          <t>Upholstery, Upholstery Set, BELSIZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3547,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BIENNE</t>
+          <t>Upholstery, Upholstery Set, BIENNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3695,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BIENNE</t>
+          <t>Upholstery, Upholstery Set, BIENNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3845,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BONAVENTURA</t>
+          <t>Upholstery, Upholstery Set, BONAVENTURA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3995,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BONAVENTURA</t>
+          <t>Upholstery, Upholstery Set, BONAVENTURA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3789,7 +4134,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, BRIANA</t>
+          <t>Upholstery, Upholstery Set, BRIANA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -3916,7 +4276,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CASSANI</t>
+          <t>Upholstery, Upholstery Set, CASSANI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4424,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CATALONIA</t>
+          <t>Upholstery, Upholstery Set, CATALONIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4572,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CATARINA</t>
+          <t>Upholstery, Upholstery Set, CATARINA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4689,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CHARLEVOIX</t>
+          <t>Upholstery, Upholstery Set, CHARLEVOIX, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4834,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CHRISTINE</t>
+          <t>Upholstery, Upholstery Set, CHRISTINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4962,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CINDERFORD</t>
+          <t>Upholstery, Upholstery Set, CINDERFORD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4640,7 +5090,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CINDERFORD</t>
+          <t>Upholstery, Upholstery Set, CINDERFORD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4775,7 +5240,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CIVELLUTINO</t>
+          <t>Upholstery, Upholstery Set, CIVELLUTINO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -4910,7 +5390,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CIVELLUTINO</t>
+          <t>Upholstery, Upholstery Set, CIVELLUTINO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5536,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, COCHRANE</t>
+          <t>Upholstery, Upholstery Set, COCHRANE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5685,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CRAYFORD</t>
+          <t>Upholstery, Upholstery Set, CRAYFORD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5834,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CRAYFORD</t>
+          <t>Upholstery, Upholstery Set, CRAYFORD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5974,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, CROYDON</t>
+          <t>Upholstery, Upholstery Set, CROYDON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5568,7 +6123,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, DELGADA</t>
+          <t>Upholstery, Upholstery Set, DELGADA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5702,7 +6272,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, DELGADA</t>
+          <t>Upholstery, Upholstery Set, DELGADA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5813,7 +6398,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, DIONYSUS</t>
+          <t>Upholstery, Upholstery Set, DIONYSUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -5924,7 +6524,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, DIONYSUS</t>
+          <t>Upholstery, Upholstery Set, DIONYSUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6641,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, DORIPHEI</t>
+          <t>Upholstery, Upholstery Set, DORIPHEI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6788,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, EALING</t>
+          <t>Upholstery, Upholstery Set, EALING, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6932,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELICIA</t>
+          <t>Upholstery, Upholstery Set, ELICIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6416,7 +7076,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELICIA</t>
+          <t>Upholstery, Upholstery Set, ELICIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6547,7 +7222,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELLIS</t>
+          <t>Upholstery, Upholstery Set, ELLIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6679,7 +7369,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELPIS</t>
+          <t>Upholstery, Upholstery Set, ELPIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6816,7 +7521,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELVERUM</t>
+          <t>Upholstery, Upholstery Set, ELVERUM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -6953,7 +7673,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELVERUM</t>
+          <t>Upholstery, Upholstery Set, ELVERUM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7825,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ELVERUM</t>
+          <t>Upholstery, Upholstery Set, ELVERUM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7973,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ENSENADA</t>
+          <t>Upholstery, Upholstery Set, ENSENADA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7354,7 +8119,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, EZRIN</t>
+          <t>Upholstery, Upholstery Set, EZRIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7486,7 +8266,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, FLETCHER</t>
+          <t>Upholstery, Upholstery Set, FLETCHER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7616,7 +8411,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, FLINTSHIRE</t>
+          <t>Upholstery, Upholstery Set, FLINTSHIRE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7752,7 +8562,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, FRANKLIN</t>
+          <t>Upholstery, Upholstery Set, FRANKLIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -7888,7 +8713,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, FRANKLIN</t>
+          <t>Upholstery, Upholstery Set, FRANKLIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8860,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GERMAINE</t>
+          <t>Upholstery, Upholstery Set, GERMAINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8152,7 +9007,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GILDA</t>
+          <t>Upholstery, Upholstery Set, GILDA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8288,7 +9158,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GIOVANNI</t>
+          <t>Upholstery, Upholstery Set, GIOVANNI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8423,7 +9308,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GIOVANNI</t>
+          <t>Upholstery, Upholstery Set, GIOVANNI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8556,7 +9456,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GLARUS</t>
+          <t>Upholstery, Upholstery Set, GLARUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8689,7 +9604,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GLARUS</t>
+          <t>Upholstery, Upholstery Set, GLARUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8822,7 +9752,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GLARUS</t>
+          <t>Upholstery, Upholstery Set, GLARUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -8956,7 +9901,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, GUSTAVO</t>
+          <t>Upholstery, Upholstery Set, GUSTAVO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9089,7 +10049,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HARSTAD</t>
+          <t>Upholstery, Upholstery Set, HARSTAD, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9219,7 +10194,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HERMILLY</t>
+          <t>Upholstery, Upholstery Set, HERMILLY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9330,7 +10320,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HIERONYMUS</t>
+          <t>Upholstery, Upholstery Set, HIERONYMUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9441,7 +10446,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HIERONYMUS</t>
+          <t>Upholstery, Upholstery Set, HIERONYMUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9577,7 +10597,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HOLBORN</t>
+          <t>Upholstery, Upholstery Set, HOLBORN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9713,7 +10748,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HOLBORN</t>
+          <t>Upholstery, Upholstery Set, HOLBORN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9836,7 +10886,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HORGEN</t>
+          <t>Upholstery, Upholstery Set, HORGEN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -9967,7 +11032,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, HUELVA</t>
+          <t>Upholstery, Upholstery Set, HUELVA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10098,7 +11178,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ILSE</t>
+          <t>Upholstery, Upholstery Set, ILSE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10231,7 +11326,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, JAMAEL</t>
+          <t>Upholstery, Upholstery Set, JAMAEL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10367,7 +11477,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, JARROW</t>
+          <t>Upholstery, Upholstery Set, JARROW, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10503,7 +11628,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, JARROW</t>
+          <t>Upholstery, Upholstery Set, JARROW, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10626,7 +11766,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, JODIE</t>
+          <t>Upholstery, Upholstery Set, JODIE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10750,7 +11905,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, KAYE</t>
+          <t>Upholstery, Upholstery Set, KAYE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -10873,7 +12043,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, KESWICK</t>
+          <t>Upholstery, Upholstery Set, KESWICK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11001,7 +12186,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LANDOVERY</t>
+          <t>Upholstery, Upholstery Set, LANDOVERY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11132,7 +12332,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LAREDO</t>
+          <t>Upholstery, Upholstery Set, LAREDO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11269,7 +12484,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LEYTONSTONE</t>
+          <t>Upholstery, Upholstery Set, LEYTONSTONE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11406,7 +12636,22 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LEYTONSTONE</t>
+          <t>Upholstery, Upholstery Set, LEYTONSTONE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11536,7 +12781,22 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LISTOWEL</t>
+          <t>Upholstery, Upholstery Set, LISTOWEL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11667,7 +12927,22 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LISTOWEL</t>
+          <t>Upholstery, Upholstery Set, LISTOWEL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11803,7 +13078,22 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LOUGHLIN</t>
+          <t>Upholstery, Upholstery Set, LOUGHLIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -11939,7 +13229,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LOUGHLIN</t>
+          <t>Upholstery, Upholstery Set, LOUGHLIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12073,7 +13378,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LYNDA</t>
+          <t>Upholstery, Upholstery Set, LYNDA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12207,7 +13527,22 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, LYNDA</t>
+          <t>Upholstery, Upholstery Set, LYNDA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12333,7 +13668,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MARIELLA</t>
+          <t>Upholstery, Upholstery Set, MARIELLA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12463,7 +13813,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MARINELLA</t>
+          <t>Upholstery, Upholstery Set, MARINELLA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12595,7 +13960,22 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MARSICANO</t>
+          <t>Upholstery, Upholstery Set, MARSICANO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12727,7 +14107,22 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MARSICANO</t>
+          <t>Upholstery, Upholstery Set, MARSICANO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12853,7 +14248,22 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MARTINIQUE</t>
+          <t>Upholstery, Upholstery Set, MARTINIQUE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -12984,7 +14394,22 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MARVIN</t>
+          <t>Upholstery, Upholstery Set, MARVIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13108,7 +14533,22 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MATTEO</t>
+          <t>Upholstery, Upholstery Set, MATTEO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13243,7 +14683,22 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MEZZANOTTE</t>
+          <t>Upholstery, Upholstery Set, MEZZANOTTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13378,7 +14833,22 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MEZZANOTTE</t>
+          <t>Upholstery, Upholstery Set, MEZZANOTTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13510,7 +14980,22 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MIRAMAR</t>
+          <t>Upholstery, Upholstery Set, MIRAMAR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13639,7 +15124,22 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MISTY</t>
+          <t>Upholstery, Upholstery Set, MISTY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13773,7 +15273,22 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MOLFETTA</t>
+          <t>Upholstery, Upholstery Set, MOLFETTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -13907,7 +15422,22 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MONTECELIO</t>
+          <t>Upholstery, Upholstery Set, MONTECELIO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14038,7 +15568,22 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MOORPARK</t>
+          <t>Upholstery, Upholstery Set, MOORPARK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14151,7 +15696,22 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MORETAINE</t>
+          <t>Upholstery, Upholstery Set, MORETAINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14264,7 +15824,22 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MORETAINE</t>
+          <t>Upholstery, Upholstery Set, MORETAINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14377,7 +15952,22 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MORETAINE</t>
+          <t>Upholstery, Upholstery Set, MORETAINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14508,7 +16098,22 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MOSSLEY</t>
+          <t>Upholstery, Upholstery Set, MOSSLEY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14639,7 +16244,22 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, MOTT</t>
+          <t>Upholstery, Upholstery Set, MOTT, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14769,7 +16389,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NADENE</t>
+          <t>Upholstery, Upholstery Set, NADENE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14900,7 +16535,22 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NASH</t>
+          <t>Upholstery, Upholstery Set, NASH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15035,7 +16685,22 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEFYN</t>
+          <t>Upholstery, Upholstery Set, NEFYN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15170,7 +16835,22 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEFYN</t>
+          <t>Upholstery, Upholstery Set, NEFYN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15307,7 +16987,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEW MEADOWS</t>
+          <t>Upholstery, Upholstery Set, NEW MEADOWS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15444,7 +17139,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEW MEADOWS</t>
+          <t>Upholstery, Upholstery Set, NEW MEADOWS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15582,7 +17292,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEWDALE</t>
+          <t>Upholstery, Upholstery Set, NEWDALE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15720,7 +17445,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEWDALE</t>
+          <t>Upholstery, Upholstery Set, NEWDALE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15859,7 +17599,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEWDALE</t>
+          <t>Upholstery, Upholstery Set, NEWDALE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15990,7 +17745,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NEWRY</t>
+          <t>Upholstery, Upholstery Set, NEWRY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16122,7 +17892,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, NICANOR</t>
+          <t>Upholstery, Upholstery Set, NICANOR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16260,7 +18045,22 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PALENCIA</t>
+          <t>Upholstery, Upholstery Set, PALENCIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16398,7 +18198,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PALENCIA</t>
+          <t>Upholstery, Upholstery Set, PALENCIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16532,7 +18347,22 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PANOZZO</t>
+          <t>Upholstery, Upholstery Set, PANOZZO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16662,7 +18492,22 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PARKER</t>
+          <t>Upholstery, Upholstery Set, PARKER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16795,7 +18640,22 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PICOTEE</t>
+          <t>Upholstery, Upholstery Set, PICOTEE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16927,7 +18787,22 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PLAISTOW</t>
+          <t>Upholstery, Upholstery Set, PLAISTOW, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17055,7 +18930,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, PORTHCAWL</t>
+          <t>Upholstery, Upholstery Set, PORTHCAWL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17192,7 +19082,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, QUIRINO</t>
+          <t>Upholstery, Upholstery Set, QUIRINO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17329,7 +19234,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, QUIRINO</t>
+          <t>Upholstery, Upholstery Set, QUIRINO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17466,7 +19386,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, QUIRINO</t>
+          <t>Upholstery, Upholstery Set, QUIRINO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17599,7 +19534,22 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, RONJA</t>
+          <t>Upholstery, Upholstery Set, RONJA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17732,7 +19682,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, RONJA</t>
+          <t>Upholstery, Upholstery Set, RONJA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17863,7 +19828,22 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SAN ROQUE</t>
+          <t>Upholstery, Upholstery Set, SAN ROQUE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17994,7 +19974,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SILVAN</t>
+          <t>Upholstery, Upholstery Set, SILVAN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18125,7 +20120,22 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SINATRA</t>
+          <t>Upholstery, Upholstery Set, SINATRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18262,7 +20272,22 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SISSETON</t>
+          <t>Upholstery, Upholstery Set, SISSETON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18399,7 +20424,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SISSETON</t>
+          <t>Upholstery, Upholstery Set, SISSETON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18536,7 +20576,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SISSETON</t>
+          <t>Upholstery, Upholstery Set, SISSETON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18674,7 +20729,22 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SKYLINE</t>
+          <t>Upholstery, Upholstery Set, SKYLINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18812,7 +20882,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, SKYLINE</t>
+          <t>Upholstery, Upholstery Set, SKYLINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -18945,7 +21030,22 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, STEPHNEY</t>
+          <t>Upholstery, Upholstery Set, STEPHNEY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19078,7 +21178,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, STICKNEY</t>
+          <t>Upholstery, Upholstery Set, STICKNEY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19214,7 +21329,22 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, TABITHA</t>
+          <t>Upholstery, Upholstery Set, TABITHA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19350,7 +21480,22 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, TABITHA</t>
+          <t>Upholstery, Upholstery Set, TABITHA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19480,7 +21625,22 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, TEPIC</t>
+          <t>Upholstery, Upholstery Set, TEPIC, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19607,7 +21767,22 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, TILDE</t>
+          <t>Upholstery, Upholstery Set, TILDE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19740,7 +21915,22 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, ULVERY</t>
+          <t>Upholstery, Upholstery Set, ULVERY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19851,7 +22041,22 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VALDOSTA</t>
+          <t>Upholstery, Upholstery Set, VALDOSTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -19962,7 +22167,22 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VALDOSTA</t>
+          <t>Upholstery, Upholstery Set, VALDOSTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20100,7 +22320,22 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERACRUZ</t>
+          <t>Upholstery, Upholstery Set, VERACRUZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20238,7 +22473,22 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERACRUZ</t>
+          <t>Upholstery, Upholstery Set, VERACRUZ, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20375,7 +22625,22 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERDAL</t>
+          <t>Upholstery, Upholstery Set, VERDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20512,7 +22777,22 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERDAL</t>
+          <t>Upholstery, Upholstery Set, VERDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20649,7 +22929,22 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERDAL</t>
+          <t>Upholstery, Upholstery Set, VERDAL, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20780,7 +23075,22 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERDANTE</t>
+          <t>Upholstery, Upholstery Set, VERDANTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -20912,7 +23222,22 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VERNE</t>
+          <t>Upholstery, Upholstery Set, VERNE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21043,7 +23368,22 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VISCONTTI</t>
+          <t>Upholstery, Upholstery Set, VISCONTTI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21176,7 +23516,22 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, VIVIANA</t>
+          <t>Upholstery, Upholstery Set, VIVIANA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21308,7 +23663,22 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, WALDSTONE</t>
+          <t>Upholstery, Upholstery Set, WALDSTONE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21444,7 +23814,22 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, WEST ACTION</t>
+          <t>Upholstery, Upholstery Set, WEST ACTION, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21580,7 +23965,22 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, WEST ACTION</t>
+          <t>Upholstery, Upholstery Set, WEST ACTION, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21712,7 +24112,22 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, WEST BROMPTON</t>
+          <t>Upholstery, Upholstery Set, WEST BROMPTON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21843,7 +24258,22 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
-          <t>Upholstery, Upholstery Set, YUCATAN</t>
+          <t>Upholstery, Upholstery Set, YUCATAN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -21976,7 +24406,22 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, AGATA</t>
+          <t>Upholstery, Motion, AGATA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22108,7 +24553,22 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, AGATA</t>
+          <t>Upholstery, Motion, AGATA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22242,7 +24702,22 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, AGATA</t>
+          <t>Upholstery, Motion, AGATA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22374,7 +24849,22 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, AGATA</t>
+          <t>Upholstery, Motion, AGATA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22509,7 +24999,22 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ALTAMURA</t>
+          <t>Upholstery, Motion, ALTAMURA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22644,7 +25149,22 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ALTAMURA</t>
+          <t>Upholstery, Motion, ALTAMURA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22775,7 +25295,22 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, AMIRAH</t>
+          <t>Upholstery, Motion, AMIRAH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -22905,7 +25440,22 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ANTENOR</t>
+          <t>Upholstery, Motion, ANTENOR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23034,7 +25584,22 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ANTONIUS</t>
+          <t>Upholstery, Motion, ANTONIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23170,7 +25735,22 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ARTEMIA</t>
+          <t>Upholstery, Motion, ARTEMIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23306,7 +25886,22 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ARTEMIA</t>
+          <t>Upholstery, Motion, ARTEMIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23443,7 +26038,22 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ASCONA</t>
+          <t>Upholstery, Motion, ASCONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23580,7 +26190,22 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ASCONA</t>
+          <t>Upholstery, Motion, ASCONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23710,7 +26335,22 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, BALDERICO</t>
+          <t>Upholstery, Motion, BALDERICO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23836,7 +26476,22 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, COSIMO</t>
+          <t>Upholstery, Motion, COSIMO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -23963,7 +26618,22 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, COSIMO</t>
+          <t>Upholstery, Motion, COSIMO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24075,7 +26745,22 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, DEMETRIUS</t>
+          <t>Upholstery, Motion, DEMETRIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24187,7 +26872,22 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, DEMETRIUS</t>
+          <t>Upholstery, Motion, DEMETRIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24316,7 +27016,22 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, EZEKIUS</t>
+          <t>Upholstery, Motion, EZEKIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24448,7 +27163,22 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, FLORINE</t>
+          <t>Upholstery, Motion, FLORINE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24577,7 +27307,22 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, GIRALDUS</t>
+          <t>Upholstery, Motion, GIRALDUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24712,7 +27457,22 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, GORGIUS</t>
+          <t>Upholstery, Motion, GORGIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24847,7 +27607,22 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, GORGIUS</t>
+          <t>Upholstery, Motion, GORGIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -24977,7 +27752,22 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, GRANUCCI</t>
+          <t>Upholstery, Motion, GRANUCCI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25111,7 +27901,22 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, JACOBUS</t>
+          <t>Upholstery, Motion, JACOBUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25245,7 +28050,22 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, JACOBUS</t>
+          <t>Upholstery, Motion, JACOBUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25374,7 +28194,22 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, LEOLINUS</t>
+          <t>Upholstery, Motion, LEOLINUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25500,7 +28335,22 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, LETHA</t>
+          <t>Upholstery, Motion, LETHA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25629,7 +28479,22 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MATTHIAS</t>
+          <t>Upholstery, Motion, MATTHIAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25766,7 +28631,22 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MORCOTE</t>
+          <t>Upholstery, Motion, MORCOTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -25900,7 +28780,22 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MORCOTE</t>
+          <t>Upholstery, Motion, MORCOTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26037,7 +28932,22 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MORCOTE</t>
+          <t>Upholstery, Motion, MORCOTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26166,7 +29076,22 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, ONORIA</t>
+          <t>Upholstery, Motion, ONORIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26293,7 +29218,22 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, OSIAS</t>
+          <t>Upholstery, Motion, OSIAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26421,7 +29361,22 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, OSIAS</t>
+          <t>Upholstery, Motion, OSIAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26557,7 +29512,22 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, PHINEAS</t>
+          <t>Upholstery, Motion, PHINEAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26693,7 +29663,22 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, PHINEAS</t>
+          <t>Upholstery, Motion, PHINEAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26829,7 +29814,22 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, PHINEAS</t>
+          <t>Upholstery, Motion, PHINEAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -26957,7 +29957,22 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SANDBACH</t>
+          <t>Upholstery, Motion, SANDBACH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27090,7 +30105,22 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SCHLIEREN</t>
+          <t>Upholstery, Motion, SCHLIEREN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27223,7 +30253,22 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SCHLIEREN</t>
+          <t>Upholstery, Motion, SCHLIEREN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27356,7 +30401,22 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SCHLIEREN</t>
+          <t>Upholstery, Motion, SCHLIEREN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27489,7 +30549,22 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SCHLIEREN</t>
+          <t>Upholstery, Motion, SCHLIEREN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27626,7 +30701,22 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SOTERIOS</t>
+          <t>Upholstery, Motion, SOTERIOS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27763,7 +30853,22 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, SOTERIOS</t>
+          <t>Upholstery, Motion, SOTERIOS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -27904,7 +31009,22 @@
       </c>
       <c r="AD208" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, TERENTIUS</t>
+          <t>Upholstery, Motion, TERENTIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28041,7 +31161,22 @@
       </c>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, TERENTIUS</t>
+          <t>Upholstery, Motion, TERENTIUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28145,7 +31280,22 @@
       </c>
       <c r="AD210" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, THADDEA</t>
+          <t>Upholstery, Motion, THADDEA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28273,7 +31423,22 @@
       </c>
       <c r="AD211" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, THEMIS</t>
+          <t>Upholstery, Motion, THEMIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28402,7 +31567,22 @@
       </c>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, THEOLA</t>
+          <t>Upholstery, Motion, THEOLA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28532,7 +31712,22 @@
       </c>
       <c r="AD213" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, TREHARRIS</t>
+          <t>Upholstery, Motion, TREHARRIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28669,7 +31864,22 @@
       </c>
       <c r="AD214" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, VASILIOS</t>
+          <t>Upholstery, Motion, VASILIOS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28806,7 +32016,22 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, VASILIOS</t>
+          <t>Upholstery, Motion, VASILIOS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -28829,7 +32054,7 @@
       </c>
       <c r="E216" s="22" t="inlineStr">
         <is>
-          <t>Uphostery Set</t>
+          <t>Upholstery Set</t>
         </is>
       </c>
       <c r="F216" s="22" t="inlineStr">
@@ -28943,7 +32168,22 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
-          <t>Upholstery, Uphostery Set, HENRICUS</t>
+          <t>Upholstery, Upholstery Set, HENRICUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -28966,7 +32206,7 @@
       </c>
       <c r="E217" s="22" t="inlineStr">
         <is>
-          <t>Uphostery Set</t>
+          <t>Upholstery Set</t>
         </is>
       </c>
       <c r="F217" s="22" t="inlineStr">
@@ -29080,7 +32320,22 @@
       </c>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>Upholstery, Uphostery Set, HENRICUS</t>
+          <t>Upholstery, Upholstery Set, HENRICUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29103,7 +32358,7 @@
       </c>
       <c r="E218" s="22" t="inlineStr">
         <is>
-          <t>Uphostery Set</t>
+          <t>Upholstery Set</t>
         </is>
       </c>
       <c r="F218" s="22" t="inlineStr">
@@ -29217,7 +32472,22 @@
       </c>
       <c r="AD218" t="inlineStr">
         <is>
-          <t>Upholstery, Uphostery Set, HENRICUS</t>
+          <t>Upholstery, Upholstery Set, HENRICUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29240,7 +32510,7 @@
       </c>
       <c r="E219" s="32" t="inlineStr">
         <is>
-          <t>Uphostery Set</t>
+          <t>Upholstery Set</t>
         </is>
       </c>
       <c r="F219" s="32" t="inlineStr">
@@ -29351,7 +32621,22 @@
       </c>
       <c r="AD219" t="inlineStr">
         <is>
-          <t>Upholstery, Uphostery Set, JOSIAS</t>
+          <t>Upholstery, Upholstery Set, JOSIAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -29485,7 +32770,22 @@
       </c>
       <c r="AD220" t="inlineStr">
         <is>
-          <t>Upholstery, Sofa, JOSIAS</t>
+          <t>Upholstery, Sofa, JOSIAS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>

--- a/FOA SETS/Upholstery-Set.xlsx
+++ b/FOA SETS/Upholstery-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -945,11 +945,11 @@
 - Box Seat Cushion w/ Welt&lt;br&gt;
 - Wing Back Design&lt;br&gt;
 - Accent Pillow Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Black or Off-White; dimensions: 84.5" W x 43"D x 48" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Black or Off-White; dimensions: 70.5" W x 43"D x 48" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Black or Off-White&lt;br&gt;
-Weight: 347.6 lbs&lt;/p&gt;</t>
+- Sofa: color: Black or Off-White or Off-White&lt;br&gt;
+- Loveseat: color: Black or Off-White or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Black or Off-White or Off-White&lt;br&gt;
+Weight: 347.6 or 355.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1087,10 +1087,11 @@
       <c r="G4" s="14" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ACAPULCO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. With Fabric, Solid Wood, construction and Off-White tones, it blends durability with visual warmth.&lt;br&gt;
+ACAPULCO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, then finished in Black or Off-White tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: Sofa: 84.5"L X 42"W X 48.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
+- Black or Off-White&lt;br&gt;
 - Diamond Tufted Back&lt;br&gt;
 - Crown Molding&lt;br&gt;
 - Carved Details&lt;br&gt;
@@ -1098,11 +1099,11 @@
 - Box Seat Cushion w/ Welt&lt;br&gt;
 - Wing Back Design&lt;br&gt;
 - Accent Pillow Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Off-White; dimensions: 84.5" W x 43"D x 48" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Off-White; dimensions: 70.5" W x 43"D x 48" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Off-White&lt;br&gt;
-Weight: 355.5 lbs&lt;/p&gt;</t>
+- Sofa: color: Black or Off-White or Off-White&lt;br&gt;
+- Loveseat: color: Black or Off-White or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Black or Off-White or Off-White&lt;br&gt;
+Weight: 347.6 or 355.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
@@ -1186,7 +1187,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1303,7 +1304,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1358,7 +1359,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ALBACETE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Velvet, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 94 1/2" X 41 3/4" X 26"&lt;/p&gt;
+Product Dimensions: 94 1/2" X 41 3/4" X 26" / 94.5" X 48.25" X 38.5"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Dark Cherry or Brown&lt;br&gt;
@@ -1367,11 +1368,11 @@
 - Reversible Seat Cushion w/ Welt&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Cherry or Brown; dimensions: 94.5" x 48.25" x 38.5"; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Cherry or Brown; dimensions: 69.5" x 48.25" x 38.5"; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Velvet, Solid Wood.&lt;br&gt;
-Color: Dark Cherry or Brown&lt;br&gt;
-Weight: 420.2 lbs&lt;/p&gt;</t>
+- Sofa: color: Dark Cherry or Brown or Champagne or Purple&lt;br&gt;
+- Loveseat: color: Dark Cherry or Brown or Champagne or Purple&lt;/p&gt;
+&lt;p&gt;Materials: Velvet, Solid Wood, Others.&lt;br&gt;
+Color: Dark Cherry or Brown or Champagne or Purple&lt;br&gt;
+Weight: 420.2 or 430.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -1455,7 +1456,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1509,21 +1510,21 @@
       <c r="G7" s="16" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALBACETE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Velvet, Solid Wood, construction and Champagne or Purple tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 94.5" X 48.25" X 38.5"&lt;/p&gt;
+ALBACETE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Velvet, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 94 1/2" X 41 3/4" X 26" / 94.5" X 48.25" X 38.5"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Champagne or Purple&lt;br&gt;
+- Dark Cherry or Brown&lt;br&gt;
 - Button Tufted Back&lt;br&gt;
 - Carved Details&lt;br&gt;
 - Reversible Seat Cushion w/ Welt&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Champagne or Purple; dimensions: 94.5" x 48.25" x 38.5"; feature: Traditional&lt;br&gt;
-- Loveseat: color: Champagne or Purple; dimensions: 69.5" x 48.25" x 38.5"; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Velvet, Solid Wood.&lt;br&gt;
-Color: Champagne or Purple&lt;br&gt;
-Weight: 430.1 lbs&lt;/p&gt;</t>
+- Sofa: color: Dark Cherry or Brown or Champagne or Purple&lt;br&gt;
+- Loveseat: color: Dark Cherry or Brown or Champagne or Purple&lt;/p&gt;
+&lt;p&gt;Materials: Velvet, Solid Wood, Others.&lt;br&gt;
+Color: Dark Cherry or Brown or Champagne or Purple&lt;br&gt;
+Weight: 420.2 or 430.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" s="16" t="inlineStr">
@@ -1607,7 +1608,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1672,10 +1673,10 @@
 - Tapered Wooden Leg&lt;br&gt;
 - Side Bolster Pillow&lt;br&gt;
 - Feather Fiber Pillow Construction Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige or Light Oak; dimensions: 87" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;br&gt;
-- Loveseat: color: Beige or Light Oak; dimensions: 65" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Beige or Light Oak&lt;br&gt;
+- Sofa: color: Beige or Light Oak or Beige or Walnut&lt;br&gt;
+- Loveseat: color: Beige or Light Oak or Beige or Walnut&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Light Oak or Beige or Walnut&lt;br&gt;
 Weight: 323 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1760,7 +1761,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1814,10 +1815,10 @@
       <c r="G9" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALESUND Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Mid-Century Modern profile gives the space a refined, approachable look. Finished in Beige or Walnut tones, the Fabric, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+ALESUND Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Mid-Century Modern character adds definition without feeling heavy. With Fabric, Solid Wood, construction and Beige or Light Oak tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 87"W X 38"D X 33"H (SEAT HT: 19", SEAT DP: 23")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Beige or Walnut&lt;br&gt;
+- Beige or Light Oak&lt;br&gt;
 - Ash Wood Trim&lt;br&gt;
 - Rattan Details&lt;br&gt;
 - Reversible Loose Pillow Back&lt;br&gt;
@@ -1825,10 +1826,10 @@
 - Tapered Wooden Leg&lt;br&gt;
 - Side Bolster Pillow&lt;br&gt;
 - Feather Fiber Pillow Construction Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige or Walnut; dimensions: 87" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;br&gt;
-- Loveseat: color: Beige or Walnut; dimensions: 65" W x 38"D x 33" H (SEAT HT: 19", SEAT DP: 23"); feature: Mid-Century Modern&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Beige or Walnut&lt;br&gt;
+- Sofa: color: Beige or Light Oak or Beige or Walnut&lt;br&gt;
+- Loveseat: color: Beige or Light Oak or Beige or Walnut&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Light Oak or Beige or Walnut&lt;br&gt;
 Weight: 323 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1913,7 +1914,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2060,7 +2061,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2208,7 +2209,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2268,10 +2269,10 @@
 - Deep Tufting w/ Acrylic Buttons&lt;br&gt;
 - Pillows Included&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: White; dimensions: 86 1 or 2" L x 39 1 or 2" W x 4" H (SEAT HT: 21 1 or 2", SEAT DP: 26"); feature: Glam&lt;br&gt;
-- Loveseat: color: White; dimensions: 68" L x 39 1 or 2" W x 4" H (SEAT HT: 21 1 or 2", SEAT DP: 26"); feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+- Sofa: color: White or Gray&lt;br&gt;
+- Loveseat: color: White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood, Others.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
 Weight: 257 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2352,7 +2353,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2406,16 +2407,16 @@
       <c r="G13" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ANTOINETTE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Glam styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Velvet-like, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+ANTOINETTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Glam profile gives the space a refined, approachable look. With Velvet-like, Solid Wood, construction and White tones, it blends durability with visual warmth.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Chesterfield Inspired Design&lt;br&gt;
 - Deep Tufting w/ Acrylic Buttons&lt;br&gt;
 - Pillows Included&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray; dimensions: 91" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Glam&lt;br&gt;
-- Loveseat: color: Gray; dimensions: 68" L x 38" W x 41" H (SEAT HT: 21", SEAT DP: 25"); feature: Glam&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Sofa: color: White or Gray&lt;br&gt;
+- Loveseat: color: White or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Solid Wood, Others.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
 Weight: 257 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2496,7 +2497,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2640,7 +2641,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2788,7 +2789,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2935,7 +2936,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3000,10 +3001,10 @@
 - Welt Trim&lt;br&gt;
 - Tapered Block Legs&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige or Navy; dimensions: 91" L x 38" W x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Beige or Navy; dimensions: 70" L x 38" W x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
-Color: Beige or Navy&lt;br&gt;
+- Sofa: color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;br&gt;
+- Loveseat: color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;br&gt;
 Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3088,7 +3089,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3142,10 +3143,10 @@
       <c r="G18" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELSIZE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Linen-like, Solid Wood, then finished in Chocolate or Tan tones to suit a range of interiors.&lt;br&gt;
+BELSIZE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Beige or Navy tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 91"L X 38"W X 40"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Chocolate or Tan&lt;br&gt;
+- Beige or Navy&lt;br&gt;
 - Box Seat Cushions&lt;br&gt;
 - Loose Pillow Backs&lt;br&gt;
 - Padded Sloped Armrests&lt;br&gt;
@@ -3153,10 +3154,10 @@
 - Welt Trim&lt;br&gt;
 - Tapered Block Legs&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: Chocolate or Tan; dimensions: 91" L x 38" W x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Chocolate or Tan; dimensions: 70" L x 38" W x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
-Color: Chocolate or Tan&lt;br&gt;
+- Sofa: color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;br&gt;
+- Loveseat: color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;br&gt;
 Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3241,7 +3242,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3295,10 +3296,10 @@
       <c r="G19" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELSIZE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Linen-like, Solid Wood, construction and Light Taupe or Black tones, it blends durability with visual warmth.&lt;br&gt;
+BELSIZE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen-like, Solid Wood, and finished in Beige or Navy tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 91"L X 38"W X 40"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Light Taupe or Black&lt;br&gt;
+- Beige or Navy&lt;br&gt;
 - Box Seat Cushions&lt;br&gt;
 - Loose Pillow Backs&lt;br&gt;
 - Padded Sloped Armrests&lt;br&gt;
@@ -3306,10 +3307,10 @@
 - Welt Trim&lt;br&gt;
 - Tapered Block Legs&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Taupe or Black; dimensions: 91" L x 38" W x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Taupe or Black; dimensions: 70" L x 38" W x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Linen-like, Solid Wood.&lt;br&gt;
-Color: Light Taupe or Black&lt;br&gt;
+- Sofa: color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;br&gt;
+- Loveseat: color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;/p&gt;
+&lt;p&gt;Materials: Linen-like, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Navy or Chocolate or Tan or Light Taupe or Black&lt;br&gt;
 Weight: 275 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3394,7 +3395,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3454,11 +3455,11 @@
 - Flared Padded Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Sofa: color: Black; dimensions: 86" W x 35.5"D x 40.5" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Black; dimensions: 62.5" W x 35.5"D x 40.5" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 363.8 lbs&lt;/p&gt;</t>
+- Sofa: color: Black or Taupe&lt;br&gt;
+- Loveseat: color: Black or Taupe&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal, Others.&lt;br&gt;
+Color: Black or Taupe&lt;br&gt;
+Weight: 363.8 or 372.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -3542,7 +3543,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3596,17 +3597,17 @@
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BIENNE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Metal, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+BIENNE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Black tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 38.6"L X 35.4"W X 40.6"H, LOVESEAT: 62.6"L X 35.4"W X 40.6"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Flared Padded Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Sofa: color: Taupe; dimensions: 86" W x 35.5"D x 40.5" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Taupe; dimensions: 62.5" W x 35.5"D x 40.5" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
-Color: Taupe&lt;br&gt;
-Weight: 372.5 lbs&lt;/p&gt;</t>
+- Sofa: color: Black or Taupe&lt;br&gt;
+- Loveseat: color: Black or Taupe&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal, Others.&lt;br&gt;
+Color: Black or Taupe&lt;br&gt;
+Weight: 363.8 or 372.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -3690,7 +3691,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3752,10 +3753,10 @@
 - Fitted Back Pillows&lt;br&gt;
 - Block Bun Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Brown; dimensions: 92" L x 43" W x 41" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Brown; dimensions: 69" L x 43" W x 41" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Brown or Gray&lt;br&gt;
+- Loveseat: color: Brown or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
+Color: Brown or Gray&lt;br&gt;
 Weight: 282 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3840,7 +3841,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3894,7 +3895,7 @@
       <c r="G23" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BONAVENTURA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Fabric, Solid Wood construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
+BONAVENTURA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 92"L X 43"W X 41"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - T-Cushion Seating&lt;br&gt;
@@ -3902,10 +3903,10 @@
 - Fitted Back Pillows&lt;br&gt;
 - Block Bun Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray or Pattern; dimensions: 92" L x 43" W x 41" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Gray or Pattern; dimensions: 69" L x 43" W x 41" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Brown or Gray&lt;br&gt;
+- Loveseat: color: Brown or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Brown or Gray&lt;br&gt;
 Weight: 282 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3990,7 +3991,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4129,7 +4130,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4271,7 +4272,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4419,7 +4420,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4567,7 +4568,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4684,7 +4685,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4829,7 +4830,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4880,12 +4881,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CINDERFORD Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22")&lt;br&gt;
 - Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
 - Beige Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
 - Beige Love Seat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
 - Beige Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-Weight: 204.18 lbs&lt;/p&gt;</t>
+Weight: 204.18 or 193.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="28" t="inlineStr">
@@ -4957,7 +4958,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5007,13 +5008,13 @@
       <c r="G31" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CINDERFORD Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
-- Dark Gray Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
-- Dark Gray Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
-- Dark Gray Love Seat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-- Dark Gray Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-Weight: 193.3 lbs&lt;/p&gt;</t>
+CINDERFORD Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22")&lt;br&gt;
+- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Sofa Arm And Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Love Seat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Beige Love Seat Arm And Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 204.18 or 193.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
@@ -5085,7 +5086,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5149,8 +5150,8 @@
 - Webbing Back and Ring Seat Suspension&lt;br&gt;
 - Chrome X Legs&lt;br&gt;
 - 100% Made in Italy&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Metal, Engineered Wood.&lt;br&gt;
-Color: Light Blue&lt;br&gt;
+&lt;p&gt;Materials: Velvet-like, Metal, Engineered Wood, Others.&lt;br&gt;
+Color: Light Blue or Teal&lt;br&gt;
 Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5235,7 +5236,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5289,18 +5290,18 @@
       <c r="G33" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CIVELLUTINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Velvet-like, Metal, Engineered Wood, then finished in Teal tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: Sofa: 79 1/2"L X 36 1/2"W X 33 1/8"H (SEAT HT: 18", SEAT DP: 21 3/4")&lt;/p&gt;
+CIVELLUTINO Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Velvet-like, Metal, Engineered Wood, and finished in Light Blue tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: SOFA: 79 1/2"L X 36 1/2"W X 33 1/8"H (SEAT HT: 18", SEAT DP: 21 3/4")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Biscuit Tufting&lt;br&gt;
-- 100% Polyester Fabric&lt;br&gt;
+- Biscuit Tufting &amp;amp; 100% Polyester Fabric&lt;br&gt;
 - Tight Back and Seat&lt;br&gt;
 - High Density Foam Seat&lt;br&gt;
 - Foam and Fiber-filled Back Pillow&lt;br&gt;
-- Chrome Legs&lt;br&gt;
-- Made in Italy&lt;/p&gt;
-&lt;p&gt;Materials: Velvet-like, Metal, Engineered Wood.&lt;br&gt;
-Color: Teal&lt;br&gt;
+- Webbing Back and Ring Seat Suspension&lt;br&gt;
+- Chrome X Legs&lt;br&gt;
+- 100% Made in Italy&lt;/p&gt;
+&lt;p&gt;Materials: Velvet-like, Metal, Engineered Wood, Others.&lt;br&gt;
+Color: Light Blue or Teal&lt;br&gt;
 Weight: 264 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5385,7 +5386,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5531,7 +5532,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5592,10 +5593,10 @@
 - Welt Trim&lt;br&gt;
 - Wooden Legs&lt;br&gt;
 - Narrow Track Arm Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Gray; dimensions: 83.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Gray; dimensions: 67.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;/p&gt;
+- Sofa: color: Light Gray or Taupe&lt;br&gt;
+- Loveseat: color: Light Gray or Taupe&lt;/p&gt;
 &lt;p&gt;Materials: Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Light Gray or Taupe&lt;br&gt;
 Weight: 268.97 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5680,7 +5681,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5734,17 +5735,17 @@
       <c r="G36" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CRAYFORD Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
+CRAYFORD Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 83.5"W X 38"D X 34.5"H (SEAT HT: 18.5", SEAT DP: 23")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Feather Blend Pillow Top Cushion and Back Pillow&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - Wooden Legs&lt;br&gt;
 - Narrow Track Arm Included items and dimensions:&lt;br&gt;
-- Sofa: color: Taupe; dimensions: 83.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Taupe; dimensions: 67.5" W x 38"D x 34.5" H (SEAT HT: 18.5", SEAT DP: 23"); feature: Transitional&lt;/p&gt;
+- Sofa: color: Light Gray or Taupe&lt;br&gt;
+- Loveseat: color: Light Gray or Taupe&lt;/p&gt;
 &lt;p&gt;Materials: Linen, Feather Blend, Foam, Solid Wood, Engineered Wood, Other.&lt;br&gt;
-Color: Taupe&lt;br&gt;
+Color: Light Gray or Taupe&lt;br&gt;
 Weight: 268.97 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5829,7 +5830,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -5969,7 +5970,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6030,10 +6031,10 @@
 - Tapered Wood Feet&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige; dimensions: 91" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Beige; dimensions: 72" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
+- Sofa: color: Beige or Graphite&lt;br&gt;
+- Loveseat: color: Beige or Graphite&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Graphite&lt;br&gt;
 Weight: 220 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6118,7 +6119,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6172,17 +6173,17 @@
       <c r="G39" s="14" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DELGADA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Graphite tones, it blends durability with visual warmth.&lt;br&gt;
+DELGADA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Chenille, Solid Wood, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 91"L X 37"W X 39"H (SEAT HT: 21 1/2", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Tapered Wood Feet&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Graphite; dimensions: 91" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Graphite; dimensions: 72" L x 37" W x 39" H (SEAT HT: 21 1 or 2", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Graphite&lt;br&gt;
+- Sofa: color: Beige or Graphite&lt;br&gt;
+- Loveseat: color: Beige or Graphite&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Graphite&lt;br&gt;
 Weight: 220 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6267,7 +6268,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6318,10 +6319,10 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DIONYSUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22-62") Included items and dimensions:&lt;br&gt;
+Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22-62") / 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22"-62)&lt;br&gt;
 - Manual Reclining Sofa w/ USB &amp;amp; LED: color: Brown; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
 - USB &amp;amp; LED Manual Reclining Loveseat w/ Console: color: Brown; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
-Weight: 348.7 lbs&lt;/p&gt;</t>
+Weight: 348.7 or 350.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" s="35" t="inlineStr">
@@ -6393,7 +6394,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6443,11 +6444,11 @@
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DIONYSUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
-Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22"-62) Included items and dimensions:&lt;br&gt;
-- Manual Reclining Sofa w/ USB &amp;amp; LED: color: Gray; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22"-62); feature: Transitional&lt;br&gt;
-- USB &amp;amp; LED Manual Reclining Loveseat w/ Console: color: Gray; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
-Weight: 350.2 lbs&lt;/p&gt;</t>
+DIONYSUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22-62") / 82.5"W X 39"D X 38"H (SEAT HT: 19.5", SEAT DP: 22"-62)&lt;br&gt;
+- Manual Reclining Sofa w/ USB &amp;amp; LED: color: Brown; dimensions: 82.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
+- USB &amp;amp; LED Manual Reclining Loveseat w/ Console: color: Brown; dimensions: 72.5" W x 39"D x 38" H (SEAT HT: 19.5", SEAT DP: 22-62"); feature: Transitional&lt;br&gt;
+Weight: 348.7 or 350.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" s="35" t="inlineStr">
@@ -6519,7 +6520,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6636,7 +6637,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6783,7 +6784,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6843,11 +6844,11 @@
 - Individual Nailhead Trim&lt;br&gt;
 - Bench Style Cushion&lt;br&gt;
 - Tapered Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Champagne or Turquoise; dimensions: 93" L x 39" W x 39" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Champagne or Turquoise; dimensions: 67" L x 39" W x 39" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Champagne or Turquoise or Silver&lt;br&gt;
+- Loveseat: color: Champagne or Turquoise or Silver&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Champagne or Turquoise&lt;br&gt;
-Weight: 285 lbs&lt;/p&gt;</t>
+Color: Champagne or Turquoise or Silver&lt;br&gt;
+Weight: 285 or 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="16" t="inlineStr">
@@ -6927,7 +6928,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -6981,17 +6982,17 @@
       <c r="G45" s="16" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELICIA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Chenille, Solid Wood construction and Silver tones, it blends durability with visual warmth.&lt;/p&gt;
+ELICIA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Champagne or Turquoise tones to suit a range of interiors.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
+- Champagne or Turquoise&lt;br&gt;
 - Individual Nailhead Trim&lt;br&gt;
 - Bench Style Cushion&lt;br&gt;
-- Chrome Legs&lt;br&gt;
 - Tapered Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Silver; dimensions: 93" L x 39" W x 39" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Silver; dimensions: 67" L x 39" W x 39" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Champagne or Turquoise or Silver&lt;br&gt;
+- Loveseat: color: Champagne or Turquoise or Silver&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Silver&lt;br&gt;
-Weight: 289 lbs&lt;/p&gt;</t>
+Color: Champagne or Turquoise or Silver&lt;br&gt;
+Weight: 285 or 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
@@ -7071,7 +7072,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7217,7 +7218,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7364,7 +7365,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7428,10 +7429,10 @@
 - High Density Foam w/ Pocket Coils&lt;br&gt;
 - Kiln-driedHardwood&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Black; dimensions: 82 1 or 2" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;br&gt;
-- Loveseat: color: Black; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+- Sofa: color: Black or Charcoal Gray or Off-White&lt;br&gt;
+- Loveseat: color: Black or Charcoal Gray or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood, Others.&lt;br&gt;
+Color: Black or Charcoal Gray or Off-White&lt;br&gt;
 Weight: 203 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7516,7 +7517,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7570,7 +7571,7 @@
       <c r="G49" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELVERUM Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Boucle, Solid Wood, construction and Charcoal Gray tones, it blends durability with visual warmth.&lt;br&gt;
+ELVERUM Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Boucle, Solid Wood, then finished in Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bench-style Seating&lt;br&gt;
@@ -7580,10 +7581,10 @@
 - High Density Foam w/ Pocket Coils&lt;br&gt;
 - Kiln-driedHardwood&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Charcoal Gray; dimensions: 82 1 or 2" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;br&gt;
-- Loveseat: color: Charcoal Gray; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
-Color: Charcoal Gray&lt;br&gt;
+- Sofa: color: Black or Charcoal Gray or Off-White&lt;br&gt;
+- Loveseat: color: Black or Charcoal Gray or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood, Others.&lt;br&gt;
+Color: Black or Charcoal Gray or Off-White&lt;br&gt;
 Weight: 203 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7668,7 +7669,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7722,7 +7723,7 @@
       <c r="G50" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELVERUM Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Off-White tones, the Boucle, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+ELVERUM Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Crafted with Boucle, Solid Wood, then finished in Black tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 82 1/2"L X 34 1/2"W X 33"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Bench-style Seating&lt;br&gt;
@@ -7732,10 +7733,10 @@
 - High Density Foam w/ Pocket Coils&lt;br&gt;
 - Kiln-driedHardwood&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Off-White; dimensions: 82 1 or 2" L x 34 1 or 2" W x 33" H (SEAT HT: 18 1 or 2", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
-- Loveseat: color: Off-White; dimensions: 63" L x 34 1 or 2" W x 34 3 or 4" H (SEAT HT: 19", SEAT DP: 20 3 or 4"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
-Color: Off-White&lt;br&gt;
+- Sofa: color: Black or Charcoal Gray or Off-White&lt;br&gt;
+- Loveseat: color: Black or Charcoal Gray or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood, Others.&lt;br&gt;
+Color: Black or Charcoal Gray or Off-White&lt;br&gt;
 Weight: 203 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7820,7 +7821,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -7968,7 +7969,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8114,7 +8115,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8261,7 +8262,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8406,7 +8407,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8469,10 +8470,10 @@
 - Pillows Included&lt;br&gt;
 - Intricate Wood Trim&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Brown or Tan; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Brown or Tan; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
-Color: Dark Brown or Tan&lt;br&gt;
+- Sofa: color: Dark Brown or Tan or Burgundy or Espresso&lt;br&gt;
+- Loveseat: color: Dark Brown or Tan or Burgundy or Espresso&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Dark Brown or Tan or Burgundy or Espresso&lt;br&gt;
 Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8557,7 +8558,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8611,19 +8612,19 @@
       <c r="G56" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FRANKLIN Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Leatherette, Solid Wood, construction and Burgundy or Espresso tones, it blends durability with visual warmth.&lt;br&gt;
+FRANKLIN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Leatherette, Solid Wood, then finished in Dark Brown or Tan tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 94"L X 37"W X 37.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Burgundy or Espresso&lt;br&gt;
+- Dark Brown or Tan&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Pillows Included&lt;br&gt;
 - Intricate Wood Trim&lt;br&gt;
 - US-Made (Incl. Foreign Materials) Included items and dimensions:&lt;br&gt;
-- Sofa: color: Burgundy or Espresso; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Burgundy or Espresso; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
-Color: Burgundy or Espresso&lt;br&gt;
+- Sofa: color: Dark Brown or Tan or Burgundy or Espresso&lt;br&gt;
+- Loveseat: color: Dark Brown or Tan or Burgundy or Espresso&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Dark Brown or Tan or Burgundy or Espresso&lt;br&gt;
 Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8708,7 +8709,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8855,7 +8856,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -9002,7 +9003,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9065,10 +9066,10 @@
 - Wooden Legs&lt;br&gt;
 - High-Density Foam Cushions&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige or Blue; dimensions: 92 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Beige or Blue; dimensions: 66 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Beige or Blue or Gray&lt;br&gt;
+- Loveseat: color: Beige or Blue or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like Fabric.&lt;br&gt;
-Color: Beige or Blue&lt;br&gt;
+Color: Beige or Blue or Gray&lt;br&gt;
 Weight: 297 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9153,7 +9154,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9207,18 +9208,19 @@
       <c r="G60" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GIOVANNI Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Gray tones, the Linen-like Fabric build keeps the look polished and practical.&lt;br&gt;
+GIOVANNI Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Linen-like Fabric construction and Beige or Blue tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 92 1/2"W X 40 1/2"D X 40 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
+- Beige or Blue&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Wooden Legs&lt;br&gt;
 - High-Density Foam Cushions&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray; dimensions: 92 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Gray; dimensions: 66 1 or 2" W x 40 1 or 2"D x 40 1 or 2" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Beige or Blue or Gray&lt;br&gt;
+- Loveseat: color: Beige or Blue or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Beige or Blue or Gray&lt;br&gt;
 Weight: 297 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9303,7 +9305,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9363,11 +9365,11 @@
 - Pillow Top Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Sofa: color: Powder Blue; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Powder Blue; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
-Color: Powder Blue&lt;br&gt;
-Weight: 365.2 lbs&lt;/p&gt;</t>
+- Sofa: color: Powder Blue or Dark Gray or White&lt;br&gt;
+- Loveseat: color: Powder Blue or Dark Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal, Others.&lt;br&gt;
+Color: Powder Blue or Dark Gray or White&lt;br&gt;
+Weight: 365.2 or 378.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="39" t="inlineStr">
@@ -9451,7 +9453,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9505,17 +9507,17 @@
       <c r="G62" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GLARUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Metal, then finished in Dark Gray tones to suit a range of interiors.&lt;br&gt;
+GLARUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Powder Blue tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Pillow Top Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Gray; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Dark Gray; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
-Weight: 378.8 lbs&lt;/p&gt;</t>
+- Sofa: color: Powder Blue or Dark Gray or White&lt;br&gt;
+- Loveseat: color: Powder Blue or Dark Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal, Others.&lt;br&gt;
+Color: Powder Blue or Dark Gray or White&lt;br&gt;
+Weight: 365.2 or 378.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="39" t="inlineStr">
@@ -9599,7 +9601,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9653,17 +9655,17 @@
       <c r="G63" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GLARUS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leather Match, Metal, construction and White tones, it blends durability with visual warmth.&lt;br&gt;
+GLARUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Metal, and finished in Powder Blue tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 38.2"L X 36.2"W X 38.6"H, LOVESEAT: 59.8"L X 36.2"W X 38.6"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Pillow Top Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Sofa: color: Off-White; dimensions: 82" W x 36"D x 38.5" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Off-White; dimensions: 60" W x 36"D x 38.5" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leather Match, Metal.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 365.2 lbs&lt;/p&gt;</t>
+- Sofa: color: Powder Blue or Dark Gray or White&lt;br&gt;
+- Loveseat: color: Powder Blue or Dark Gray or White&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Metal, Others.&lt;br&gt;
+Color: Powder Blue or Dark Gray or White&lt;br&gt;
+Weight: 365.2 or 378.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="39" t="inlineStr">
@@ -9747,7 +9749,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9896,7 +9898,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -10044,7 +10046,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10189,7 +10191,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10240,7 +10242,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 HIERONYMUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
-Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46") Included items and dimensions:&lt;br&gt;
+Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46")&lt;br&gt;
 - Manual Sofa: color: Dark Brown; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
 - Manual Loveseat w/ Console: color: Dark Brown; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
 Weight: 444 lbs&lt;/p&gt;</t>
@@ -10315,7 +10317,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10365,10 +10367,10 @@
       <c r="G68" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HIERONYMUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
-Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46") Included items and dimensions:&lt;br&gt;
-- Manual Sofa: color: Dark Gray; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
-- Manual Loveseat w/ Console: color: Dark Gray; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
+HIERONYMUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 92"W X 40.5"D X 40"H (SEAT HT: 20", SEAT DP: 23.5-46")&lt;br&gt;
+- Manual Sofa: color: Dark Brown; dimensions: 92" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
+- Manual Loveseat w/ Console: color: Dark Brown; dimensions: 80.5" W x 40.5"D x 40" H (SEAT HT: 20", SEAT DP: 23.5-46"); feature: Transitional&lt;br&gt;
 Weight: 444 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10441,7 +10443,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10504,10 +10506,10 @@
 - Low Flared Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige; dimensions: 101" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Beige; dimensions: 75" L x 44" W x 40" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Beige or Gray&lt;br&gt;
+- Loveseat: color: Beige or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Gray&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10592,7 +10594,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10646,7 +10648,7 @@
       <c r="G70" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOLBORN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Chenille, Solid Wood and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+HOLBORN Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Beige tones, the Chenille, Solid Wood build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 101"L X 44"W X 40"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - T-Seat Cushion&lt;br&gt;
@@ -10655,10 +10657,10 @@
 - Low Flared Arms&lt;br&gt;
 - Welt Trim&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray; dimensions: 101" L x 44" W x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Gray; dimensions: 75" L x 44" W x 40" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Beige or Gray&lt;br&gt;
+- Loveseat: color: Beige or Gray&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Beige or Gray&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10743,7 +10745,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -10881,7 +10883,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -11027,7 +11029,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -11173,7 +11175,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11321,7 +11323,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11384,10 +11386,10 @@
 - Curved Shelter Arms&lt;br&gt;
 - Accent Pillows&lt;br&gt;
 - High Density Foam Cushions Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Gray; dimensions: 98" L x 40" W x 38" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Gray; dimensions: 74" L x 40" W x 38" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Light Gray or Ivory&lt;br&gt;
+- Loveseat: color: Light Gray or Ivory&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Light Gray or Ivory&lt;br&gt;
 Weight: 350 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11472,7 +11474,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -11526,7 +11528,7 @@
       <c r="G76" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JARROW Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Linen-like Fabric, Solid Wood and finished in Ivory tones for a clean, cohesive look.&lt;br&gt;
+JARROW Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Light Gray tones, the Linen-like Fabric, Solid Wood build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 98"L X 40"W X 38"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Plush Back Cushions&lt;br&gt;
@@ -11535,10 +11537,10 @@
 - Curved Shelter Arms&lt;br&gt;
 - Accent Pillows&lt;br&gt;
 - High Density Foam Cushions Included items and dimensions:&lt;br&gt;
-- Sofa: color: Ivory; dimensions: 98" L x 40" W x 38" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Ivory; dimensions: 74" L x 40" W x 38" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Light Gray or Ivory&lt;br&gt;
+- Loveseat: color: Light Gray or Ivory&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like Fabric, Solid Wood.&lt;br&gt;
-Color: Ivory&lt;br&gt;
+Color: Light Gray or Ivory&lt;br&gt;
 Weight: 350 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11623,7 +11625,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -11761,7 +11763,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -11900,7 +11902,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -12038,7 +12040,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -12181,7 +12183,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12327,7 +12329,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12391,10 +12393,10 @@
 - 100% Polyster Body Fabric&lt;br&gt;
 - Flared Arms&lt;br&gt;
 - Gray Oak Bracket Fee Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray; dimensions: 92" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Gray; dimensions: 67" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Sofa: color: Gray or Cream&lt;br&gt;
+- Loveseat: color: Gray or Cream&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Cream&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12479,7 +12481,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
@@ -12533,7 +12535,7 @@
       <c r="G83" s="14" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LEYTONSTONE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Cream tones, the Fabric, Foam, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+LEYTONSTONE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Foam, Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 92"L X 40"W X 37"H (SEAT HT: 20", SEAT DP: 25")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - T Seat Cushion&lt;br&gt;
@@ -12543,10 +12545,10 @@
 - 100% Polyster Body Fabric&lt;br&gt;
 - Flared Arms&lt;br&gt;
 - Gray Oak Bracket Fee Included items and dimensions:&lt;br&gt;
-- Sofa: color: Cream; dimensions: 92" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Cream; dimensions: 67" L x 40" W x 37" H (SEAT HT: 20", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Foam, Solid Wood.&lt;br&gt;
-Color: Cream&lt;br&gt;
+- Sofa: color: Gray or Cream&lt;br&gt;
+- Loveseat: color: Gray or Cream&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Foam, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Cream&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12631,7 +12633,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12776,7 +12778,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12922,7 +12924,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -12977,7 +12979,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LOUGHLIN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Solid Wood and finished in Light Brown tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: Sofa: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25")&lt;/p&gt;
+Product Dimensions: Sofa: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25") / Sofa: 98"L X 39"W X 38"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Ultra Soft Back Cushions and Accent Pillows w/ Channel Tufting&lt;br&gt;
 - Bolt-on Removable Arms for Easy Door Access&lt;br&gt;
@@ -12985,10 +12987,10 @@
 - Padded Arms&lt;br&gt;
 - T-Seat Cushions&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Brown; dimensions: 98" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Brown; dimensions: 72" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+- Sofa: color: Light Brown or Gun Metal&lt;br&gt;
+- Loveseat: color: Light Brown or Gun Metal&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Light Brown&lt;br&gt;
+Color: Light Brown or Gun Metal&lt;br&gt;
 Weight: 292 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13073,7 +13075,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -13127,8 +13129,8 @@
       <c r="G87" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LOUGHLIN Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Chenille, Solid Wood, then finished in Gun Metal tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: Sofa: 98"L X 39"W X 38"H&lt;/p&gt;
+LOUGHLIN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Chenille, Solid Wood and finished in Light Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 98"L X 39"W X 38"H (SEAT HT: 21", SEAT DP: 25") / Sofa: 98"L X 39"W X 38"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Ultra Soft Back Cushions and Accent Pillows w/ Channel Tufting&lt;br&gt;
 - Bolt-on Removable Arms for Easy Door Access&lt;br&gt;
@@ -13136,10 +13138,10 @@
 - Padded Arms&lt;br&gt;
 - T-Seat Cushions&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gun Metal; dimensions: 98" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Gun Metal; dimensions: 72" W x 39"D x 38" H (SEAT HT: 21", SEAT DP: 25"); feature: Transitional&lt;/p&gt;
+- Sofa: color: Light Brown or Gun Metal&lt;br&gt;
+- Loveseat: color: Light Brown or Gun Metal&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Gun Metal&lt;br&gt;
+Color: Light Brown or Gun Metal&lt;br&gt;
 Weight: 292 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13224,7 +13226,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13285,10 +13287,10 @@
 - Loose Pillow Backs&lt;br&gt;
 - Wooden Legs&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa w/ Pillows: color: Dark Gray; dimensions: 73 1 or 4" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;br&gt;
-- Loveseat w/ Pillows: color: Dark Gray; dimensions: 51 1 or 2" L x 32 5 or 8" WX 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+- Sofa w/ Pillows: color: Dark Gray or Light Gray&lt;br&gt;
+- Loveseat w/ Pillows: color: Dark Gray or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Dark Gray or Light Gray&lt;br&gt;
 Weight: 206.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13373,7 +13375,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13427,17 +13429,17 @@
       <c r="G89" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LYNDA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Chenille, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.&lt;br&gt;
+LYNDA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Chenille, Solid Wood, then finished in Dark Gray tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 75 5/8"L X 32 5/8"W X 34 5/8"H (SEAT HT: 17 3/4", SEAT DP: 20 1/2")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Biscuit Tufting&lt;br&gt;
 - Loose Pillow Backs&lt;br&gt;
 - Wooden Legs&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa w/ Pillows: color: Light Gray; dimensions: 73 1 or 4" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;br&gt;
-- Loveseat w/ Pillows: color: Light Gray; dimensions: 51 1 or 2" L x 32 5 or 8" W x 34 5 or 8" H (SEAT HT: 17 3 or 4", SEAT DP: 22"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+- Sofa w/ Pillows: color: Dark Gray or Light Gray&lt;br&gt;
+- Loveseat w/ Pillows: color: Dark Gray or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Dark Gray or Light Gray&lt;br&gt;
 Weight: 206.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13522,7 +13524,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13663,7 +13665,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -13808,7 +13810,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -13955,7 +13957,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -14102,7 +14104,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -14243,7 +14245,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -14389,7 +14391,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -14528,7 +14530,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -14583,7 +14585,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MEZZANOTTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Real Italian Leather, Engineered Wood, construction and Midnight Blue tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: SOFA: 90"L X 38 1/2"W X 32 1/2"H (SEAT HT: 17", SEAT DP: 23 1/2")&lt;/p&gt;
+Product Dimensions: SOFA: 90"L X 38 1/2"W X 32 1/2"H (SEAT HT: 17", SEAT DP: 23 1/2") / Sofa: 90"L X 38 1/2"W X 32 1/2"H, LV: 77.2"L X 38 1/2"W X 32 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Wide Seating w/ Metal Leg &amp;amp; Track Arms&lt;br&gt;
 - High Density Foam Seat&lt;br&gt;
@@ -14592,9 +14594,9 @@
 - Attached Seat and Back Cushions w/ Welt&lt;br&gt;
 - 100% Made in Italy&lt;br&gt;
 - Fully Upholstered in Leather on all Sides&lt;/p&gt;
-&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
-Color: Midnight Blue&lt;br&gt;
-Weight: 264 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood, Others.&lt;br&gt;
+Color: Midnight Blue or Gray&lt;br&gt;
+Weight: 264 or 260.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" s="16" t="inlineStr">
@@ -14678,7 +14680,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -14732,19 +14734,19 @@
       <c r="G98" s="16" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MEZZANOTTE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Gray tones, the Real Italian Leather, Engineered Wood, build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: Sofa: 90"L X 38 1/2"W X 32 1/2"H, LV: 77.2"L X 38 1/2"W X 32 1/2"H&lt;/p&gt;
+MEZZANOTTE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. With Real Italian Leather, Engineered Wood, construction and Midnight Blue tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 38 1/2"W X 32 1/2"H (SEAT HT: 17", SEAT DP: 23 1/2") / Sofa: 90"L X 38 1/2"W X 32 1/2"H, LV: 77.2"L X 38 1/2"W X 32 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Wide Seating w/ Metal Leg &amp;amp; Track Arms&lt;br&gt;
 - High Density Foam Seat&lt;br&gt;
 - Foam and Fiber-filled Back Pillow&lt;br&gt;
 - Webbing Back and Ring Seat Suspension&lt;br&gt;
 - Attached Seat and Back Cushions w/ Welt&lt;br&gt;
-- Fully Upholstered in Leather on all Sides&lt;br&gt;
-- Made in Italy&lt;/p&gt;
-&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 260.1 lbs&lt;/p&gt;</t>
+- 100% Made in Italy&lt;br&gt;
+- Fully Upholstered in Leather on all Sides&lt;/p&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood, Others.&lt;br&gt;
+Color: Midnight Blue or Gray&lt;br&gt;
+Weight: 264 or 260.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" s="16" t="inlineStr">
@@ -14828,7 +14830,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14975,7 +14977,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -15119,7 +15121,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -15268,7 +15270,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15417,7 +15419,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15563,7 +15565,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15614,12 +15616,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MORETAINE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22")&lt;br&gt;
 - Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
 - Beige Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
 - Beige Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
 - Beige Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-Weight: 211 lbs&lt;/p&gt;</t>
+Weight: 211 or 197.22 or 195.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="37" t="inlineStr">
@@ -15691,7 +15693,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -15741,13 +15743,13 @@
       <c r="G105" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORETAINE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
-- Black Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
-- Black Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
-- Black Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-- Black Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-Weight: 197.22 lbs&lt;/p&gt;</t>
+MORETAINE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22")&lt;br&gt;
+- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Beige Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 211 or 197.22 or 195.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" s="37" t="inlineStr">
@@ -15819,7 +15821,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -15869,13 +15871,13 @@
       <c r="G106" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORETAINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
-Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22") Included items and dimensions:&lt;br&gt;
-- Dark Gray Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
-- Dark Gray Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
-- Dark Gray Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-- Dark Gray Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
-Weight: 195.5 lbs&lt;/p&gt;</t>
+MORETAINE Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 61"W X 34"D X 35"H (SEAT HT: 18", SEAT DP: 22")&lt;br&gt;
+- Beige Sofa Base: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Sofa Arm &amp;amp; Pillows: dimensions: 85" W x 34"D x 35" H&lt;br&gt;
+- Beige Loveseat Base: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+- Beige Loveseat Arm &amp;amp; Pillows: dimensions: 61" W x 34"D x 35" H&lt;br&gt;
+Weight: 211 or 197.22 or 195.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" s="37" t="inlineStr">
@@ -15947,7 +15949,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -16093,7 +16095,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -16239,7 +16241,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -16384,7 +16386,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16530,7 +16532,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -16592,10 +16594,10 @@
 - Single Cushion Seat&lt;br&gt;
 - Turned Legs&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Ivory; dimensions: 90" W x 41"D x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Ivory; dimensions: 65" W x 41"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Burlap Weave, Solid Wood.&lt;br&gt;
-Color: Ivory&lt;br&gt;
+- Sofa: color: Ivory or Gray&lt;br&gt;
+- Loveseat: color: Ivory or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Burlap Weave, Solid Wood, Others.&lt;br&gt;
+Color: Ivory or Gray&lt;br&gt;
 Weight: 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16680,7 +16682,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -16734,18 +16736,18 @@
       <c r="G112" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEFYN Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Burlap Weave, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+NEFYN Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Ivory tones, the Burlap Weave, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 90"W X 41"D X 40"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Medium Density Foam&lt;br&gt;
 - Sloped Arms&lt;br&gt;
 - Single Cushion Seat&lt;br&gt;
-- Tapered Block Legs&lt;br&gt;
+- Turned Legs&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray; dimensions: 90" W x 41"D x 40" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Gray; dimensions: 65" W x 41"D x 40" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Burlap Weave, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Sofa: color: Ivory or Gray&lt;br&gt;
+- Loveseat: color: Ivory or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Burlap Weave, Solid Wood, Others.&lt;br&gt;
+Color: Ivory or Gray&lt;br&gt;
 Weight: 289 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16830,7 +16832,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -16894,10 +16896,10 @@
 - Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
 - Kiln-Dried Wooden Frame&lt;br&gt;
 - Bracket Wooden Feet Included items and dimensions:&lt;br&gt;
-- MEADOWS Sofa: color: Ash Green or Ivory; dimensions: 101" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;br&gt;
-- MEADOWS Loveseat: color: Ash Green or Ivory; dimensions: 75" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
-Color: Ash Green or Ivory&lt;br&gt;
+- MEADOWS Sofa: color: Ash Green or Ivory or Sand or Caramel&lt;br&gt;
+- MEADOWS Loveseat: color: Ash Green or Ivory or Sand or Caramel&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood, Others.&lt;br&gt;
+Color: Ash Green or Ivory or Sand or Caramel&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16982,7 +16984,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -17036,20 +17038,20 @@
       <c r="G114" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEW MEADOWS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Fabric, Leatherette, Foam, Solid Wood, and finished in Sand or Caramel tones for a clean, cohesive look.&lt;br&gt;
+NEW MEADOWS Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Finished in Ash Green or Ivory tones, the Fabric, Leatherette, Foam, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 101"L X 44"W X 40"H (SEAT HT: 21", SEAT DP: 30")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Sand or Caramel&lt;br&gt;
+- Ash Green or Ivory&lt;br&gt;
 - T Seat Cushion&lt;br&gt;
 - 100% Polyester Body Fabric&lt;br&gt;
 - Spring Seat &amp;amp; Webbing Back Suspension&lt;br&gt;
 - Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
 - Kiln-Dried Wooden Frame&lt;br&gt;
 - Bracket Wooden Feet Included items and dimensions:&lt;br&gt;
-- MEADOWS Sofa: color: Sand or Caramel; dimensions: 101" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;br&gt;
-- MEADOWS Loveseat: color: Sand or Caramel; dimensions: 75" L x 44" W x 40" H (SEAT HT: 21", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
-Color: Sand or Caramel&lt;br&gt;
+- MEADOWS Sofa: color: Ash Green or Ivory or Sand or Caramel&lt;br&gt;
+- MEADOWS Loveseat: color: Ash Green or Ivory or Sand or Caramel&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood, Others.&lt;br&gt;
+Color: Ash Green or Ivory or Sand or Caramel&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17134,7 +17136,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -17199,10 +17201,10 @@
 - Arched Black Design&lt;br&gt;
 - Round Bun Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Gray; dimensions: 93" L x 36" W x 40" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Gray; dimensions: 70" L x 36" W x 40" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Sofa: color: Gray or Ivory or Brown or Gold&lt;br&gt;
+- Loveseat: color: Gray or Ivory or Brown or Gold&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Ivory or Brown or Gold&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17287,7 +17289,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -17341,7 +17343,7 @@
       <c r="G116" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEWDALE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Finished in Ivory tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+NEWDALE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 93"L X 36"W X 40"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
@@ -17352,10 +17354,10 @@
 - Arched Black Design&lt;br&gt;
 - Round Bun Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Ivory; dimensions: 93" L x 36" W x 40" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Ivory; dimensions: 70" L x 36" W x 40" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Ivory&lt;br&gt;
+- Sofa: color: Gray or Ivory or Brown or Gold&lt;br&gt;
+- Loveseat: color: Gray or Ivory or Brown or Gold&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Ivory or Brown or Gold&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17440,7 +17442,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -17494,11 +17496,10 @@
       <c r="G117" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NEWDALE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood, and finished in Brown or Gold tones for a clean, cohesive look.&lt;br&gt;
+NEWDALE Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Chenille, Solid Wood, construction and Gray tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 93"L X 36"W X 40"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Brown or Gold&lt;br&gt;
 - Medium Density Foam&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Wood Trim&lt;br&gt;
@@ -17506,10 +17507,10 @@
 - Arched Black Design&lt;br&gt;
 - Round Bun Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Brown or Gold; dimensions: 93" L x 36" W x 40" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Brown or Gold; dimensions: 70" L x 36" W x 40" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Brown or Gold&lt;br&gt;
+- Sofa: color: Gray or Ivory or Brown or Gold&lt;br&gt;
+- Loveseat: color: Gray or Ivory or Brown or Gold&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Ivory or Brown or Gold&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17594,7 +17595,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -17740,7 +17741,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -17887,7 +17888,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -17952,11 +17953,11 @@
 - Rolled Arms&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Cherry or Beige; dimensions: 94 1 or 2" x 41 3 or 4" x 26"; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Cherry or Beige; dimensions: 69 3 or 4" x 41 3 or 4" x 26"; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Dark Cherry or Beige&lt;br&gt;
-Weight: 414.9 lbs&lt;/p&gt;</t>
+- Sofa: color: Dark Cherry or Beige or Dark Cherry or Brown&lt;br&gt;
+- Loveseat: color: Dark Cherry or Beige or Dark Cherry or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others or Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Dark Cherry or Beige or Dark Cherry or Brown&lt;br&gt;
+Weight: 414.9 or 426.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" s="22" t="inlineStr">
@@ -18040,7 +18041,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -18094,22 +18095,22 @@
       <c r="G121" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PALENCIA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, then finished in Dark Cherry or Brown tones to suit a range of interiors.&lt;br&gt;
+PALENCIA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Built from Fabric, Solid Wood, and finished in Dark Cherry or Beige tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: 94 1/2" X 41 3/4" X 26"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Dark Cherry or Brown&lt;br&gt;
+- Dark Cherry or Beige&lt;br&gt;
 - Button Tufted Back&lt;br&gt;
 - Carved Details&lt;br&gt;
 - Reversible Seat Cushion w/ Welt&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Cherry or Brown; dimensions: 94 1 or 2" x 41 3 or 4" x 26"; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Cherry or Brown; dimensions: 69 3 or 4" x 41 3 or 4" x 26"; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
-Color: Dark Cherry or Brown&lt;br&gt;
-Weight: 426.8 lbs&lt;/p&gt;</t>
+- Sofa: color: Dark Cherry or Beige or Dark Cherry or Brown&lt;br&gt;
+- Loveseat: color: Dark Cherry or Beige or Dark Cherry or Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others or Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Dark Cherry or Beige or Dark Cherry or Brown&lt;br&gt;
+Weight: 414.9 or 426.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" s="22" t="inlineStr">
@@ -18193,7 +18194,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -18342,7 +18343,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -18487,7 +18488,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -18635,7 +18636,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18782,7 +18783,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -18925,7 +18926,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -18989,10 +18990,10 @@
 - High-Density Foam Cushions&lt;br&gt;
 - Loose Back Pillows&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Burgundy or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Burgundy or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional&lt;/p&gt;
+- Sofa: color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;br&gt;
+- Loveseat: color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
-Color: Burgundy or Dark Brown&lt;br&gt;
+Color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19077,7 +19078,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -19131,20 +19132,20 @@
       <c r="G128" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-QUIRINO Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Leatherette, Solid Wood construction and Light Brown or Dark Brown tones, it blends durability with visual warmth.&lt;br&gt;
+QUIRINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Chenille, Leatherette, Solid Wood, then finished in Burgundy or Dark Brown tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 93"L X 38"W X 42"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Light Brown or Dark Brown&lt;br&gt;
+- Burgundy or Dark Brown&lt;br&gt;
 - Intricate Wood Trim&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - High-Density Foam Cushions&lt;br&gt;
 - Loose Back Pillows&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Brown or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Light Brown or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional&lt;/p&gt;
+- Sofa: color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;br&gt;
+- Loveseat: color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
-Color: Light Brown or Dark Brown&lt;br&gt;
+Color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19229,7 +19230,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -19283,20 +19284,20 @@
       <c r="G129" s="26" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-QUIRINO Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Tan or Dark Brown tones, the Chenille, Leatherette, Solid Wood build keeps the look polished and practical.&lt;br&gt;
+QUIRINO Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. Crafted with Chenille, Leatherette, Solid Wood, then finished in Burgundy or Dark Brown tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 93"L X 38"W X 42"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Tan or Dark Brown&lt;br&gt;
+- Burgundy or Dark Brown&lt;br&gt;
 - Intricate Wood Trim&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - High-Density Foam Cushions&lt;br&gt;
 - Loose Back Pillows&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Tan or Dark Brown; dimensions: 93" L x 38" W x 42" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Tan or Dark Brown; dimensions: 71" L x 38" W x 42" H; feature: Traditional&lt;/p&gt;
+- Sofa: color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;br&gt;
+- Loveseat: color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Leatherette, Solid Wood.&lt;br&gt;
-Color: Tan or Dark Brown&lt;br&gt;
+Color: Burgundy or Dark Brown or Light Brown or Dark Brown or Tan or Dark Brown&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -19381,7 +19382,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -19445,9 +19446,9 @@
 - Darl Brown Welting&lt;br&gt;
 - Rolled Arms With Wood Trim&lt;br&gt;
 - Round Bun Feet Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Brown; dimensions: 94" L x 37" W x 44" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Brown; dimensions: 72" L x 37" W x 44" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+- Sofa: color: Dark Brown&lt;br&gt;
+- Loveseat: color: Dark Brown&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
 Color: Dark Brown&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
@@ -19529,7 +19530,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -19583,7 +19584,7 @@
       <c r="G131" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RONJA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Finished in Dark Brown tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;/p&gt;
+RONJA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. With Chenille, Solid Wood, construction and Dark Brown tones, it blends durability with visual warmth.&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
 - Damask Fabric&lt;br&gt;
@@ -19593,9 +19594,9 @@
 - Darl Brown Welting&lt;br&gt;
 - Rolled Arms With Wood Trim&lt;br&gt;
 - Round Bun Feet Included items and dimensions:&lt;br&gt;
-- Sofa: color: Black; dimensions: 94" L x 37" W x 44" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Black; dimensions: 72" L x 37" W x 44" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
+- Sofa: color: Dark Brown&lt;br&gt;
+- Loveseat: color: Dark Brown&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others.&lt;br&gt;
 Color: Dark Brown&lt;br&gt;
 Weight: 330 lbs&lt;/p&gt;</t>
         </is>
@@ -19677,7 +19678,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19823,7 +19824,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19969,7 +19970,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -20115,7 +20116,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -20179,10 +20180,10 @@
 - Loose Back Pillows&lt;br&gt;
 - Cabriole Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Gray; dimensions: 91" L x 37" W x 36" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Gray; dimensions: 71" L x 37" W x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+- Sofa: color: Light Gray or Purple or Navy&lt;br&gt;
+- Loveseat: color: Light Gray or Purple or Navy&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others or Small Weave Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Light Gray or Purple or Navy&lt;br&gt;
 Weight: 276 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20267,7 +20268,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -20321,7 +20322,7 @@
       <c r="G136" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SISSETON Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood, and finished in Purple tones for a clean, cohesive look.&lt;br&gt;
+SISSETON Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 91"L X 37"W X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Medium Density Foam&lt;br&gt;
@@ -20331,10 +20332,10 @@
 - Loose Back Pillows&lt;br&gt;
 - Cabriole Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Purple; dimensions: 91" L x 37" W x 36" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Purple; dimensions: 71" L x 37" W x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Purple&lt;br&gt;
+- Sofa: color: Light Gray or Purple or Navy&lt;br&gt;
+- Loveseat: color: Light Gray or Purple or Navy&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others or Small Weave Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Light Gray or Purple or Navy&lt;br&gt;
 Weight: 276 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20419,7 +20420,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -20473,7 +20474,7 @@
       <c r="G137" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SISSETON Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Small Weave Chenille, Solid Wood, then finished in Navy tones to suit a range of interiors.&lt;br&gt;
+SISSETON Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Light Gray tones, the Chenille, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 91"L X 37"W X 36"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Medium Density Foam&lt;br&gt;
@@ -20483,10 +20484,10 @@
 - Loose Back Pillows&lt;br&gt;
 - Cabriole Feet&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Navy; dimensions: 91" L x 37" W x 36" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Navy; dimensions: 71" L x 37" W x 36" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Small Weave Chenille, Solid Wood.&lt;br&gt;
-Color: Navy&lt;br&gt;
+- Sofa: color: Light Gray or Purple or Navy&lt;br&gt;
+- Loveseat: color: Light Gray or Purple or Navy&lt;/p&gt;
+&lt;p&gt;Materials: Chenille, Solid Wood, Others or Small Weave Chenille, Solid Wood, Others.&lt;br&gt;
+Color: Light Gray or Purple or Navy&lt;br&gt;
 Weight: 276 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20571,7 +20572,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -20636,10 +20637,10 @@
 - Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
 - Kiln Dried Wooden Frame&lt;br&gt;
 - Bracket Wooden Fee Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Gray or Brown; dimensions: 96" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Gray or Brown; dimensions: 71" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
-Color: Light Gray or Brown&lt;br&gt;
+- Sofa: color: Light Gray or Brown or Pewter or Gray&lt;br&gt;
+- Loveseat: color: Light Gray or Brown or Pewter or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood, Others.&lt;br&gt;
+Color: Light Gray or Brown or Pewter or Gray&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20724,7 +20725,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -20778,10 +20779,10 @@
       <c r="G139" s="14" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SKYLINE Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Leatherette, Foam, Solid Wood, and finished in Pewter or Gray tones for a clean, cohesive look.&lt;br&gt;
+SKYLINE Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Light Gray or Brown tones, the Fabric, Leatherette, Foam, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 96"L X 44"W X 40"H (SEAT HT: 22", SEAT DP: 30")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Pewter or Gray&lt;br&gt;
+- Light Gray or Brown&lt;br&gt;
 - Oversized Sofa&lt;br&gt;
 - T Seat Cushion&lt;br&gt;
 - Sloped Track Arms w/ Welt&lt;br&gt;
@@ -20789,10 +20790,10 @@
 - Reversible Back Pillows &amp;amp; Accent Pillows w/ Fiber Fill&lt;br&gt;
 - Kiln Dried Wooden Frame&lt;br&gt;
 - Bracket Wooden Fee Included items and dimensions:&lt;br&gt;
-- Sofa: color: Pewter or Gray; dimensions: 96" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;br&gt;
-- Loveseat: color: Pewter or Gray; dimensions: 71" L x 44" W x 40" H (SEAT HT: 22", SEAT DP: 30"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood.&lt;br&gt;
-Color: Pewter or Gray&lt;br&gt;
+- Sofa: color: Light Gray or Brown or Pewter or Gray&lt;br&gt;
+- Loveseat: color: Light Gray or Brown or Pewter or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Foam, Solid Wood, Others.&lt;br&gt;
+Color: Light Gray or Brown or Pewter or Gray&lt;br&gt;
 Weight: 225 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20877,7 +20878,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -21025,7 +21026,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -21173,7 +21174,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -21236,10 +21237,10 @@
 - Intricate Wood Trim&lt;br&gt;
 - High-Density Foam Cushions&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Brown or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Brown or Gold; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
-Color: Brown or Gold&lt;br&gt;
+- Sofa: color: Brown or Gold or Wine or Gold&lt;br&gt;
+- Loveseat: color: Brown or Gold or Wine or Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Brown or Gold or Wine or Gold&lt;br&gt;
 Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -21324,7 +21325,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -21378,19 +21379,19 @@
       <c r="G143" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TABITHA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Traditional profile gives the space a refined, approachable look. Finished in Wine or Gold tones, the Fabric, Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+TABITHA Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Leatherette, Solid Wood, construction and Brown or Gold tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 94"L X 37"W X 37.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Wine or Gold&lt;br&gt;
+- Brown or Gold&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Intricate Wood Trim&lt;br&gt;
 - High-Density Foam Cushions&lt;br&gt;
 - Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Wine or Gold; dimensions: 94" L x 37" W x 41" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Wine or Gold; dimensions: 72" L x 37" W x 41" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood.&lt;br&gt;
-Color: Wine or Gold&lt;br&gt;
+- Sofa: color: Brown or Gold or Wine or Gold&lt;br&gt;
+- Loveseat: color: Brown or Gold or Wine or Gold&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Brown or Gold or Wine or Gold&lt;br&gt;
 Weight: 295 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -21475,7 +21476,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -21620,7 +21621,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -21762,7 +21763,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -21910,7 +21911,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -21961,10 +21962,10 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 VALDOSTA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
-Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 25.5") Included items and dimensions:&lt;br&gt;
+Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 25.5") / 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 26")&lt;br&gt;
 - Sofa: color: Beige or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam&lt;br&gt;
 - Loveseat: color: Beige or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam&lt;br&gt;
-Weight: 344 lbs&lt;/p&gt;</t>
+Weight: 344 or 343 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="18" t="inlineStr">
@@ -22036,7 +22037,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -22086,11 +22087,11 @@
       <c r="G148" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VALDOSTA Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery upholstery set is made to fit naturally into the room.&lt;br&gt;
-Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 26") Included items and dimensions:&lt;br&gt;
-- Sofa: color: Black or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam&lt;br&gt;
-- Loveseat: color: Black or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 26"); feature: Glam&lt;br&gt;
-Weight: 343 lbs&lt;/p&gt;</t>
+VALDOSTA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery upholstery set, it is designed to coordinate with matching pieces.&lt;br&gt;
+Product Dimensions: 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 25.5") / 92"W X 35"D X 35"H (SEAT HT: 19", SEAT DP: 26")&lt;br&gt;
+- Sofa: color: Beige or Gold; dimensions: 92" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam&lt;br&gt;
+- Loveseat: color: Beige or Gold; dimensions: 68" W x 35"D x 35" H (SEAT HT: 19", SEAT DP: 25.5"); feature: Glam&lt;br&gt;
+Weight: 344 or 343 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="18" t="inlineStr">
@@ -22162,7 +22163,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -22227,10 +22228,10 @@
 - Rolled Arms&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Cherry or Beige; dimensions: 90" W x 38"D x 44.5" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Cherry or Beige; dimensions: 69.5" W x 38"D x 44.5" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Dark Cherry or Beige&lt;br&gt;
+- Sofa: color: Dark Cherry or Beige or Dark Cherry or Light Brown&lt;br&gt;
+- Loveseat: color: Dark Cherry or Beige or Dark Cherry or Light Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Dark Cherry or Beige or Dark Cherry or Light Brown&lt;br&gt;
 Weight: 350.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22315,7 +22316,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -22369,21 +22370,21 @@
       <c r="G150" s="20" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VERACRUZ Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Traditional character adds definition without feeling heavy. With Fabric, Solid Wood, construction and Dark Cherry or Light Brown tones, it blends durability with visual warmth.&lt;br&gt;
+VERACRUZ Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Traditional styling keeps the room feeling polished yet comfortable. Crafted with Fabric, Solid Wood, then finished in Dark Cherry or Beige tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: Sofa: 89.75"L X 38"W X 45"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Traditional&lt;br&gt;
-- Dark Cherry or Light Brown&lt;br&gt;
+- Dark Cherry or Beige&lt;br&gt;
 - Button Tufted Back&lt;br&gt;
 - Carved Details&lt;br&gt;
 - Jacquard Pattern Box Seat Cushion w/ Welt&lt;br&gt;
 - Rolled Arms&lt;br&gt;
 - Nailhead Trim&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Cherry or Light Brown; dimensions: 90" W x 38"D x 44.5" H; feature: Traditional&lt;br&gt;
-- Loveseat: color: Dark Cherry or Light Brown; dimensions: 69.5" W x 38"D x 44.5" H; feature: Traditional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Dark Cherry or Light Brown&lt;br&gt;
+- Sofa: color: Dark Cherry or Beige or Dark Cherry or Light Brown&lt;br&gt;
+- Loveseat: color: Dark Cherry or Beige or Dark Cherry or Light Brown&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Dark Cherry or Beige or Dark Cherry or Light Brown&lt;br&gt;
 Weight: 350.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22468,7 +22469,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -22532,10 +22533,10 @@
 - High Density Foam w/ Pocket Coils&lt;br&gt;
 - Kiln-dried Hardwood&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Black; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
-- Loveseat: color: Black; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+- Sofa: color: Black or Charcoal Gray or Off-White&lt;br&gt;
+- Loveseat: color: Black or Charcoal Gray or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood, Others.&lt;br&gt;
+Color: Black or Charcoal Gray or Off-White&lt;br&gt;
 Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22620,7 +22621,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -22674,7 +22675,7 @@
       <c r="G152" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VERDAL Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Boucle, Solid Wood, and finished in Charcoal Gray tones for a clean, cohesive look.&lt;br&gt;
+VERDAL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black tones, the Boucle, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Tuxedo-inspired Design&lt;br&gt;
@@ -22684,10 +22685,10 @@
 - High Density Foam w/ Pocket Coils&lt;br&gt;
 - Kiln-dried Hardwood&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Charcoal Gray; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
-- Loveseat: color: Charcoal Gray; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
-Color: Charcoal Gray&lt;br&gt;
+- Sofa: color: Black or Charcoal Gray or Off-White&lt;br&gt;
+- Loveseat: color: Black or Charcoal Gray or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood, Others.&lt;br&gt;
+Color: Black or Charcoal Gray or Off-White&lt;br&gt;
 Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22772,7 +22773,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -22826,7 +22827,7 @@
       <c r="G153" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VERDAL Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery upholstery set, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Boucle, Solid Wood, then finished in Off-White tones to suit a range of interiors.&lt;br&gt;
+VERDAL Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Black tones, the Boucle, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 86 1/2"L X 34 1/2"W X 31 1/2"H (SEAT HT: 18 1/2", SEAT DP: 23")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Tuxedo-inspired Design&lt;br&gt;
@@ -22836,10 +22837,10 @@
 - High Density Foam w/ Pocket Coils&lt;br&gt;
 - Kiln-dried Hardwood&lt;br&gt;
 - Wooden Legs Included items and dimensions:&lt;br&gt;
-- Sofa: color: Off-White; dimensions: 87 1 or 4" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;br&gt;
-- Loveseat: color: Off-White; dimensions: 67 1 or 2" L x 35 1 or 4" W x 30 1 or 4" H (SEAT HT: 19", SEAT DP: 23"); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle, Solid Wood.&lt;br&gt;
-Color: Off-White&lt;br&gt;
+- Sofa: color: Black or Charcoal Gray or Off-White&lt;br&gt;
+- Loveseat: color: Black or Charcoal Gray or Off-White&lt;/p&gt;
+&lt;p&gt;Materials: Boucle, Solid Wood, Others.&lt;br&gt;
+Color: Black or Charcoal Gray or Off-White&lt;br&gt;
 Weight: 256 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22924,7 +22925,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -23070,7 +23071,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -23217,7 +23218,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -23363,7 +23364,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -23511,7 +23512,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -23658,7 +23659,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -23721,10 +23722,10 @@
 - Track Arms&lt;br&gt;
 - Tapered Block Legs&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- ACTION Sofa: color: Chocolate; dimensions: 83" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;br&gt;
-- ACTION Loveseat: color: Chocolate; dimensions: 61" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;/p&gt;
+- ACTION Sofa: color: Chocolate or Beige&lt;br&gt;
+- ACTION Loveseat: color: Chocolate or Beige&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Chocolate&lt;br&gt;
+Color: Chocolate or Beige&lt;br&gt;
 Weight: 202 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -23809,7 +23810,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23863,7 +23864,7 @@
       <c r="G160" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WEST ACTION Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery upholstery set, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Built from Chenille, Solid Wood and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
+WEST ACTION Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery upholstery set is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Finished in Chocolate tones, the Chenille, Solid Wood build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 83"L X 36"W X 39"H (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Box Seat Cushion&lt;br&gt;
@@ -23872,10 +23873,10 @@
 - Track Arms&lt;br&gt;
 - Tapered Block Legs&lt;br&gt;
 - Accent Pillows Included Included items and dimensions:&lt;br&gt;
-- ACTION Sofa: color: Beige; dimensions: 83" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;br&gt;
-- ACTION Loveseat: color: Beige; dimensions: 61" L x 36" W x 39" H (SEAT HT: 20", SEAT DP: 21"); feature: Contemporary&lt;/p&gt;
+- ACTION Sofa: color: Chocolate or Beige&lt;br&gt;
+- ACTION Loveseat: color: Chocolate or Beige&lt;/p&gt;
 &lt;p&gt;Materials: Chenille, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Chocolate or Beige&lt;br&gt;
 Weight: 202 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -23960,7 +23961,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -24107,7 +24108,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -24253,7 +24254,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -24313,11 +24314,11 @@
 - Drop-Down Table With Cup Holders on Sofa&lt;br&gt;
 - Storage Console and Cupholders on Love Seat&lt;br&gt;
 - Contrast Welt Included items and dimensions:&lt;br&gt;
-- Sofa: color: Brown; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Brown; dimensions: 79" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
-Weight: 428.5 lbs&lt;/p&gt;</t>
+- Sofa: color: Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Brown or Dark Gray&lt;br&gt;
+Weight: 428.5 or 430 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" s="41" t="inlineStr">
@@ -24401,7 +24402,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -24455,16 +24456,17 @@
       <c r="G164" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AGATA Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leatherette, Solid Wood, and finished in Dark Gray tones for a clean, cohesive look.&lt;br&gt;
+AGATA Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Finished in Brown tones, the Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Double Stitching&lt;br&gt;
-- Plush Cushions&lt;br&gt;
-- Recliners&lt;br&gt;
-- Console w/ Cup Holders&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
-Weight: 430 lbs&lt;/p&gt;</t>
+- Drop-Down Table With Cup Holders on Sofa&lt;br&gt;
+- Storage Console and Cupholders on Love Seat&lt;br&gt;
+- Contrast Welt Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Brown or Dark Gray&lt;br&gt;
+Weight: 428.5 or 430 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" s="41" t="inlineStr">
@@ -24548,7 +24550,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -24608,12 +24610,12 @@
 - Drop-Down Table With Cup Holders on Sofa&lt;br&gt;
 - Storage Console and Cupholders on Love Seat&lt;br&gt;
 - Contrast Welt Included items and dimensions:&lt;br&gt;
-- Sofa: color: Brown; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Brown; dimensions: 79" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
-- Glider Recliner: color: Brown; dimensions: 41.5" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
-Weight: 535.4 lbs&lt;/p&gt;</t>
+- Sofa: color: Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Brown or Dark Gray&lt;br&gt;
+- Glider Recliner: color: Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Brown or Dark Gray&lt;br&gt;
+Weight: 535.4 or 537.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H165" s="35" t="inlineStr">
@@ -24697,7 +24699,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -24751,16 +24753,18 @@
       <c r="G166" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AGATA Sofa and Loveseat and Chair creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Leatherette, Solid Wood, construction and Dark Gray tones, it blends durability with visual warmth.&lt;br&gt;
+AGATA Sofa and Loveseat and Chair offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leatherette, Solid Wood, then finished in Brown tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: Sofa: 87.3"L X 38.6"W X 41"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Double Stitching&lt;br&gt;
-- Plush Cushions&lt;br&gt;
-- Recliners&lt;br&gt;
-- Console w/ Cup Holders&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
-Weight: 537.6 lbs&lt;/p&gt;</t>
+- Drop-Down Table With Cup Holders on Sofa&lt;br&gt;
+- Storage Console and Cupholders on Love Seat&lt;br&gt;
+- Contrast Welt Included items and dimensions:&lt;br&gt;
+- Sofa: color: Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Brown or Dark Gray&lt;br&gt;
+- Glider Recliner: color: Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Brown or Dark Gray&lt;br&gt;
+Weight: 535.4 or 537.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H166" s="35" t="inlineStr">
@@ -24844,7 +24848,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -24908,8 +24912,8 @@
 - Pillow Top Arm &amp;amp; Accent Stitching&lt;br&gt;
 - 100% Made in Italy&lt;br&gt;
 - Fully Upholstered in Leather on all Sides&lt;/p&gt;
-&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood, Others.&lt;br&gt;
+Color: Gray or Taupe&lt;br&gt;
 Weight: 149 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -24994,7 +24998,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -25048,7 +25052,7 @@
       <c r="G168" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALTAMURA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Real Italian Leather, Engineered Wood, construction and Taupe tones, it blends durability with visual warmth.&lt;br&gt;
+ALTAMURA Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Real Italian Leather, Engineered Wood, then finished in Gray tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 80"L X 39"W X 39 1/4"H (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recliners&lt;br&gt;
@@ -25058,8 +25062,8 @@
 - Pillow Top Arm &amp;amp; Accent Stitching&lt;br&gt;
 - 100% Made in Italy&lt;br&gt;
 - Fully Upholstered in Leather on all Sides&lt;/p&gt;
-&lt;p&gt;Materials: Real Italian Leather, Engineered Wood.&lt;br&gt;
-Color: Taupe&lt;br&gt;
+&lt;p&gt;Materials: Real Italian Leather, Engineered Wood, Others.&lt;br&gt;
+Color: Gray or Taupe&lt;br&gt;
 Weight: 149 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25144,7 +25148,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -25290,7 +25294,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -25435,7 +25439,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -25579,7 +25583,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -25643,9 +25647,9 @@
 - Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Light Taupe; dimensions: 89" L x 40" W x 41" H (EXTENDED: 71" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
-Color: Light Taupe&lt;br&gt;
+- Power Sofa: color: Light Taupe or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Light Taupe or Gray&lt;br&gt;
 Weight: 246 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25730,7 +25734,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -25784,7 +25788,7 @@
       <c r="G173" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ARTEMIA Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Breathable Leatherette, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
+ARTEMIA Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Light Taupe tones, the Breathable Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 89"L X 40"W X 41"H (EXTENDED: 71"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
@@ -25794,9 +25798,9 @@
 - Wall-hugger Design Requires Only 3-inches Off Wall&lt;br&gt;
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Gray; dimensions: 89" L x 40" W x 41" H (EXTENDED: 71" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Power Sofa: color: Light Taupe or Gray&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Light Taupe or Gray&lt;br&gt;
 Weight: 246 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25881,7 +25885,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -25945,10 +25949,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Black; dimensions: 88" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Black; dimensions: 72" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Metal, Solid Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+- Power Sofa: color: Black or Light Taupe&lt;br&gt;
+- Power Loveseat: color: Black or Light Taupe&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Metal, Solid Wood, Others.&lt;br&gt;
+Color: Black or Light Taupe&lt;br&gt;
 Weight: 249.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -26033,7 +26037,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -26087,7 +26091,7 @@
       <c r="G175" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ASCONA Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Light Taupe tones, the Breathable Leatherette, Metal, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
+ASCONA Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. With Breathable Leatherette, Metal, Solid Wood, construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
 Product Dimensions: SOFA: 88"L X 42"W X 31"H (EXTENDED: 63"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
@@ -26097,10 +26101,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Light Taupe; dimensions: 88" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Light Taupe; dimensions: 72" L x 42" W x 31" H (EXTENDED: 63" W); feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Metal, Solid Wood.&lt;br&gt;
-Color: Light Taupe&lt;br&gt;
+- Power Sofa: color: Black or Light Taupe&lt;br&gt;
+- Power Loveseat: color: Black or Light Taupe&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Metal, Solid Wood, Others.&lt;br&gt;
+Color: Black or Light Taupe&lt;br&gt;
 Weight: 249.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -26185,7 +26189,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -26330,7 +26334,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -26471,7 +26475,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -26613,7 +26617,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -26664,7 +26668,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 DEMETRIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:&lt;br&gt;
+Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65")&lt;br&gt;
 - Laf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
 - Raf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
 - Armless Chair Texas Slate: dimensions: 24" W x 39"D x 40" H&lt;br&gt;
@@ -26740,7 +26744,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -26790,11 +26794,11 @@
       <c r="G180" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-DEMETRIUS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces.&lt;br&gt;
-Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65") Included items and dimensions:&lt;br&gt;
-- Laf Power Recliner Texas Granite: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
-- Raf Power Recliner Texas Granite: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
-- Armless Chair Texas Granite: dimensions: 24" W x 39"D x 40" H&lt;br&gt;
+DEMETRIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 90"W X 39"D X 40"H (SEAT HT: 19", SEAT DP: 21.5-65")&lt;br&gt;
+- Laf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
+- Raf Power Recliner Texas Slate: dimensions: 33" W x 39"D x 40" H&lt;br&gt;
+- Armless Chair Texas Slate: dimensions: 24" W x 39"D x 40" H&lt;br&gt;
 Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -26867,7 +26871,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -27011,7 +27015,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -27158,7 +27162,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -27302,7 +27306,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -27357,7 +27361,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 GORGIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather Match, Solid Wood, then finished in Espresso tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
+Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 67 1/2"W) / 92"L X 40"W X 40"H (EXTENDED: 65 1/2"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recline Footrest&lt;br&gt;
 - Manual Recline Armless Chair&lt;br&gt;
@@ -27366,8 +27370,8 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Cornerblocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Espresso&lt;br&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Espresso or Light Gray&lt;br&gt;
 Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27452,7 +27456,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -27506,8 +27510,8 @@
       <c r="G185" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GORGIUS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Top Grain Leather Match, Solid Wood, construction and Light Gray tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 65 1/2"W)&lt;/p&gt;
+GORGIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather Match, Solid Wood, then finished in Espresso tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 92"L X 40"W X 40"H (EXTENDED: 67 1/2"W) / 92"L X 40"W X 40"H (EXTENDED: 65 1/2"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recline Footrest&lt;br&gt;
 - Manual Recline Armless Chair&lt;br&gt;
@@ -27516,8 +27520,8 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Cornerblocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Espresso or Light Gray&lt;br&gt;
 Weight: 232 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27602,7 +27606,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -27747,7 +27751,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -27802,16 +27806,16 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 JACOBUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Top Grain Leather and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: Sofa: 41.3"L X 38.6"W X 40.9"H&lt;/p&gt;
+Product Dimensions: Sofa: 41.3"L X 38.6"W X 40.9"H / Sofa: 38.6"L X 38.6"W X 40.9"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Contour Arm&lt;br&gt;
 - Wide Seats&lt;br&gt;
 - 100% Polyester Fiber&lt;br&gt;
 - Solid Wood Frame Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Beige; dimensions: 78" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Beige or Light Gray&lt;br&gt;
+- Loveseat: color: Beige or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Top Grain Leather.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Light Gray&lt;br&gt;
 Weight: 443.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27896,7 +27900,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -27950,17 +27954,17 @@
       <c r="G188" s="28" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JACOBUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Top Grain Leather, then finished in Light Gray tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: Sofa: 38.6"L X 38.6"W X 40.9"H&lt;/p&gt;
+JACOBUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Top Grain Leather and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: Sofa: 41.3"L X 38.6"W X 40.9"H / Sofa: 38.6"L X 38.6"W X 40.9"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Contour Arm&lt;br&gt;
 - Wide Seats&lt;br&gt;
 - 100% Polyester Fiber&lt;br&gt;
 - Solid Wood Frame Included items and dimensions:&lt;br&gt;
-- Sofa: color: Light Gray; dimensions: 87" W x 38.5"D x 41" H; feature: Transitional&lt;br&gt;
-- Loveseat: color: Light Gray; dimensions: 78" W x 38.5"D x 41" H; feature: Transitional&lt;/p&gt;
+- Sofa: color: Beige or Light Gray&lt;br&gt;
+- Loveseat: color: Beige or Light Gray&lt;/p&gt;
 &lt;p&gt;Materials: Top Grain Leather.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Beige or Light Gray&lt;br&gt;
 Weight: 443.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28045,7 +28049,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -28189,7 +28193,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -28330,7 +28334,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -28474,7 +28478,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -28529,7 +28533,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MORCOTE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Boucle Fabric, Solid Wood, construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
-Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21") / 82.5"W X 39"D X 38"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recliners&lt;br&gt;
 - S-Spring Seat and Webbing Back Suspension&lt;br&gt;
@@ -28538,11 +28542,11 @@
 - Contoured Seat Cushion&lt;br&gt;
 - 100% Polyester&lt;br&gt;
 - High Density Foam Pocketed Coil Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Beige; dimensions: 90" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Beige; dimensions: 67" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Boucle Fabric, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 199 lbs&lt;/p&gt;</t>
+- Power Sofa: color: Beige or Gray or Light Gray&lt;br&gt;
+- Power Loveseat: color: Beige or Gray or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood, Others or Boucle Fabric, Solid Wood, Engineered Wood, Other.&lt;br&gt;
+Color: Beige or Gray or Light Gray&lt;br&gt;
+Weight: 199 or 408.41 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" s="18" t="inlineStr">
@@ -28626,7 +28630,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -28680,157 +28684,8 @@
       <c r="G193" s="18" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORCOTE Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Finished in Gray tones, the Boucle Fabric, Solid Wood, Engineered Wood, Other build keeps the look polished and practical.&lt;br&gt;
-Product Dimensions: 82.5"W X 39"D X 38"H&lt;/p&gt;
-&lt;p&gt;Features&lt;br&gt;
-- Pillow Top Arms&lt;br&gt;
-- Console with Stainless Steel Cup Holders on Loveseat&lt;br&gt;
-- USB-A &amp;amp; USB-C Charger&lt;br&gt;
-- Envelope Arms Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Gray; dimensions: 82.5" W x 39"D x 38" H; feature: Contemporary&lt;br&gt;
-- Power Loveseat w/ Console: color: Gray; dimensions: 72.5" W x 39"D x 38" H; feature: Contemporary&lt;/p&gt;
-&lt;p&gt;Materials: Boucle Fabric, Solid Wood, Engineered Wood, Other.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 408.41 lbs&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H193" s="18" t="inlineStr">
-        <is>
-          <t>MORCOTE Power Sofa and Loveseat in Gray | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="I193" s="18" t="inlineStr">
-        <is>
-          <t>The MORCOTE Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
-        </is>
-      </c>
-      <c r="J193" s="18" t="inlineStr">
-        <is>
-          <t>MORCOTE</t>
-        </is>
-      </c>
-      <c r="K193" s="18" t="inlineStr">
-        <is>
-          <t>Power Sofa + Loveseat</t>
-        </is>
-      </c>
-      <c r="L193" s="18" t="n"/>
-      <c r="M193" s="18" t="inlineStr">
-        <is>
-          <t>Set</t>
-        </is>
-      </c>
-      <c r="N193" s="18" t="inlineStr">
-        <is>
-          <t>FM62001GY-SF-PM, FM62001GY-LV-PM</t>
-        </is>
-      </c>
-      <c r="O193" s="18" t="inlineStr">
-        <is>
-          <t>FM62001GY-PM-1.jpg</t>
-        </is>
-      </c>
-      <c r="P193" s="18" t="n">
-        <v>1159</v>
-      </c>
-      <c r="Q193" s="19" t="n">
-        <v>1199</v>
-      </c>
-      <c r="R193" s="18" t="n">
-        <v>2877</v>
-      </c>
-      <c r="S193" s="18" t="n">
-        <v>408.41</v>
-      </c>
-      <c r="T193" s="18" t="inlineStr">
-        <is>
-          <t>82.5"W X 39"D X 38"H</t>
-        </is>
-      </c>
-      <c r="U193" s="18" t="inlineStr">
-        <is>
-          <t>Contemporary</t>
-        </is>
-      </c>
-      <c r="V193" s="18" t="inlineStr">
-        <is>
-          <t>Boucle Fabric, Solid Wood, Engineered Wood, Other</t>
-        </is>
-      </c>
-      <c r="W193" s="18" t="inlineStr">
-        <is>
-          <t>Contemporary,Gray,Boucle Fabric, Solid Wood, Engineered Wood, Other,Pillow Top Arms,Console with Stainless Steel Cup Holders on Loveseat,USB-A &amp; USB-C Charger,Envelope Arms</t>
-        </is>
-      </c>
-      <c r="X193" s="18" t="inlineStr">
-        <is>
-          <t>VN</t>
-        </is>
-      </c>
-      <c r="Y193" s="18" t="n"/>
-      <c r="Z193" s="18" t="n"/>
-      <c r="AA193" s="18" t="n"/>
-      <c r="AB193" s="18" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>Upholstery, Motion, MORCOTE, LIVING ROOM FURNITURE</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>GOODDEGG</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>Furniture &gt; Sofas</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="inlineStr">
-        <is>
-          <t>Light Gray</t>
-        </is>
-      </c>
-      <c r="B194" s="18" t="n"/>
-      <c r="C194" s="18" t="inlineStr">
-        <is>
-          <t>FM62001LG-PM-2PC</t>
-        </is>
-      </c>
-      <c r="D194" s="18" t="inlineStr">
-        <is>
-          <t>Upholstery</t>
-        </is>
-      </c>
-      <c r="E194" s="18" t="inlineStr">
-        <is>
-          <t>Motion</t>
-        </is>
-      </c>
-      <c r="F194" s="18" t="inlineStr">
-        <is>
-          <t>MORCOTE Power Sofa and Loveseat</t>
-        </is>
-      </c>
-      <c r="G194" s="18" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORCOTE Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Boucle Fabric, Solid Wood, and finished in Light Gray tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21")&lt;/p&gt;
+MORCOTE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Boucle Fabric, Solid Wood, construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21") / 82.5"W X 39"D X 38"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recliners&lt;br&gt;
 - S-Spring Seat and Webbing Back Suspension&lt;br&gt;
@@ -28839,11 +28694,163 @@
 - Contoured Seat Cushion&lt;br&gt;
 - 100% Polyester&lt;br&gt;
 - High Density Foam Pocketed Coil Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Light Gray; dimensions: 90" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Light Gray; dimensions: 67" L x 39" W x 41" H (EXTENDED: 59" W) (SEAT HT: 20", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Boucle Fabric, Solid Wood.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
-Weight: 199 lbs&lt;/p&gt;</t>
+- Power Sofa: color: Beige or Gray or Light Gray&lt;br&gt;
+- Power Loveseat: color: Beige or Gray or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood, Others or Boucle Fabric, Solid Wood, Engineered Wood, Other.&lt;br&gt;
+Color: Beige or Gray or Light Gray&lt;br&gt;
+Weight: 199 or 408.41 lbs&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H193" s="18" t="inlineStr">
+        <is>
+          <t>MORCOTE Power Sofa and Loveseat in Gray | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="I193" s="18" t="inlineStr">
+        <is>
+          <t>The MORCOTE Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+        </is>
+      </c>
+      <c r="J193" s="18" t="inlineStr">
+        <is>
+          <t>MORCOTE</t>
+        </is>
+      </c>
+      <c r="K193" s="18" t="inlineStr">
+        <is>
+          <t>Power Sofa + Loveseat</t>
+        </is>
+      </c>
+      <c r="L193" s="18" t="n"/>
+      <c r="M193" s="18" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N193" s="18" t="inlineStr">
+        <is>
+          <t>FM62001GY-SF-PM, FM62001GY-LV-PM</t>
+        </is>
+      </c>
+      <c r="O193" s="18" t="inlineStr">
+        <is>
+          <t>FM62001GY-PM-1.jpg</t>
+        </is>
+      </c>
+      <c r="P193" s="18" t="n">
+        <v>1159</v>
+      </c>
+      <c r="Q193" s="19" t="n">
+        <v>1199</v>
+      </c>
+      <c r="R193" s="18" t="n">
+        <v>2877</v>
+      </c>
+      <c r="S193" s="18" t="n">
+        <v>408.41</v>
+      </c>
+      <c r="T193" s="18" t="inlineStr">
+        <is>
+          <t>82.5"W X 39"D X 38"H</t>
+        </is>
+      </c>
+      <c r="U193" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary</t>
+        </is>
+      </c>
+      <c r="V193" s="18" t="inlineStr">
+        <is>
+          <t>Boucle Fabric, Solid Wood, Engineered Wood, Other</t>
+        </is>
+      </c>
+      <c r="W193" s="18" t="inlineStr">
+        <is>
+          <t>Contemporary,Gray,Boucle Fabric, Solid Wood, Engineered Wood, Other,Pillow Top Arms,Console with Stainless Steel Cup Holders on Loveseat,USB-A &amp; USB-C Charger,Envelope Arms</t>
+        </is>
+      </c>
+      <c r="X193" s="18" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="Y193" s="18" t="n"/>
+      <c r="Z193" s="18" t="n"/>
+      <c r="AA193" s="18" t="n"/>
+      <c r="AB193" s="18" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MORCOTE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>Light Gray</t>
+        </is>
+      </c>
+      <c r="B194" s="18" t="n"/>
+      <c r="C194" s="18" t="inlineStr">
+        <is>
+          <t>FM62001LG-PM-2PC</t>
+        </is>
+      </c>
+      <c r="D194" s="18" t="inlineStr">
+        <is>
+          <t>Upholstery</t>
+        </is>
+      </c>
+      <c r="E194" s="18" t="inlineStr">
+        <is>
+          <t>Motion</t>
+        </is>
+      </c>
+      <c r="F194" s="18" t="inlineStr">
+        <is>
+          <t>MORCOTE Power Sofa and Loveseat</t>
+        </is>
+      </c>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORCOTE Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Boucle Fabric, Solid Wood, construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
+Product Dimensions: SOFA: 90"L X 39"W X 41"H (EXTENDED: 59"W) (SEAT HT: 20", SEAT DP: 21") / 82.5"W X 39"D X 38"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Power Recliners&lt;br&gt;
+- S-Spring Seat and Webbing Back Suspension&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- Accent Stitching&lt;br&gt;
+- Contoured Seat Cushion&lt;br&gt;
+- 100% Polyester&lt;br&gt;
+- High Density Foam Pocketed Coil Included items and dimensions:&lt;br&gt;
+- Power Sofa: color: Beige or Gray or Light Gray&lt;br&gt;
+- Power Loveseat: color: Beige or Gray or Light Gray&lt;/p&gt;
+&lt;p&gt;Materials: Boucle Fabric, Solid Wood, Others or Boucle Fabric, Solid Wood, Engineered Wood, Other.&lt;br&gt;
+Color: Beige or Gray or Light Gray&lt;br&gt;
+Weight: 199 or 408.41 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H194" s="18" t="inlineStr">
@@ -28927,7 +28934,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -29071,7 +29078,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -29213,7 +29220,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -29356,7 +29363,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -29419,10 +29426,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Gray; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Gray; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Power Sofa: color: Gray or Pale Blue or Beige&lt;br&gt;
+- Power Loveseat: color: Gray or Pale Blue or Beige&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Pale Blue or Beige&lt;br&gt;
 Weight: 247 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -29507,7 +29514,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -29561,7 +29568,7 @@
       <c r="G199" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PHINEAS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Crafted with Top Grain Leather Match, Solid Wood, then finished in Pale Blue tones to suit a range of interiors.&lt;br&gt;
+PHINEAS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Top Grain Leather Match, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
@@ -29570,10 +29577,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Pale Blue; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Pale Blue; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Pale Blue&lt;br&gt;
+- Power Sofa: color: Gray or Pale Blue or Beige&lt;br&gt;
+- Power Loveseat: color: Gray or Pale Blue or Beige&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Pale Blue or Beige&lt;br&gt;
 Weight: 247 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -29658,7 +29665,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29712,7 +29719,7 @@
       <c r="G200" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PHINEAS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. With Top Grain Leather Match, Solid Wood, construction and Beige tones, it blends durability with visual warmth.&lt;br&gt;
+PHINEAS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Built from Top Grain Leather Match, Solid Wood, and finished in Gray tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 85"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Zero Gravity Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
@@ -29721,10 +29728,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Beige; dimensions: 85" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Beige; dimensions: 74" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
+- Power Sofa: color: Gray or Pale Blue or Beige&lt;br&gt;
+- Power Loveseat: color: Gray or Pale Blue or Beige&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Pale Blue or Beige&lt;br&gt;
 Weight: 247 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -29809,7 +29816,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -29952,7 +29959,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -30012,11 +30019,11 @@
 - Contour Arms&lt;br&gt;
 - USB-A &amp;amp; USB-C Chargers&lt;br&gt;
 - Flange Trim Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Beige; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Beige; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+- Power Sofa: color: Beige or Black or Gray or Light Brown&lt;br&gt;
+- Power Loveseat: color: Beige or Black or Gray or Light Brown&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 357.6 lbs&lt;/p&gt;</t>
+Color: Beige or Black or Gray or Light Brown&lt;br&gt;
+Weight: 357.6 or 346.5 or 374.4 or 369.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" s="30" t="inlineStr">
@@ -30100,7 +30107,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -30154,17 +30161,17 @@
       <c r="G203" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SCHLIEREN Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. With Leatherette, Foam, Other construction and Black tones, it blends durability with visual warmth.&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Foam, Other, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Contour Arms&lt;br&gt;
 - USB-A &amp;amp; USB-C Chargers&lt;br&gt;
 - Flange Trim Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Black; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Black; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+- Power Sofa: color: Beige or Black or Gray or Light Brown&lt;br&gt;
+- Power Loveseat: color: Beige or Black or Gray or Light Brown&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 346.5 lbs&lt;/p&gt;</t>
+Color: Beige or Black or Gray or Light Brown&lt;br&gt;
+Weight: 357.6 or 346.5 or 374.4 or 369.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" s="30" t="inlineStr">
@@ -30248,7 +30255,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -30302,17 +30309,17 @@
       <c r="G204" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SCHLIEREN Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Contemporary styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Leatherette, Foam, Other build keeps the look polished and practical.&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Foam, Other, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Contour Arms&lt;br&gt;
 - USB-A &amp;amp; USB-C Chargers&lt;br&gt;
 - Flange Trim Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Gray; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Gray; dimensions: 57" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+- Power Sofa: color: Beige or Black or Gray or Light Brown&lt;br&gt;
+- Power Loveseat: color: Beige or Black or Gray or Light Brown&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 374.4 lbs&lt;/p&gt;</t>
+Color: Beige or Black or Gray or Light Brown&lt;br&gt;
+Weight: 357.6 or 346.5 or 374.4 or 369.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" s="30" t="inlineStr">
@@ -30396,7 +30403,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -30450,17 +30457,17 @@
       <c r="G205" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SCHLIEREN Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leatherette, Foam, Other and finished in Light Brown tones for a clean, cohesive look.&lt;br&gt;
+SCHLIEREN Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Crafted with Leatherette, Foam, Other, then finished in Beige tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: 80.5"W X 38.5"D X 40.5"H (SEAT HT: 20", SEAT DP: 30.5 - 63.5")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Contour Arms&lt;br&gt;
 - USB-A &amp;amp; USB-C Chargers&lt;br&gt;
 - Flange Trim Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Light Brown; dimensions: 80.5" W x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Light Brown; dimensions: 57"D x 38.5"D x 40.5" H (SEAT HT: 20", SEAT DP: 30.5 - 63.5"); feature: Contemporary&lt;/p&gt;
+- Power Sofa: color: Beige or Black or Gray or Light Brown&lt;br&gt;
+- Power Loveseat: color: Beige or Black or Gray or Light Brown&lt;/p&gt;
 &lt;p&gt;Materials: Leatherette, Foam, Other.&lt;br&gt;
-Color: Light Brown&lt;br&gt;
-Weight: 369.08 lbs&lt;/p&gt;</t>
+Color: Beige or Black or Gray or Light Brown&lt;br&gt;
+Weight: 357.6 or 346.5 or 374.4 or 369.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" s="30" t="inlineStr">
@@ -30544,7 +30551,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -30608,10 +30615,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Charcoal; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Charcoal; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Charcoal&lt;br&gt;
+- Power Sofa: color: Charcoal or Medium Brown&lt;br&gt;
+- Power Loveseat: color: Charcoal or Medium Brown&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Charcoal or Medium Brown&lt;br&gt;
 Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30696,7 +30703,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -30750,7 +30757,7 @@
       <c r="G207" s="41" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SOTERIOS Power Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Top Grain Leather Match, Solid Wood, construction and Medium Brown tones, it blends durability with visual warmth.&lt;br&gt;
+SOTERIOS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Top Grain Leather Match, Solid Wood, then finished in Charcoal tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
@@ -30760,10 +30767,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Medium Brown; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Medium Brown; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood.&lt;br&gt;
-Color: Medium Brown&lt;br&gt;
+- Power Sofa: color: Charcoal or Medium Brown&lt;br&gt;
+- Power Loveseat: color: Charcoal or Medium Brown&lt;/p&gt;
+&lt;p&gt;Materials: Top Grain Leather Match, Solid Wood, Others.&lt;br&gt;
+Color: Charcoal or Medium Brown&lt;br&gt;
 Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30848,7 +30855,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -30903,7 +30910,7 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 TERENTIUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension and finished in Caramel Brown tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 19", SEAT DP: 22")&lt;/p&gt;
+Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 19", SEAT DP: 22") / 86"W X 35.5"D X 40.5"H (SEAT HT: 18.5", SEAT DP: 21 - 61")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recliner&lt;br&gt;
 - 2" Wall Clearance&lt;br&gt;
@@ -30912,11 +30919,11 @@
 - Single Power&lt;br&gt;
 - 2.0 LB High Density Foam w/ Pocketed Coil Spring&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Caramel Brown; dimensions: 86" W x 35.5"D x 40.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Caramel Brown; dimensions: 62.5" W x 35.5"D x 40.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Contemporary&lt;/p&gt;
+- Power Sofa: color: Caramel Brown or Taupe&lt;br&gt;
+- Power Loveseat: color: Caramel Brown or Taupe&lt;/p&gt;
 &lt;p&gt;Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension.&lt;br&gt;
-Color: Caramel Brown&lt;br&gt;
-Weight: 420.2 lbs&lt;/p&gt;</t>
+Color: Caramel Brown or Taupe&lt;br&gt;
+Weight: 420.2 or 433.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H208" s="16" t="inlineStr">
@@ -31004,7 +31011,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -31058,8 +31065,8 @@
       <c r="G209" s="16" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TERENTIUS Power Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery motion is made to fit naturally into the room. A Contemporary profile gives the space a refined, approachable look. Crafted with Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension, then finished in Taupe tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 18.5", SEAT DP: 21 - 61")&lt;/p&gt;
+TERENTIUS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Contemporary character adds definition without feeling heavy. Built from Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension and finished in Caramel Brown tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 86"W X 35.5"D X 40.5"H (SEAT HT: 19", SEAT DP: 22") / 86"W X 35.5"D X 40.5"H (SEAT HT: 18.5", SEAT DP: 21 - 61")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recliner&lt;br&gt;
 - 2" Wall Clearance&lt;br&gt;
@@ -31068,11 +31075,11 @@
 - Single Power&lt;br&gt;
 - 2.0 LB High Density Foam w/ Pocketed Coil Spring&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Taupe; dimensions: 86" W x 35.5"D x 40.5" H (SEAT HT: 18.5", SEAT DP: 21 - 61"); feature: Contemporary&lt;br&gt;
-- Power Loveseat: color: Taupe; dimensions: 62.5" W x 35.5"D x 40.5" H (SEAT HT: 18.5", SEAT DP: 21 - 61"); feature: Contemporary&lt;/p&gt;
+- Power Sofa: color: Caramel Brown or Taupe&lt;br&gt;
+- Power Loveseat: color: Caramel Brown or Taupe&lt;/p&gt;
 &lt;p&gt;Materials: Leather Match, High Density Foam, Pocket Coil Spring, Tropical Hardwood, Engineered Wood, Sinuous Spring and Webbing Suspension.&lt;br&gt;
-Color: Taupe&lt;br&gt;
-Weight: 433.9 lbs&lt;/p&gt;</t>
+Color: Caramel Brown or Taupe&lt;br&gt;
+Weight: 420.2 or 433.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" s="16" t="inlineStr">
@@ -31156,7 +31163,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -31275,7 +31282,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -31418,7 +31425,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -31562,7 +31569,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -31707,7 +31714,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -31771,10 +31778,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Gray; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Gray; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+- Power Sofa: color: Gray or Taupe&lt;br&gt;
+- Power Loveseat: color: Gray or Taupe&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Taupe&lt;br&gt;
 Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -31859,7 +31866,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -31913,7 +31920,7 @@
       <c r="G215" s="37" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VASILIOS Power Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Breathable Leatherette, Solid Wood, and finished in Taupe tones for a clean, cohesive look.&lt;br&gt;
+VASILIOS Power Sofa and Loveseat brings a composed, welcoming feel to the room without overwhelming the space. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Finished in Gray tones, the Breathable Leatherette, Solid Wood, build keeps the look polished and practical.&lt;br&gt;
 Product Dimensions: SOFA: 86"L X 41"W X 41"H (EXTENDED: 67 1/2"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Power Recline Footrest &amp;amp; Headrest&lt;br&gt;
@@ -31923,10 +31930,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps Included items and dimensions:&lt;br&gt;
-- Power Sofa: color: Taupe; dimensions: 86" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;br&gt;
-- Power Loveseat: color: Taupe; dimensions: 64" L x 41" W x 41" H (EXTENDED: 67 1 or 2" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
-Color: Taupe&lt;br&gt;
+- Power Sofa: color: Gray or Taupe&lt;br&gt;
+- Power Loveseat: color: Gray or Taupe&lt;/p&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood, Others.&lt;br&gt;
+Color: Gray or Taupe&lt;br&gt;
 Weight: 255 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32011,7 +32018,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -32075,10 +32082,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered EvenUnder Back Flaps Included items and dimensions:&lt;br&gt;
-- Sofa: color: Beige; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
-- Loveseat: color: Beige; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
+- Sofa: color: Beige or Dark Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Beige or Dark Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Dark Brown or Dark Gray&lt;br&gt;
 Weight: 218 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32163,7 +32170,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -32217,7 +32224,7 @@
       <c r="G217" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HENRICUS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. This upholstery uphostery set is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. Crafted with Fabric, Solid Wood, then finished in Dark Brown tones to suit a range of interiors.&lt;br&gt;
+HENRICUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Solid Wood, and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Manual Recline Sofa and Loveseat&lt;br&gt;
@@ -32227,10 +32234,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered EvenUnder Back Flaps Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Brown; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
-- Loveseat: color: Dark Brown; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Dark Brown&lt;br&gt;
+- Sofa: color: Beige or Dark Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Beige or Dark Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Dark Brown or Dark Gray&lt;br&gt;
 Weight: 218 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32315,7 +32322,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -32369,7 +32376,7 @@
       <c r="G218" s="22" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HENRICUS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. Designed as a upholstery uphostery set, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. With Fabric, Solid Wood, construction and Dark Gray tones, it blends durability with visual warmth.&lt;br&gt;
+HENRICUS Sofa and Loveseat is designed for everyday living, balancing comfort with a clean, finished look. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Built from Fabric, Solid Wood, and finished in Beige tones for a clean, cohesive look.&lt;br&gt;
 Product Dimensions: SOFA: 88"L X 40"W X 40"H (EXTENDED: 70"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Manual Recline Sofa and Loveseat&lt;br&gt;
@@ -32379,10 +32386,10 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered EvenUnder Back Flaps Included items and dimensions:&lt;br&gt;
-- Sofa: color: Dark Gray; dimensions: 88" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;br&gt;
-- Loveseat: color: Dark Gray; dimensions: 68" L x 40" W x 40" H (EXTENDED: 70" W); feature: Transitional&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+- Sofa: color: Beige or Dark Brown or Dark Gray&lt;br&gt;
+- Loveseat: color: Beige or Dark Brown or Dark Gray&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Beige or Dark Brown or Dark Gray&lt;br&gt;
 Weight: 218 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32467,7 +32474,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -32530,8 +32537,8 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps&lt;/p&gt;
-&lt;p&gt;Materials: Breathable Leatherette, Solid Wood.&lt;br&gt;
-Color: Dark Gray Leatherette&lt;br&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood, Others or Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Dark Gray Leatherette or Light Gray Fabric&lt;br&gt;
 Weight: 234 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32616,7 +32623,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -32670,7 +32677,7 @@
       <c r="G220" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JOSIAS Sofa and Loveseat creates a cohesive setup that feels inviting the moment you walk in. This upholstery sofa is made to fit naturally into the room. A Transitional profile gives the space a refined, approachable look. With Fabric, Solid Wood, construction and Light Gray Fabric tones, it blends durability with visual warmth.&lt;br&gt;
+JOSIAS Sofa and Loveseat offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery uphostery set, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Breathable Leatherette, Solid Wood, then finished in Dark Gray Leatherette tones to suit a range of interiors.&lt;br&gt;
 Product Dimensions: SOFA: 88"L X 39"W X 40"H (EXTENDED: 65"W)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Manual Recline Sofa&lt;br&gt;
@@ -32679,8 +32686,8 @@
 - No Sag Suspension w/ Sinuous Wire&lt;br&gt;
 - Corner-blocked Kiln-dried Hardwood Frame&lt;br&gt;
 - Fully Upholstered Even Under Back Flaps&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Solid Wood.&lt;br&gt;
-Color: Light Gray Fabric&lt;br&gt;
+&lt;p&gt;Materials: Breathable Leatherette, Solid Wood, Others or Fabric, Solid Wood, Others.&lt;br&gt;
+Color: Dark Gray Leatherette or Light Gray Fabric&lt;br&gt;
 Weight: 234 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32765,7 +32772,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">

--- a/FOA SETS/Upholstery-Set.xlsx
+++ b/FOA SETS/Upholstery-Set.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ABERPORTH Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>ABERPORTH Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The ABERPORTH Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABERPORTH Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>ACAPULCO Sofa and Loveseat in Black Off-White | GOODDEGG</t>
+          <t>ACAPULCO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>The ACAPULCO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACAPULCO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" s="14" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>ACAPULCO Sofa and Loveseat in Off-White | GOODDEGG</t>
+          <t>ACAPULCO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>The ACAPULCO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACAPULCO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" s="14" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The ADELPHA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ADELPHA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>ALBACETE Sofa and Loveseat in Dark Cherry Brown | GOODDEGG</t>
+          <t>ALBACETE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>The ALBACETE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALBACETE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="H7" s="16" t="inlineStr">
         <is>
-          <t>ALBACETE Sofa and Loveseat in Champagne Purple | GOODDEGG</t>
+          <t>ALBACETE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>The ALBACETE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALBACETE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="H8" s="18" t="inlineStr">
         <is>
-          <t>ALESUND Sofa and Loveseat in Beige Light Oak | GOODDEGG</t>
+          <t>ALESUND Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>The ALESUND Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALESUND Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" s="18" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="H9" s="18" t="inlineStr">
         <is>
-          <t>ALESUND Sofa and Loveseat in Beige Walnut | GOODDEGG</t>
+          <t>ALESUND Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>The ALESUND Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALESUND Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" s="18" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AMAYA Sofa and Loveseat in Cream | GOODDEGG</t>
+          <t>AMAYA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The AMAYA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMAYA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ANDALUSIA Sofa and Loveseat in Light Brown Dark Cherry | GOODDE</t>
+          <t>ANDALUSIA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The ANDALUSIA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANDALUSIA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>ANTOINETTE Sofa and Loveseat in White | GOODDEGG</t>
+          <t>ANTOINETTE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>The ANTOINETTE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTOINETTE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>ANTOINETTE Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>ANTOINETTE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>The ANTOINETTE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTOINETTE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ATTWELL Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>ATTWELL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>The ATTWELL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ATTWELL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>AZULETTI Sofa and Loveseat in Dark Teal Apple Green | GOODDEGG</t>
+          <t>AZULETTI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The AZULETTI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AZULETTI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BASIE Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>BASIE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The BASIE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASIE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>BELSIZE Sofa and Loveseat in Beige Navy | GOODDEGG</t>
+          <t>BELSIZE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>The BELSIZE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELSIZE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>BELSIZE Sofa and Loveseat in Chocolate Tan | GOODDEGG</t>
+          <t>BELSIZE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>The BELSIZE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELSIZE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>BELSIZE Sofa and Loveseat in Light Taupe Black | GOODDEGG</t>
+          <t>BELSIZE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
-          <t>The BELSIZE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELSIZE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>BIENNE Sofa and Loveseat in Black | GOODDEGG</t>
+          <t>BIENNE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>The BIENNE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BIENNE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" s="24" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>BIENNE Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>BIENNE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>The BIENNE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BIENNE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" s="24" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>BONAVENTURA Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>BONAVENTURA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
-          <t>BONAVENTURA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BONAVENTURA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" s="26" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>BONAVENTURA Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>BONAVENTURA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
-          <t>BONAVENTURA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BONAVENTURA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" s="26" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BRIANA Sofa and Loveseat in Beige Gold | GOODDEGG</t>
+          <t>BRIANA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>The BRIANA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRIANA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CASSANI Sofa and Loveseat in Light Gray Walnut | GOODDEGG</t>
+          <t>CASSANI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>The CASSANI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CASSANI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CATALONIA Sofa and Loveseat in Beige Dark Cherry | GOODDEGG</t>
+          <t>CATALONIA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The CATALONIA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CATALONIA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CATARINA Sofa and Loveseat in Beige Teal | GOODDEGG</t>
+          <t>CATARINA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The CATARINA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CATARINA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The CHARLEVOIX Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHARLEVOIX Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CHRISTINE Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>CHRISTINE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>The CHRISTINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHRISTINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="I30" s="28" t="inlineStr">
         <is>
-          <t>The CINDERFORD Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CINDERFORD Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" s="28" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="I31" s="28" t="inlineStr">
         <is>
-          <t>The CINDERFORD Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CINDERFORD Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" s="28" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="H32" s="30" t="inlineStr">
         <is>
-          <t>CIVELLUTINO Sofa and Loveseat in Light Blue | GOODDEGG</t>
+          <t>CIVELLUTINO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" s="30" t="inlineStr">
         <is>
-          <t>CIVELLUTINO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CIVELLUTINO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" s="30" t="inlineStr">
@@ -5307,12 +5307,12 @@
       </c>
       <c r="H33" s="30" t="inlineStr">
         <is>
-          <t>CIVELLUTINO Sofa and Loveseat in Teal | GOODDEGG</t>
+          <t>CIVELLUTINO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I33" s="30" t="inlineStr">
         <is>
-          <t>CIVELLUTINO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CIVELLUTINO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" s="30" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>COCHRANE Sofa and Loveseat in Cream Beige | GOODDEGG</t>
+          <t>COCHRANE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The COCHRANE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>COCHRANE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="H35" s="32" t="inlineStr">
         <is>
-          <t>CRAYFORD Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>CRAYFORD Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I35" s="32" t="inlineStr">
         <is>
-          <t>The CRAYFORD Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRAYFORD Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" s="32" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H36" s="32" t="inlineStr">
         <is>
-          <t>CRAYFORD Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>CRAYFORD Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" s="32" t="inlineStr">
         <is>
-          <t>The CRAYFORD Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRAYFORD Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" s="32" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CROYDON Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>CROYDON Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The CROYDON Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CROYDON Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>DELGADA Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>DELGADA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>The DELGADA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DELGADA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>DELGADA Sofa and Loveseat in Graphite | GOODDEGG</t>
+          <t>DELGADA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>The DELGADA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DELGADA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="I40" s="35" t="inlineStr">
         <is>
-          <t>DIONYSUS Power Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIONYSUS Power Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" s="35" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I41" s="35" t="inlineStr">
         <is>
-          <t>DIONYSUS Power Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIONYSUS Power Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" s="35" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The DORIPHEI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DORIPHEI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>EALING Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>EALING Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>The EALING Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EALING Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="H44" s="16" t="inlineStr">
         <is>
-          <t>ELICIA Sofa and Loveseat in Champagne Turquoise | GOODDEGG</t>
+          <t>ELICIA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
-          <t>The ELICIA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELICIA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" s="16" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>ELICIA Sofa and Loveseat in Silver | GOODDEGG</t>
+          <t>ELICIA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
-          <t>The ELICIA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELICIA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ELLIS Sofa and Loveseat in Brown Burgundy | GOODDEGG</t>
+          <t>ELLIS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>The ELLIS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELLIS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ELPIS Sofa and Loveseat in Brown Espresso | GOODDEGG</t>
+          <t>ELPIS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The ELPIS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELPIS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>ELVERUM Sofa and Loveseat in Black | GOODDEGG</t>
+          <t>ELVERUM Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>The ELVERUM Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELVERUM Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" s="18" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>ELVERUM Sofa and Loveseat in Charcoal Gray | GOODDEGG</t>
+          <t>ELVERUM Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>The ELVERUM Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELVERUM Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" s="18" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="H50" s="18" t="inlineStr">
         <is>
-          <t>ELVERUM Sofa and Loveseat in Off-White | GOODDEGG</t>
+          <t>ELVERUM Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>The ELVERUM Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELVERUM Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" s="18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ENSENADA Sofa and Loveseat in Dark Cherry Brown | GOODDEGG</t>
+          <t>ENSENADA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>The ENSENADA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ENSENADA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>EZRIN Sofa and Loveseat in Light Brown | GOODDEGG</t>
+          <t>EZRIN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>The EZRIN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EZRIN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>FLETCHER Sofa and Loveseat in Brown Tan | GOODDEGG</t>
+          <t>FLETCHER Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>The FLETCHER Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FLETCHER Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FLINTSHIRE Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>FLINTSHIRE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>The FLINTSHIRE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FLINTSHIRE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="H55" s="37" t="inlineStr">
         <is>
-          <t>FRANKLIN Sofa and Loveseat in Dark Brown Tan | GOODDEGG</t>
+          <t>FRANKLIN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" s="37" t="inlineStr">
         <is>
-          <t>The FRANKLIN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FRANKLIN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" s="37" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="H56" s="37" t="inlineStr">
         <is>
-          <t>FRANKLIN Sofa and Loveseat in Burgundy Espresso | GOODDEGG</t>
+          <t>FRANKLIN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I56" s="37" t="inlineStr">
         <is>
-          <t>The FRANKLIN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FRANKLIN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J56" s="37" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>GERMAINE Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>GERMAINE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>The GERMAINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GERMAINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>GILDA Sofa and Loveseat in Beige Black | GOODDEGG</t>
+          <t>GILDA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>The GILDA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GILDA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -9075,12 +9075,12 @@
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>GIOVANNI Sofa and Loveseat in Beige Blue | GOODDEGG</t>
+          <t>GIOVANNI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>The GIOVANNI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIOVANNI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="H60" s="20" t="inlineStr">
         <is>
-          <t>GIOVANNI Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>GIOVANNI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>The GIOVANNI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIOVANNI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J60" s="20" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="H61" s="39" t="inlineStr">
         <is>
-          <t>GLARUS Sofa and Loveseat in Powder Blue | GOODDEGG</t>
+          <t>GLARUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I61" s="39" t="inlineStr">
         <is>
-          <t>The GLARUS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLARUS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J61" s="39" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="H62" s="39" t="inlineStr">
         <is>
-          <t>GLARUS Sofa and Loveseat in Dark Gray | GOODDEGG</t>
+          <t>GLARUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I62" s="39" t="inlineStr">
         <is>
-          <t>The GLARUS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLARUS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J62" s="39" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="H63" s="39" t="inlineStr">
         <is>
-          <t>GLARUS Sofa and Loveseat in White | GOODDEGG</t>
+          <t>GLARUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I63" s="39" t="inlineStr">
         <is>
-          <t>The GLARUS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLARUS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J63" s="39" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>GUSTAVO Sofa and Loveseat in Gray Walnut | GOODDEGG</t>
+          <t>GUSTAVO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>The GUSTAVO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GUSTAVO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>HARSTAD Sofa and Loveseat in Light Brown Natural | GOODDEGG</t>
+          <t>HARSTAD Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The HARSTAD Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HARSTAD Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>HERMILLY Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>HERMILLY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The HERMILLY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERMILLY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="I67" s="24" t="inlineStr">
         <is>
-          <t>HIERONYMUS Power Sofa and Loveseat makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Upholstery Set HIERONYMUS Power Sofa and supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J67" s="24" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="I68" s="24" t="inlineStr">
         <is>
-          <t>HIERONYMUS Power Sofa and Loveseat makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Upholstery Set HIERONYMUS Power Sofa and supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J68" s="24" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="H69" s="26" t="inlineStr">
         <is>
-          <t>HOLBORN Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>HOLBORN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
-          <t>The HOLBORN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLBORN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="H70" s="26" t="inlineStr">
         <is>
-          <t>HOLBORN Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>HOLBORN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I70" s="26" t="inlineStr">
         <is>
-          <t>The HOLBORN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLBORN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J70" s="26" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>HORGEN Sofa and Loveseat in Off-White | GOODDEGG</t>
+          <t>HORGEN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>The HORGEN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HORGEN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>HUELVA Sofa and Loveseat in Beige Dark Cherry | GOODDEGG</t>
+          <t>HUELVA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>The HUELVA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HUELVA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11100,12 +11100,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ILSE Sofa and Loveseat in Off-White Blue | GOODDEGG</t>
+          <t>ILSE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>The ILSE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILSE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>JAMAEL Sofa and Loveseat in Brown Espresso | GOODDEGG</t>
+          <t>JAMAEL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>The JAMAEL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JAMAEL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H75" s="30" t="inlineStr">
         <is>
-          <t>JARROW Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>JARROW Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I75" s="30" t="inlineStr">
         <is>
-          <t>The JARROW Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JARROW Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J75" s="30" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H76" s="30" t="inlineStr">
         <is>
-          <t>JARROW Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>JARROW Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I76" s="30" t="inlineStr">
         <is>
-          <t>The JARROW Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JARROW Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J76" s="30" t="inlineStr">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>JODIE Sofa and Loveseat in Satin Blue Silver | GOODDEGG</t>
+          <t>JODIE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>The JODIE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JODIE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KAYE Sofa and Loveseat in Green | GOODDEGG</t>
+          <t>KAYE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>The KAYE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KAYE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KESWICK Sofa and Loveseat in Charcoal | GOODDEGG</t>
+          <t>KESWICK Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>The KESWICK Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KESWICK Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>LANDOVERY Sofa and Loveseat in White Gold | GOODDEGG</t>
+          <t>LANDOVERY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>The LANDOVERY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LANDOVERY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>LAREDO Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>LAREDO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The LAREDO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAREDO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>LEYTONSTONE Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>LEYTONSTONE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>LEYTONSTONE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEYTONSTONE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>LEYTONSTONE Sofa and Loveseat in Cream | GOODDEGG</t>
+          <t>LEYTONSTONE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>LEYTONSTONE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEYTONSTONE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J83" s="14" t="inlineStr">
@@ -12703,12 +12703,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>LISTOWEL Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>LISTOWEL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>The LISTOWEL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LISTOWEL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>LISTOWEL Sofa and Loveseat and Chair in Brown | GOODDEGG</t>
+          <t>LISTOWEL Sofa and Loveseat and Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LISTOWEL Sofa and Loveseat and Chair makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Upholstery Set LISTOWEL Sofa and Loveseat and supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -12996,12 +12996,12 @@
       </c>
       <c r="H86" s="41" t="inlineStr">
         <is>
-          <t>LOUGHLIN Sofa and Loveseat in Light Brown | GOODDEGG</t>
+          <t>LOUGHLIN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I86" s="41" t="inlineStr">
         <is>
-          <t>The LOUGHLIN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOUGHLIN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J86" s="41" t="inlineStr">
@@ -13147,12 +13147,12 @@
       </c>
       <c r="H87" s="41" t="inlineStr">
         <is>
-          <t>LOUGHLIN Sofa and Loveseat in Gun Metal | GOODDEGG</t>
+          <t>LOUGHLIN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I87" s="41" t="inlineStr">
         <is>
-          <t>The LOUGHLIN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOUGHLIN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J87" s="41" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="H88" s="35" t="inlineStr">
         <is>
-          <t>LYNDA Sofa and Loveseat in Dark Gray | GOODDEGG</t>
+          <t>LYNDA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I88" s="35" t="inlineStr">
         <is>
-          <t>The LYNDA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYNDA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J88" s="35" t="inlineStr">
@@ -13445,12 +13445,12 @@
       </c>
       <c r="H89" s="35" t="inlineStr">
         <is>
-          <t>LYNDA Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>LYNDA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I89" s="35" t="inlineStr">
         <is>
-          <t>The LYNDA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYNDA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J89" s="35" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MARIELLA Sofa and Loveseat in Gray Beige Teal Olive</t>
+          <t>MARIELLA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>The MARIELLA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARIELLA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MARINELLA Sofa and Loveseat in Royal Blue | GOODDEGG</t>
+          <t>MARINELLA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>The MARINELLA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARINELLA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -13882,12 +13882,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MARSICANO Power Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>MARSICANO Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MARSICANO Power Sofa and Loveseat makes it easy to furnish the room with a coordinated. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSICANO Power Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>MARSICANO Sofa and Loveseat in Cognac | GOODDEGG</t>
+          <t>MARSICANO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>The MARSICANO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSICANO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -14175,12 +14175,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>MARTINIQUE Sofa and Loveseat in Blue | GOODDEGG</t>
+          <t>MARTINIQUE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>The MARTINIQUE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARTINIQUE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -14316,12 +14316,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>MARVIN Sofa and Loveseat in Pewter | GOODDEGG</t>
+          <t>MARVIN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>The MARVIN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARVIN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>MATTEO Sofa and Loveseat in Burgundy Brown | GOODDEGG</t>
+          <t>MATTEO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>The MATTEO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MATTEO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -14601,12 +14601,12 @@
       </c>
       <c r="H97" s="16" t="inlineStr">
         <is>
-          <t>MEZZANOTTE Sofa and Loveseat in Midnight Blue | GOODDEGG</t>
+          <t>MEZZANOTTE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
-          <t>The MEZZANOTTE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEZZANOTTE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J97" s="16" t="inlineStr">
@@ -14751,12 +14751,12 @@
       </c>
       <c r="H98" s="16" t="inlineStr">
         <is>
-          <t>MEZZANOTTE Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>MEZZANOTTE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
-          <t>The MEZZANOTTE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEZZANOTTE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J98" s="16" t="inlineStr">
@@ -14902,12 +14902,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MIRAMAR Sofa and Loveseat in Beige Charcoal | GOODDEGG</t>
+          <t>MIRAMAR Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The MIRAMAR Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MIRAMAR Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -15046,12 +15046,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>MISTY Sofa and Loveseat in Blue Gray | GOODDEGG</t>
+          <t>MISTY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>The MISTY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MISTY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>MOLFETTA Sofa and Loveseat in Light Brown Black | GOODDEGG</t>
+          <t>MOLFETTA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>The MOLFETTA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOLFETTA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -15344,12 +15344,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MONTECELIO Sofa and Loveseat in Light Gray Navy | GOODDEGG</t>
+          <t>MONTECELIO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>The MONTECELIO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTECELIO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -15490,12 +15490,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>MOORPARK Sofa and Loveseat in Off-White | GOODDEGG</t>
+          <t>MOORPARK Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>The MOORPARK Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOORPARK Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="I104" s="37" t="inlineStr">
         <is>
-          <t>The MORETAINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORETAINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J104" s="37" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="I105" s="37" t="inlineStr">
         <is>
-          <t>The MORETAINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORETAINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J105" s="37" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="I106" s="37" t="inlineStr">
         <is>
-          <t>The MORETAINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORETAINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J106" s="37" t="inlineStr">
@@ -16020,12 +16020,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>MOSSLEY Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>MOSSLEY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>The MOSSLEY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOSSLEY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -16166,12 +16166,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>MOTT Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>MOTT Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>The MOTT Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOTT Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>NADENE Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>NADENE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>The NADENE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NADENE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -16457,12 +16457,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>NASH Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>NASH Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>The NASH Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NASH Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="H111" s="20" t="inlineStr">
         <is>
-          <t>NEFYN Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>NEFYN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>The NEFYN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEFYN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="H112" s="20" t="inlineStr">
         <is>
-          <t>NEFYN Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>NEFYN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
-          <t>The NEFYN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEFYN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J112" s="20" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H113" s="39" t="inlineStr">
         <is>
-          <t>NEW MEADOWS Sofa and Loveseat in Ash Green Ivory | GOODDEGG</t>
+          <t>NEW MEADOWS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I113" s="39" t="inlineStr">
         <is>
-          <t>NEW MEADOWS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEW MEADOWS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J113" s="39" t="inlineStr">
@@ -17057,12 +17057,12 @@
       </c>
       <c r="H114" s="39" t="inlineStr">
         <is>
-          <t>NEW MEADOWS Sofa and Loveseat in Sand Caramel | GOODDEGG</t>
+          <t>NEW MEADOWS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I114" s="39" t="inlineStr">
         <is>
-          <t>NEW MEADOWS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEW MEADOWS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J114" s="39" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="H115" s="45" t="inlineStr">
         <is>
-          <t>NEWDALE Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>NEWDALE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I115" s="45" t="inlineStr">
         <is>
-          <t>The NEWDALE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEWDALE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J115" s="45" t="inlineStr">
@@ -17363,12 +17363,12 @@
       </c>
       <c r="H116" s="45" t="inlineStr">
         <is>
-          <t>NEWDALE Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>NEWDALE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I116" s="45" t="inlineStr">
         <is>
-          <t>The NEWDALE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEWDALE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J116" s="45" t="inlineStr">
@@ -17516,12 +17516,12 @@
       </c>
       <c r="H117" s="45" t="inlineStr">
         <is>
-          <t>NEWDALE Sofa and Loveseat in Brown Gold | GOODDEGG</t>
+          <t>NEWDALE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I117" s="45" t="inlineStr">
         <is>
-          <t>The NEWDALE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEWDALE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J117" s="45" t="inlineStr">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>NEWRY Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>NEWRY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>The NEWRY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEWRY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>NICANOR Sofa and Loveseat in Tan Gold | GOODDEGG</t>
+          <t>NICANOR Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>The NICANOR Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NICANOR Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -17962,12 +17962,12 @@
       </c>
       <c r="H120" s="22" t="inlineStr">
         <is>
-          <t>PALENCIA Sofa and Loveseat in Dark Cherry Beige | GOODDEGG</t>
+          <t>PALENCIA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I120" s="22" t="inlineStr">
         <is>
-          <t>The PALENCIA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALENCIA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J120" s="22" t="inlineStr">
@@ -18115,12 +18115,12 @@
       </c>
       <c r="H121" s="22" t="inlineStr">
         <is>
-          <t>PALENCIA Sofa and Loveseat in Dark Cherry Brown | GOODDEGG</t>
+          <t>PALENCIA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I121" s="22" t="inlineStr">
         <is>
-          <t>The PALENCIA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALENCIA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J121" s="22" t="inlineStr">
@@ -18268,12 +18268,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>PANOZZO Sofa and Loveseat in Beige Walnut | GOODDEGG</t>
+          <t>PANOZZO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>The PANOZZO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PANOZZO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -18413,12 +18413,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>PARKER Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>PARKER Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>The PARKER Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PARKER Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>PICOTEE Sofa and Loveseat in Light Gray Charcoal | GOODDEGG</t>
+          <t>PICOTEE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>The PICOTEE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PICOTEE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -18708,12 +18708,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>PLAISTOW Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>PLAISTOW Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>The PLAISTOW Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PLAISTOW Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>PORTHCAWL Sofa and Loveseat in Ivory | GOODDEGG</t>
+          <t>PORTHCAWL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>The PORTHCAWL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PORTHCAWL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="H127" s="26" t="inlineStr">
         <is>
-          <t>QUIRINO Sofa and Loveseat in Burgundy Dark Brown | GOODDEGG</t>
+          <t>QUIRINO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I127" s="26" t="inlineStr">
         <is>
-          <t>The QUIRINO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>QUIRINO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J127" s="26" t="inlineStr">
@@ -19151,12 +19151,12 @@
       </c>
       <c r="H128" s="26" t="inlineStr">
         <is>
-          <t>QUIRINO Sofa and Loveseat in Light Brown Dark Brown | GOODDEGG</t>
+          <t>QUIRINO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I128" s="26" t="inlineStr">
         <is>
-          <t>The QUIRINO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>QUIRINO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J128" s="26" t="inlineStr">
@@ -19303,12 +19303,12 @@
       </c>
       <c r="H129" s="26" t="inlineStr">
         <is>
-          <t>QUIRINO Sofa and Loveseat in Tan Dark Brown | GOODDEGG</t>
+          <t>QUIRINO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I129" s="26" t="inlineStr">
         <is>
-          <t>The QUIRINO Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>QUIRINO Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J129" s="26" t="inlineStr">
@@ -19455,12 +19455,12 @@
       </c>
       <c r="H130" s="28" t="inlineStr">
         <is>
-          <t>RONJA Sofa and Loveseat in Dark Brown | GOODDEGG</t>
+          <t>RONJA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I130" s="28" t="inlineStr">
         <is>
-          <t>The RONJA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RONJA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J130" s="28" t="inlineStr">
@@ -19603,12 +19603,12 @@
       </c>
       <c r="H131" s="28" t="inlineStr">
         <is>
-          <t>RONJA Sofa and Loveseat in Dark Brown | GOODDEGG</t>
+          <t>RONJA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I131" s="28" t="inlineStr">
         <is>
-          <t>The RONJA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RONJA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J131" s="28" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The SAN ROQUE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SAN ROQUE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -19895,12 +19895,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>SILVAN Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>SILVAN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>The SILVAN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SILVAN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -20041,12 +20041,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>SINATRA Sofa &amp; Loveseat in Light Mocha Navy Champagne | GO</t>
+          <t>SINATRA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The SINATRA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINATRA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -20189,12 +20189,12 @@
       </c>
       <c r="H135" s="32" t="inlineStr">
         <is>
-          <t>SISSETON Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>SISSETON Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I135" s="32" t="inlineStr">
         <is>
-          <t>The SISSETON Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SISSETON Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J135" s="32" t="inlineStr">
@@ -20341,12 +20341,12 @@
       </c>
       <c r="H136" s="32" t="inlineStr">
         <is>
-          <t>SISSETON Sofa and Loveseat in Purple | GOODDEGG</t>
+          <t>SISSETON Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I136" s="32" t="inlineStr">
         <is>
-          <t>The SISSETON Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SISSETON Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J136" s="32" t="inlineStr">
@@ -20493,12 +20493,12 @@
       </c>
       <c r="H137" s="32" t="inlineStr">
         <is>
-          <t>SISSETON Sofa and Loveseat in Navy | GOODDEGG</t>
+          <t>SISSETON Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I137" s="32" t="inlineStr">
         <is>
-          <t>The SISSETON Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SISSETON Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J137" s="32" t="inlineStr">
@@ -20646,12 +20646,12 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>SKYLINE Sofa and Loveseat in Light Gray Brown | GOODDEGG</t>
+          <t>SKYLINE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>The SKYLINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SKYLINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J138" s="14" t="inlineStr">
@@ -20799,12 +20799,12 @@
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
-          <t>SKYLINE Sofa and Loveseat in Pewter Gray | GOODDEGG</t>
+          <t>SKYLINE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
-          <t>The SKYLINE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SKYLINE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -20951,12 +20951,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>STEPHNEY Sofa and Loveseat in Gray Gold | GOODDEGG</t>
+          <t>STEPHNEY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>The STEPHNEY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STEPHNEY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -21099,12 +21099,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>STICKNEY Sofa and Loveseat in Light Gray Navy | GOODDEGG</t>
+          <t>STICKNEY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>The STICKNEY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STICKNEY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -21246,12 +21246,12 @@
       </c>
       <c r="H142" s="35" t="inlineStr">
         <is>
-          <t>TABITHA Sofa and Loveseat in Brown Gold | GOODDEGG</t>
+          <t>TABITHA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I142" s="35" t="inlineStr">
         <is>
-          <t>The TABITHA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TABITHA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J142" s="35" t="inlineStr">
@@ -21397,12 +21397,12 @@
       </c>
       <c r="H143" s="35" t="inlineStr">
         <is>
-          <t>TABITHA Sofa and Loveseat in Wine Gold | GOODDEGG</t>
+          <t>TABITHA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I143" s="35" t="inlineStr">
         <is>
-          <t>The TABITHA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TABITHA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J143" s="35" t="inlineStr">
@@ -21546,12 +21546,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>TEPIC Manual Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>TEPIC Manual Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>TEPIC Manual Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TEPIC Manual Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -21693,12 +21693,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>TILDE Sofa and Loveseat in Brown Dark Walnut | GOODDEGG</t>
+          <t>TILDE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The TILDE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TILDE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -21836,12 +21836,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ULVERY Sofa and Loveseat in Beige Brown | GOODDEGG</t>
+          <t>ULVERY Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>The ULVERY Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ULVERY Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -21975,7 +21975,7 @@
       </c>
       <c r="I147" s="18" t="inlineStr">
         <is>
-          <t>The VALDOSTA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALDOSTA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J147" s="18" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="I148" s="18" t="inlineStr">
         <is>
-          <t>The VALDOSTA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALDOSTA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J148" s="18" t="inlineStr">
@@ -22237,12 +22237,12 @@
       </c>
       <c r="H149" s="20" t="inlineStr">
         <is>
-          <t>VERACRUZ Sofa and Loveseat in Dark Cherry Beige | GOODDEGG</t>
+          <t>VERACRUZ Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I149" s="20" t="inlineStr">
         <is>
-          <t>The VERACRUZ Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERACRUZ Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J149" s="20" t="inlineStr">
@@ -22390,12 +22390,12 @@
       </c>
       <c r="H150" s="20" t="inlineStr">
         <is>
-          <t>VERACRUZ Sofa and Loveseat in Dark Cherry Light Brown | GOODDEG</t>
+          <t>VERACRUZ Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I150" s="20" t="inlineStr">
         <is>
-          <t>The VERACRUZ Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERACRUZ Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J150" s="20" t="inlineStr">
@@ -22542,12 +22542,12 @@
       </c>
       <c r="H151" s="39" t="inlineStr">
         <is>
-          <t>VERDAL Sofa and Loveseat in Black | GOODDEGG</t>
+          <t>VERDAL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I151" s="39" t="inlineStr">
         <is>
-          <t>The VERDAL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERDAL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J151" s="39" t="inlineStr">
@@ -22694,12 +22694,12 @@
       </c>
       <c r="H152" s="39" t="inlineStr">
         <is>
-          <t>VERDAL Sofa and Loveseat in Charcoal Gray | GOODDEGG</t>
+          <t>VERDAL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I152" s="39" t="inlineStr">
         <is>
-          <t>The VERDAL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERDAL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J152" s="39" t="inlineStr">
@@ -22846,12 +22846,12 @@
       </c>
       <c r="H153" s="39" t="inlineStr">
         <is>
-          <t>VERDAL Sofa and Loveseat in Off-White | GOODDEGG</t>
+          <t>VERDAL Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I153" s="39" t="inlineStr">
         <is>
-          <t>The VERDAL Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERDAL Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J153" s="39" t="inlineStr">
@@ -22996,12 +22996,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>VERDANTE Sofa and Loveseat in Emerald Green Gold | GOODDEGG</t>
+          <t>VERDANTE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>The VERDANTE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERDANTE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -23143,12 +23143,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>VERNE Sofa and Loveseat in Bluish Gray | GOODDEGG</t>
+          <t>VERNE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>The VERNE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VERNE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>VISCONTTI Sofa and Loveseat in Gold Gray | GOODDEGG</t>
+          <t>VISCONTTI Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The VISCONTTI Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VISCONTTI Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -23437,12 +23437,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>VIVIANA Sofa and Loveseat in Gray Black | GOODDEGG</t>
+          <t>VIVIANA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The VIVIANA Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VIVIANA Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -23584,12 +23584,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>WALDSTONE Sofa and Loveseat in Navy | GOODDEGG</t>
+          <t>WALDSTONE Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>The WALDSTONE Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WALDSTONE Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -23731,12 +23731,12 @@
       </c>
       <c r="H159" s="45" t="inlineStr">
         <is>
-          <t>WEST ACTION Sofa and Loveseat in Chocolate | GOODDEGG</t>
+          <t>WEST ACTION Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I159" s="45" t="inlineStr">
         <is>
-          <t>WEST ACTION Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WEST ACTION Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J159" s="45" t="inlineStr">
@@ -23882,12 +23882,12 @@
       </c>
       <c r="H160" s="45" t="inlineStr">
         <is>
-          <t>WEST ACTION Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>WEST ACTION Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I160" s="45" t="inlineStr">
         <is>
-          <t>WEST ACTION Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WEST ACTION Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J160" s="45" t="inlineStr">
@@ -24033,12 +24033,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>WEST BROMPTON Sofa and Loveseat in Navy Yellow | GOODDEGG</t>
+          <t>WEST BROMPTON Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>WEST BROMPTON Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WEST BROMPTON Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -24179,12 +24179,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>YUCATAN Sofa and Loveseat in Dark Cherry Beige | GOODDEGG</t>
+          <t>YUCATAN Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>The YUCATAN Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YUCATAN Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -24323,12 +24323,12 @@
       </c>
       <c r="H163" s="41" t="inlineStr">
         <is>
-          <t>AGATA Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>AGATA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I163" s="41" t="inlineStr">
         <is>
-          <t>The AGATA Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AGATA Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J163" s="41" t="inlineStr">
@@ -24471,12 +24471,12 @@
       </c>
       <c r="H164" s="41" t="inlineStr">
         <is>
-          <t>AGATA Sofa and Loveseat in Dark Gray | GOODDEGG</t>
+          <t>AGATA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I164" s="41" t="inlineStr">
         <is>
-          <t>The AGATA Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AGATA Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J164" s="41" t="inlineStr">
@@ -24620,12 +24620,12 @@
       </c>
       <c r="H165" s="35" t="inlineStr">
         <is>
-          <t>AGATA Sofa and Loveseat and Chair in Brown | GOODDEGG</t>
+          <t>AGATA Sofa and Loveseat and Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I165" s="35" t="inlineStr">
         <is>
-          <t>The AGATA Sofa and Loveseat and Chair brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AGATA Sofa and Loveseat and Chair Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J165" s="35" t="inlineStr">
@@ -24769,12 +24769,12 @@
       </c>
       <c r="H166" s="35" t="inlineStr">
         <is>
-          <t>AGATA Sofa and Loveseat and Chair in Dark Gray | GOODDEGG</t>
+          <t>AGATA Sofa and Loveseat and Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I166" s="35" t="inlineStr">
         <is>
-          <t>The AGATA Sofa and Loveseat and Chair brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AGATA Sofa and Loveseat and Chair Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J166" s="35" t="inlineStr">
@@ -24919,12 +24919,12 @@
       </c>
       <c r="H167" s="37" t="inlineStr">
         <is>
-          <t>ALTAMURA Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>ALTAMURA Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I167" s="37" t="inlineStr">
         <is>
-          <t>The ALTAMURA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALTAMURA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J167" s="37" t="inlineStr">
@@ -25069,12 +25069,12 @@
       </c>
       <c r="H168" s="37" t="inlineStr">
         <is>
-          <t>ALTAMURA Power Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>ALTAMURA Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I168" s="37" t="inlineStr">
         <is>
-          <t>The ALTAMURA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALTAMURA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J168" s="37" t="inlineStr">
@@ -25219,12 +25219,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>AMIRAH Sofa and Glider Loveseat in Dark Gray | GOODDEGG</t>
+          <t>AMIRAH Sofa and Glider Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>The AMIRAH Sofa and Glider Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMIRAH Sofa and Glider Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -25364,12 +25364,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ANTENOR Power Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>ANTENOR Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>The ANTENOR Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTENOR Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -25508,12 +25508,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ANTONIUS Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>ANTONIUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>The ANTONIUS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTONIUS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -25655,12 +25655,12 @@
       </c>
       <c r="H172" s="39" t="inlineStr">
         <is>
-          <t>ARTEMIA Power Sofa and Loveseat in Light Taupe | GOODDEGG</t>
+          <t>ARTEMIA Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I172" s="39" t="inlineStr">
         <is>
-          <t>The ARTEMIA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARTEMIA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J172" s="39" t="inlineStr">
@@ -25806,12 +25806,12 @@
       </c>
       <c r="H173" s="39" t="inlineStr">
         <is>
-          <t>ARTEMIA Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>ARTEMIA Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I173" s="39" t="inlineStr">
         <is>
-          <t>The ARTEMIA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARTEMIA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J173" s="39" t="inlineStr">
@@ -25958,12 +25958,12 @@
       </c>
       <c r="H174" s="45" t="inlineStr">
         <is>
-          <t>ASCONA Power Sofa and Loveseat in Black | GOODDEGG</t>
+          <t>ASCONA Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I174" s="45" t="inlineStr">
         <is>
-          <t>The ASCONA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ASCONA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J174" s="45" t="inlineStr">
@@ -26110,12 +26110,12 @@
       </c>
       <c r="H175" s="45" t="inlineStr">
         <is>
-          <t>ASCONA Power Sofa and Loveseat in Light Taupe | GOODDEGG</t>
+          <t>ASCONA Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I175" s="45" t="inlineStr">
         <is>
-          <t>The ASCONA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ASCONA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J175" s="45" t="inlineStr">
@@ -26259,12 +26259,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>BALDERICO Power Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>BALDERICO Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>The BALDERICO Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BALDERICO Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -26400,12 +26400,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>COSIMO Sofa and Loveseat in Mocha | GOODDEGG</t>
+          <t>COSIMO Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>The COSIMO Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>COSIMO Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -26542,12 +26542,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>COSIMO Sofa and Loveseat and Chair in Mocha | GOODDEGG</t>
+          <t>COSIMO Sofa and Loveseat and Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>The COSIMO Sofa and Loveseat and Chair brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>COSIMO Sofa and Loveseat and Chair Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -26682,7 +26682,7 @@
       </c>
       <c r="I179" s="41" t="inlineStr">
         <is>
-          <t>The DEMETRIUS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEMETRIUS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J179" s="41" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="I180" s="41" t="inlineStr">
         <is>
-          <t>The DEMETRIUS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEMETRIUS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J180" s="41" t="inlineStr">
@@ -26940,12 +26940,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>EZEKIUS Manual Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>EZEKIUS Manual Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>The EZEKIUS Manual Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EZEKIUS Manual Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -27087,12 +27087,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>FLORINE Power Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>FLORINE Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>The FLORINE Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FLORINE Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -27231,12 +27231,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>GIRALDUS Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>GIRALDUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>The GIRALDUS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GIRALDUS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -27377,12 +27377,12 @@
       </c>
       <c r="H184" s="45" t="inlineStr">
         <is>
-          <t>GORGIUS Power Sofa and Loveseat in Espresso | GOODDEGG</t>
+          <t>GORGIUS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I184" s="45" t="inlineStr">
         <is>
-          <t>The GORGIUS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GORGIUS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J184" s="45" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="H185" s="45" t="inlineStr">
         <is>
-          <t>GORGIUS Power Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>GORGIUS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I185" s="45" t="inlineStr">
         <is>
-          <t>The GORGIUS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GORGIUS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J185" s="45" t="inlineStr">
@@ -27676,12 +27676,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>GRANUCCI Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>GRANUCCI Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>The GRANUCCI Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRANUCCI Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -27821,12 +27821,12 @@
       </c>
       <c r="H187" s="28" t="inlineStr">
         <is>
-          <t>JACOBUS Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>JACOBUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I187" s="28" t="inlineStr">
         <is>
-          <t>The JACOBUS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JACOBUS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J187" s="28" t="inlineStr">
@@ -27970,12 +27970,12 @@
       </c>
       <c r="H188" s="28" t="inlineStr">
         <is>
-          <t>JACOBUS Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>JACOBUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I188" s="28" t="inlineStr">
         <is>
-          <t>The JACOBUS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JACOBUS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J188" s="28" t="inlineStr">
@@ -28118,12 +28118,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>LEOLINUS Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>LEOLINUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>The LEOLINUS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEOLINUS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -28259,12 +28259,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>LETHA Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>LETHA Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>The LETHA Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LETHA Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -28403,12 +28403,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>MATTHIAS Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>MATTHIAS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>The MATTHIAS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MATTHIAS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -28551,12 +28551,12 @@
       </c>
       <c r="H192" s="18" t="inlineStr">
         <is>
-          <t>MORCOTE Power Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>MORCOTE Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I192" s="18" t="inlineStr">
         <is>
-          <t>The MORCOTE Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORCOTE Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J192" s="18" t="inlineStr">
@@ -28703,12 +28703,12 @@
       </c>
       <c r="H193" s="18" t="inlineStr">
         <is>
-          <t>MORCOTE Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>MORCOTE Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I193" s="18" t="inlineStr">
         <is>
-          <t>The MORCOTE Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORCOTE Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J193" s="18" t="inlineStr">
@@ -28855,12 +28855,12 @@
       </c>
       <c r="H194" s="18" t="inlineStr">
         <is>
-          <t>MORCOTE Power Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>MORCOTE Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I194" s="18" t="inlineStr">
         <is>
-          <t>The MORCOTE Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORCOTE Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J194" s="18" t="inlineStr">
@@ -29003,12 +29003,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ONORIA Sofa and Loveseat Manual in Brown | GOODDEGG</t>
+          <t>ONORIA Sofa and Loveseat Manual | GOODDEGG</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>The ONORIA Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ONORIA Sofa and Loveseat Manual Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -29145,12 +29145,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>OSIAS Sofa and Loveseat in Brown | GOODDEGG</t>
+          <t>OSIAS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>The OSIAS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OSIAS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -29288,12 +29288,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>OSIAS Sofa and Loveseat and Chair in Brown | GOODDEGG</t>
+          <t>OSIAS Sofa and Loveseat and Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>The OSIAS Sofa and Loveseat and Chair brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OSIAS Sofa and Loveseat and Chair Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -29435,12 +29435,12 @@
       </c>
       <c r="H198" s="24" t="inlineStr">
         <is>
-          <t>PHINEAS Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>PHINEAS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I198" s="24" t="inlineStr">
         <is>
-          <t>The PHINEAS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PHINEAS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J198" s="24" t="inlineStr">
@@ -29586,12 +29586,12 @@
       </c>
       <c r="H199" s="24" t="inlineStr">
         <is>
-          <t>PHINEAS Power Sofa and Loveseat in Pale Blue | GOODDEGG</t>
+          <t>PHINEAS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I199" s="24" t="inlineStr">
         <is>
-          <t>The PHINEAS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PHINEAS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J199" s="24" t="inlineStr">
@@ -29737,12 +29737,12 @@
       </c>
       <c r="H200" s="24" t="inlineStr">
         <is>
-          <t>PHINEAS Power Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>PHINEAS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I200" s="24" t="inlineStr">
         <is>
-          <t>The PHINEAS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PHINEAS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J200" s="24" t="inlineStr">
@@ -29884,12 +29884,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>SANDBACH Sofa and Loveseat in Light Gray | GOODDEGG</t>
+          <t>SANDBACH Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>The SANDBACH Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANDBACH Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -30028,12 +30028,12 @@
       </c>
       <c r="H202" s="30" t="inlineStr">
         <is>
-          <t>SCHLIEREN Power Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>SCHLIEREN Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I202" s="30" t="inlineStr">
         <is>
-          <t>The SCHLIEREN Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCHLIEREN Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J202" s="30" t="inlineStr">
@@ -30176,12 +30176,12 @@
       </c>
       <c r="H203" s="30" t="inlineStr">
         <is>
-          <t>SCHLIEREN Power Sofa and Loveseat in Black | GOODDEGG</t>
+          <t>SCHLIEREN Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I203" s="30" t="inlineStr">
         <is>
-          <t>The SCHLIEREN Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCHLIEREN Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J203" s="30" t="inlineStr">
@@ -30324,12 +30324,12 @@
       </c>
       <c r="H204" s="30" t="inlineStr">
         <is>
-          <t>SCHLIEREN Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>SCHLIEREN Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I204" s="30" t="inlineStr">
         <is>
-          <t>The SCHLIEREN Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCHLIEREN Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J204" s="30" t="inlineStr">
@@ -30472,12 +30472,12 @@
       </c>
       <c r="H205" s="30" t="inlineStr">
         <is>
-          <t>SCHLIEREN Power Sofa and Loveseat in Light Brown | GOODDEGG</t>
+          <t>SCHLIEREN Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I205" s="30" t="inlineStr">
         <is>
-          <t>The SCHLIEREN Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCHLIEREN Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J205" s="30" t="inlineStr">
@@ -30624,12 +30624,12 @@
       </c>
       <c r="H206" s="41" t="inlineStr">
         <is>
-          <t>SOTERIOS Power Sofa and Loveseat in Charcoal | GOODDEGG</t>
+          <t>SOTERIOS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I206" s="41" t="inlineStr">
         <is>
-          <t>The SOTERIOS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOTERIOS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J206" s="41" t="inlineStr">
@@ -30776,12 +30776,12 @@
       </c>
       <c r="H207" s="41" t="inlineStr">
         <is>
-          <t>SOTERIOS Power Sofa and Loveseat in Medium Brown | GOODDEGG</t>
+          <t>SOTERIOS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I207" s="41" t="inlineStr">
         <is>
-          <t>The SOTERIOS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOTERIOS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J207" s="41" t="inlineStr">
@@ -30928,12 +30928,12 @@
       </c>
       <c r="H208" s="16" t="inlineStr">
         <is>
-          <t>TERENTIUS Power Sofa and Loveseat in Caramel Brown | GOODDEGG</t>
+          <t>TERENTIUS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I208" s="16" t="inlineStr">
         <is>
-          <t>The TERENTIUS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TERENTIUS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J208" s="16" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="H209" s="16" t="inlineStr">
         <is>
-          <t>TERENTIUS Power Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>TERENTIUS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I209" s="16" t="inlineStr">
         <is>
-          <t>The TERENTIUS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TERENTIUS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J209" s="16" t="inlineStr">
@@ -31227,7 +31227,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>The THADDEA Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THADDEA Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -31350,12 +31350,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>THEMIS Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>THEMIS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>The THEMIS Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THEMIS Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -31494,12 +31494,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>THEOLA Sofa and Loveseat and Chair in Gray | GOODDEGG</t>
+          <t>THEOLA Sofa and Loveseat and Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>The THEOLA Sofa and Loveseat and Chair brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THEOLA Sofa and Loveseat and Chair Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -31639,12 +31639,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>TREHARRIS Power Sofa and Loveseat in White | GOODDEGG</t>
+          <t>TREHARRIS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>The TREHARRIS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TREHARRIS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -31787,12 +31787,12 @@
       </c>
       <c r="H214" s="37" t="inlineStr">
         <is>
-          <t>VASILIOS Power Sofa and Loveseat in Gray | GOODDEGG</t>
+          <t>VASILIOS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I214" s="37" t="inlineStr">
         <is>
-          <t>The VASILIOS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VASILIOS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J214" s="37" t="inlineStr">
@@ -31939,12 +31939,12 @@
       </c>
       <c r="H215" s="37" t="inlineStr">
         <is>
-          <t>VASILIOS Power Sofa and Loveseat in Taupe | GOODDEGG</t>
+          <t>VASILIOS Power Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I215" s="37" t="inlineStr">
         <is>
-          <t>The VASILIOS Power Sofa and Loveseat brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VASILIOS Power Sofa and Loveseat Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J215" s="37" t="inlineStr">
@@ -32091,12 +32091,12 @@
       </c>
       <c r="H216" s="22" t="inlineStr">
         <is>
-          <t>HENRICUS Sofa and Loveseat in Beige | GOODDEGG</t>
+          <t>HENRICUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I216" s="22" t="inlineStr">
         <is>
-          <t>The HENRICUS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HENRICUS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J216" s="22" t="inlineStr">
@@ -32243,12 +32243,12 @@
       </c>
       <c r="H217" s="22" t="inlineStr">
         <is>
-          <t>HENRICUS Sofa and Loveseat in Dark Brown | GOODDEGG</t>
+          <t>HENRICUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I217" s="22" t="inlineStr">
         <is>
-          <t>The HENRICUS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HENRICUS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J217" s="22" t="inlineStr">
@@ -32395,12 +32395,12 @@
       </c>
       <c r="H218" s="22" t="inlineStr">
         <is>
-          <t>HENRICUS Sofa and Loveseat in Dark Gray | GOODDEGG</t>
+          <t>HENRICUS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I218" s="22" t="inlineStr">
         <is>
-          <t>The HENRICUS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HENRICUS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J218" s="22" t="inlineStr">
@@ -32544,12 +32544,12 @@
       </c>
       <c r="H219" s="32" t="inlineStr">
         <is>
-          <t>JOSIAS Sofa and Loveseat in Dark Gray Leatherette | GOODDEGG</t>
+          <t>JOSIAS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I219" s="32" t="inlineStr">
         <is>
-          <t>The JOSIAS Sofa and Loveseat makes it easy to furnish the room with a coordinated look. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOSIAS Sofa and Loveseat Upholstery Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J219" s="32" t="inlineStr">
@@ -32693,12 +32693,12 @@
       </c>
       <c r="H220" s="32" t="inlineStr">
         <is>
-          <t>JOSIAS Sofa and Loveseat in Light Gray Fabric | GOODDEGG</t>
+          <t>JOSIAS Sofa and Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I220" s="32" t="inlineStr">
         <is>
-          <t>The JOSIAS Sofa and Loveseat offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOSIAS Sofa and Loveseat supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J220" s="32" t="inlineStr">
